--- a/AAII_Financials/Quarterly/JD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JD_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
   <si>
     <t>JD</t>
   </si>
@@ -656,416 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>34202100</v>
+        <v>42550800</v>
       </c>
       <c r="E8" s="3">
-        <v>39757500</v>
+        <v>34435000</v>
       </c>
       <c r="F8" s="3">
-        <v>33547400</v>
+        <v>40028200</v>
       </c>
       <c r="G8" s="3">
-        <v>40795200</v>
+        <v>33775700</v>
       </c>
       <c r="H8" s="3">
-        <v>33627300</v>
+        <v>41072900</v>
       </c>
       <c r="I8" s="3">
-        <v>36950200</v>
+        <v>33856200</v>
       </c>
       <c r="J8" s="3">
+        <v>37201800</v>
+      </c>
+      <c r="K8" s="3">
         <v>33091600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>38014500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>31089400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>36450800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>28282100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>31226500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>25672200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>29627300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>23065300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>26281900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>20763100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>22959900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>18498800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>19581700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>14663400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>17546300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>14366400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>16349600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>12428800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>13832100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>10939000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>11548800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>8751100</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>28851400</v>
+        <v>36503200</v>
       </c>
       <c r="E9" s="3">
-        <v>34036400</v>
+        <v>29047800</v>
       </c>
       <c r="F9" s="3">
-        <v>28574000</v>
+        <v>34268200</v>
       </c>
       <c r="G9" s="3">
-        <v>35059800</v>
+        <v>28768500</v>
       </c>
       <c r="H9" s="3">
-        <v>28629400</v>
+        <v>35298400</v>
       </c>
       <c r="I9" s="3">
-        <v>31994000</v>
+        <v>28824300</v>
       </c>
       <c r="J9" s="3">
+        <v>32211800</v>
+      </c>
+      <c r="K9" s="3">
         <v>28473300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>32899800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>26669600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>31893800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>24228300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>26891500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>21723700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>25407600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>19510100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>22586700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>17665900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>19579600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>15720700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>16797400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>12408700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>15176900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>12334900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>14218500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>10502000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>11955000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>18670800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>19852900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>14923400</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>5350700</v>
+        <v>6047600</v>
       </c>
       <c r="E10" s="3">
-        <v>5721100</v>
+        <v>5387200</v>
       </c>
       <c r="F10" s="3">
-        <v>4973400</v>
+        <v>5760000</v>
       </c>
       <c r="G10" s="3">
-        <v>5735400</v>
+        <v>5007200</v>
       </c>
       <c r="H10" s="3">
-        <v>4997900</v>
+        <v>5774500</v>
       </c>
       <c r="I10" s="3">
-        <v>4956200</v>
+        <v>5032000</v>
       </c>
       <c r="J10" s="3">
+        <v>4990000</v>
+      </c>
+      <c r="K10" s="3">
         <v>4618200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5114600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4419800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4557000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4053800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4335000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3948500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4219700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3555200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3695200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3097200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3380300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2778100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2784300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2254700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2369400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2031400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2131100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1926800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1877100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>-7731900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>-8304100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>-6172300</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,100 +1110,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>514800</v>
+        <v>594300</v>
       </c>
       <c r="E12" s="3">
-        <v>550800</v>
+        <v>518300</v>
       </c>
       <c r="F12" s="3">
-        <v>565600</v>
+        <v>554600</v>
       </c>
       <c r="G12" s="3">
-        <v>590400</v>
+        <v>569400</v>
       </c>
       <c r="H12" s="3">
-        <v>556900</v>
+        <v>594400</v>
       </c>
       <c r="I12" s="3">
-        <v>547800</v>
+        <v>560700</v>
       </c>
       <c r="J12" s="3">
+        <v>551500</v>
+      </c>
+      <c r="K12" s="3">
         <v>600100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>562000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>565400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>526700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>627000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>623400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>601500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>527400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>616900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>549200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>548200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>565400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>564000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>505400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>478900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>395500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>342700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>302600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>257500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>226400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>184500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>168700</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>175700</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1282,192 +1298,201 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>597100</v>
+      </c>
+      <c r="E14" s="3">
         <v>-700</v>
       </c>
-      <c r="E14" s="3">
-        <v>-143300</v>
-      </c>
       <c r="F14" s="3">
-        <v>-68100</v>
+        <v>-144300</v>
       </c>
       <c r="G14" s="3">
+        <v>-68500</v>
+      </c>
+      <c r="H14" s="3">
         <v>-11500</v>
       </c>
-      <c r="H14" s="3">
-        <v>-173400</v>
-      </c>
       <c r="I14" s="3">
+        <v>-174600</v>
+      </c>
+      <c r="J14" s="3">
         <v>-4300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>490000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-2500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-82300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-12500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-11500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-154400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-50700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-28800</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>-598200</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>10</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>3100</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>10</v>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3" t="s">
+      <c r="AE14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>58700</v>
+      </c>
+      <c r="E15" s="3">
+        <v>58500</v>
+      </c>
+      <c r="F15" s="3">
+        <v>60900</v>
+      </c>
+      <c r="G15" s="3">
+        <v>62000</v>
+      </c>
+      <c r="H15" s="3">
+        <v>61000</v>
+      </c>
+      <c r="I15" s="3">
+        <v>61600</v>
+      </c>
+      <c r="J15" s="3">
         <v>58100</v>
       </c>
-      <c r="E15" s="3">
-        <v>60500</v>
-      </c>
-      <c r="F15" s="3">
-        <v>61600</v>
-      </c>
-      <c r="G15" s="3">
-        <v>60600</v>
-      </c>
-      <c r="H15" s="3">
-        <v>61200</v>
-      </c>
-      <c r="I15" s="3">
-        <v>57700</v>
-      </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>54100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>51900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>53400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>53300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>50600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>51900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>50300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>43800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>44500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>72600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>22500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>22600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>67800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>65800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>63900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>64600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>64000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>66700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>66300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>65700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>63900</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>65100</v>
       </c>
       <c r="AF15" s="3">
         <v>65100</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>65100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>32916900</v>
+        <v>42259400</v>
       </c>
       <c r="E17" s="3">
-        <v>38611600</v>
+        <v>33141000</v>
       </c>
       <c r="F17" s="3">
-        <v>32657000</v>
+        <v>38874400</v>
       </c>
       <c r="G17" s="3">
-        <v>40137800</v>
+        <v>32879300</v>
       </c>
       <c r="H17" s="3">
-        <v>32418400</v>
+        <v>40411000</v>
       </c>
       <c r="I17" s="3">
-        <v>36427000</v>
+        <v>32639100</v>
       </c>
       <c r="J17" s="3">
+        <v>36675000</v>
+      </c>
+      <c r="K17" s="3">
         <v>33249000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>38068500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>30723700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>36407600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>28051100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>31143700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>25026300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>28884000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>22699300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>26200400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>19997300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>22613600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>18311500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>19718100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>14754400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>17694700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>14365700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>16586500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>12354200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>13891900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>10842800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>11598000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>8785200</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1285200</v>
+        <v>291400</v>
       </c>
       <c r="E18" s="3">
-        <v>1145900</v>
+        <v>1294000</v>
       </c>
       <c r="F18" s="3">
-        <v>890300</v>
+        <v>1153700</v>
       </c>
       <c r="G18" s="3">
-        <v>657400</v>
+        <v>896400</v>
       </c>
       <c r="H18" s="3">
-        <v>1208900</v>
+        <v>661900</v>
       </c>
       <c r="I18" s="3">
-        <v>523200</v>
+        <v>1217100</v>
       </c>
       <c r="J18" s="3">
+        <v>526700</v>
+      </c>
+      <c r="K18" s="3">
         <v>-157400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-54000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>365700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>43200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>231000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>82800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>645900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>743300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>366100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>81500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>765800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>346300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>187200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-136400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-91100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-148400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-236900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>74600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-59800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>96200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-49200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-34100</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,468 +1747,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>304300</v>
+        <v>297100</v>
       </c>
       <c r="E20" s="3">
-        <v>288400</v>
+        <v>306400</v>
       </c>
       <c r="F20" s="3">
-        <v>269300</v>
+        <v>290400</v>
       </c>
       <c r="G20" s="3">
-        <v>-34100</v>
+        <v>271100</v>
       </c>
       <c r="H20" s="3">
-        <v>-64300</v>
+        <v>-34300</v>
       </c>
       <c r="I20" s="3">
-        <v>269400</v>
+        <v>-64800</v>
       </c>
       <c r="J20" s="3">
+        <v>271200</v>
+      </c>
+      <c r="K20" s="3">
         <v>-197500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-591600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-698300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>140600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>378600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3292200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>617500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1840500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-115100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>573300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-562800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-172200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>990200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-542100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>534700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-120500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>265800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>95700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>120500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>42100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-15000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-113100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-26100</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1596100</v>
+        <v>556100</v>
       </c>
       <c r="E21" s="3">
-        <v>1447400</v>
+        <v>1606900</v>
       </c>
       <c r="F21" s="3">
-        <v>1430200</v>
+        <v>1457200</v>
       </c>
       <c r="G21" s="3">
-        <v>639400</v>
+        <v>1440000</v>
       </c>
       <c r="H21" s="3">
-        <v>1165800</v>
+        <v>643800</v>
       </c>
       <c r="I21" s="3">
-        <v>798200</v>
+        <v>1173700</v>
       </c>
       <c r="J21" s="3">
+        <v>803700</v>
+      </c>
+      <c r="K21" s="3">
         <v>-124000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-641300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-321900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>153900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>841900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3397100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1272200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2592000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>472700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>658500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>207000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>126300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1433100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-660600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>476100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-259600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>437800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-31900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>117300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-15000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>219700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-158100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-50000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>98000</v>
+        <v>128900</v>
       </c>
       <c r="E22" s="3">
-        <v>90300</v>
+        <v>98700</v>
       </c>
       <c r="F22" s="3">
-        <v>81500</v>
+        <v>90900</v>
       </c>
       <c r="G22" s="3">
-        <v>96400</v>
+        <v>82000</v>
       </c>
       <c r="H22" s="3">
-        <v>79900</v>
+        <v>97000</v>
       </c>
       <c r="I22" s="3">
-        <v>66800</v>
+        <v>80500</v>
       </c>
       <c r="J22" s="3">
+        <v>67300</v>
+      </c>
+      <c r="K22" s="3">
         <v>47600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>61500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>39300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>33400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>35900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>41200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>43900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>47800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>32700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>33800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>25100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>23700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>28600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>21000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>33700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>34400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>32800</v>
       </c>
-      <c r="AA22" s="3" t="s">
+      <c r="AB22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>42000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>30900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>27600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>9200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>10400</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1491500</v>
+        <v>459600</v>
       </c>
       <c r="E23" s="3">
-        <v>1344100</v>
+        <v>1501700</v>
       </c>
       <c r="F23" s="3">
-        <v>1078100</v>
+        <v>1353200</v>
       </c>
       <c r="G23" s="3">
-        <v>526900</v>
+        <v>1085500</v>
       </c>
       <c r="H23" s="3">
-        <v>1064600</v>
+        <v>530500</v>
       </c>
       <c r="I23" s="3">
-        <v>725700</v>
+        <v>1071800</v>
       </c>
       <c r="J23" s="3">
+        <v>730700</v>
+      </c>
+      <c r="K23" s="3">
         <v>-402500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-707200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-371900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>150400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>573800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3333800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1219500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2536000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>218300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>621000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>177900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>150400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1148800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-699500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>409900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-303300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>233600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-141200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>153100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-48600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>53600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-171500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-70600</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>356100</v>
+        <v>193800</v>
       </c>
       <c r="E24" s="3">
-        <v>388100</v>
+        <v>358500</v>
       </c>
       <c r="F24" s="3">
-        <v>222200</v>
+        <v>390800</v>
       </c>
       <c r="G24" s="3">
-        <v>82200</v>
+        <v>223700</v>
       </c>
       <c r="H24" s="3">
-        <v>241800</v>
+        <v>82700</v>
       </c>
       <c r="I24" s="3">
-        <v>169400</v>
+        <v>243400</v>
       </c>
       <c r="J24" s="3">
+        <v>170600</v>
+      </c>
+      <c r="K24" s="3">
         <v>83300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>25600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>92700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>81800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>66700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-46200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>101700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>117400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>51500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>73800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>93100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>67000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>42700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>8900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>7200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>23400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>21700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>7900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>13000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>14600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1135400</v>
+        <v>265800</v>
       </c>
       <c r="E26" s="3">
-        <v>955900</v>
+        <v>1143200</v>
       </c>
       <c r="F26" s="3">
-        <v>856000</v>
+        <v>962400</v>
       </c>
       <c r="G26" s="3">
-        <v>444800</v>
+        <v>861800</v>
       </c>
       <c r="H26" s="3">
-        <v>822800</v>
+        <v>447800</v>
       </c>
       <c r="I26" s="3">
-        <v>556300</v>
+        <v>828400</v>
       </c>
       <c r="J26" s="3">
+        <v>560100</v>
+      </c>
+      <c r="K26" s="3">
         <v>-485800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-732800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-464600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>68600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>507000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3380000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1117800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2418600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>166800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>547200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>84800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>83400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1106100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-708400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>402600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-326700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>212000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-143100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>145200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-46200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>40500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-186100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-70900</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1095800</v>
+        <v>471100</v>
       </c>
       <c r="E27" s="3">
-        <v>908700</v>
+        <v>1103300</v>
       </c>
       <c r="F27" s="3">
-        <v>864500</v>
+        <v>914900</v>
       </c>
       <c r="G27" s="3">
-        <v>418700</v>
+        <v>870400</v>
       </c>
       <c r="H27" s="3">
-        <v>823400</v>
+        <v>421500</v>
       </c>
       <c r="I27" s="3">
-        <v>604200</v>
+        <v>829000</v>
       </c>
       <c r="J27" s="3">
+        <v>608400</v>
+      </c>
+      <c r="K27" s="3">
         <v>-413000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-711600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-398900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>114100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>503500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3386100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1114100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2423600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>169200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>559600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>94300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>94500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1118200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-697800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>420000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-317400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>218800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-134900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>150500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-42600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>43500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-183400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-68000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2624,19 +2684,22 @@
         <v>0</v>
       </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-31100</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-8700</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-67100</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-66100</v>
       </c>
     </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2885,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-304300</v>
+        <v>-297100</v>
       </c>
       <c r="E32" s="3">
-        <v>-288400</v>
+        <v>-306400</v>
       </c>
       <c r="F32" s="3">
-        <v>-269300</v>
+        <v>-290400</v>
       </c>
       <c r="G32" s="3">
-        <v>34100</v>
+        <v>-271100</v>
       </c>
       <c r="H32" s="3">
-        <v>64300</v>
+        <v>34300</v>
       </c>
       <c r="I32" s="3">
-        <v>-269400</v>
+        <v>64800</v>
       </c>
       <c r="J32" s="3">
+        <v>-271200</v>
+      </c>
+      <c r="K32" s="3">
         <v>197500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>591600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>698300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-140600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-378600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3292200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-617500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1840500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>115100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-573300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>562800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>172200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-990200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>542100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-534700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>120500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-265800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-95700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-120500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-42100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>15000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>113100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1095800</v>
+        <v>471100</v>
       </c>
       <c r="E33" s="3">
-        <v>908700</v>
+        <v>1103300</v>
       </c>
       <c r="F33" s="3">
-        <v>864500</v>
+        <v>914900</v>
       </c>
       <c r="G33" s="3">
-        <v>418700</v>
+        <v>870400</v>
       </c>
       <c r="H33" s="3">
-        <v>823400</v>
+        <v>421500</v>
       </c>
       <c r="I33" s="3">
-        <v>604200</v>
+        <v>829000</v>
       </c>
       <c r="J33" s="3">
+        <v>608400</v>
+      </c>
+      <c r="K33" s="3">
         <v>-413000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-711600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-398900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>114100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>503500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3386100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1114100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2423600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>169200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>559600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>94300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>94500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1118200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-697800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>420000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-317400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>218800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-134900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>150500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-73700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>34800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-250600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-134000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1095800</v>
+        <v>471100</v>
       </c>
       <c r="E35" s="3">
-        <v>908700</v>
+        <v>1103300</v>
       </c>
       <c r="F35" s="3">
-        <v>864500</v>
+        <v>914900</v>
       </c>
       <c r="G35" s="3">
-        <v>418700</v>
+        <v>870400</v>
       </c>
       <c r="H35" s="3">
-        <v>823400</v>
+        <v>421500</v>
       </c>
       <c r="I35" s="3">
-        <v>604200</v>
+        <v>829000</v>
       </c>
       <c r="J35" s="3">
+        <v>608400</v>
+      </c>
+      <c r="K35" s="3">
         <v>-413000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-711600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-398900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>114100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>503500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3386100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1114100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2423600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>169200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>559600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>94300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>94500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1118200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-697800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>420000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-317400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>218800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-134900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>150500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-73700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>34800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-250600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-134000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,836 +3437,864 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>16013300</v>
+        <v>9994400</v>
       </c>
       <c r="E41" s="3">
-        <v>12568000</v>
+        <v>16122300</v>
       </c>
       <c r="F41" s="3">
-        <v>10269400</v>
+        <v>12653600</v>
       </c>
       <c r="G41" s="3">
-        <v>10889100</v>
+        <v>10339300</v>
       </c>
       <c r="H41" s="3">
-        <v>11509800</v>
+        <v>10963300</v>
       </c>
       <c r="I41" s="3">
-        <v>10883600</v>
+        <v>11588200</v>
       </c>
       <c r="J41" s="3">
+        <v>10957700</v>
+      </c>
+      <c r="K41" s="3">
         <v>11662700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9750300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>12508900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>13981000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9940000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11983000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10773900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10546800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6867200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5692900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4946600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5007900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5202700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4975900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4758300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5055400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5051100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3812400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3207200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4134000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3435700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2263900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3611700</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>17450800</v>
+        <v>16439700</v>
       </c>
       <c r="E42" s="3">
-        <v>19897500</v>
+        <v>17569600</v>
       </c>
       <c r="F42" s="3">
-        <v>16906500</v>
+        <v>20032900</v>
       </c>
       <c r="G42" s="3">
-        <v>19482400</v>
+        <v>17021600</v>
       </c>
       <c r="H42" s="3">
-        <v>17736200</v>
+        <v>19615000</v>
       </c>
       <c r="I42" s="3">
-        <v>16876600</v>
+        <v>17857000</v>
       </c>
       <c r="J42" s="3">
+        <v>16991400</v>
+      </c>
+      <c r="K42" s="3">
         <v>13268900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>15784600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>14548600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>10836500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>8835100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>8432300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>7132600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>7180900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>4632500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>3788300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>3767300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>3752600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>644900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>295600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>723900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1829700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1713700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1274500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>2383300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1890700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>3089800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>2623300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1793200</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3498500</v>
+        <v>3116300</v>
       </c>
       <c r="E43" s="3">
-        <v>3366100</v>
+        <v>3522300</v>
       </c>
       <c r="F43" s="3">
-        <v>2890000</v>
+        <v>3389000</v>
       </c>
       <c r="G43" s="3">
-        <v>3689200</v>
+        <v>2909700</v>
       </c>
       <c r="H43" s="3">
-        <v>3344600</v>
+        <v>3714300</v>
       </c>
       <c r="I43" s="3">
-        <v>2695300</v>
+        <v>3367300</v>
       </c>
       <c r="J43" s="3">
+        <v>2713700</v>
+      </c>
+      <c r="K43" s="3">
         <v>2280400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2397400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2461700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3709000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2365400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2013200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2079900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1986200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1702600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1844100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2499900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2102900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1622800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2463500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2348300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3701700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2819300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4850500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5597400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>6769800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5409200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4288500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>4025000</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>8925200</v>
+        <v>9461400</v>
       </c>
       <c r="E44" s="3">
-        <v>8776600</v>
+        <v>8986000</v>
       </c>
       <c r="F44" s="3">
-        <v>8740300</v>
+        <v>8836400</v>
       </c>
       <c r="G44" s="3">
-        <v>10763200</v>
+        <v>8799800</v>
       </c>
       <c r="H44" s="3">
-        <v>9908200</v>
+        <v>10836500</v>
       </c>
       <c r="I44" s="3">
-        <v>10498100</v>
+        <v>9975700</v>
       </c>
       <c r="J44" s="3">
+        <v>10569600</v>
+      </c>
+      <c r="K44" s="3">
         <v>9498500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>10416300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8535300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>9445600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8285800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8203400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>8155700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>8027700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>7980200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>8920400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>7431900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>6954700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5841700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>6394500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>5578100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>6227400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5188800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>6188800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5388800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4622900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3906300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4204300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3287100</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3490700</v>
+        <v>3780000</v>
       </c>
       <c r="E45" s="3">
-        <v>3607100</v>
+        <v>3514400</v>
       </c>
       <c r="F45" s="3">
-        <v>3324000</v>
+        <v>3631600</v>
       </c>
       <c r="G45" s="3">
-        <v>3652400</v>
+        <v>3346600</v>
       </c>
       <c r="H45" s="3">
-        <v>3674700</v>
+        <v>3677200</v>
       </c>
       <c r="I45" s="3">
-        <v>3783100</v>
+        <v>3699700</v>
       </c>
       <c r="J45" s="3">
+        <v>3808900</v>
+      </c>
+      <c r="K45" s="3">
         <v>3226200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2940200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2998600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3046100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2252800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2052400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2445100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2537400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1621900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1172100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1310600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1654700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1212300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1098700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1921800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2095000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1439700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>945200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1774000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2015800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1285200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3842100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>840300</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>49378500</v>
+        <v>42791700</v>
       </c>
       <c r="E46" s="3">
-        <v>48215300</v>
+        <v>49714700</v>
       </c>
       <c r="F46" s="3">
-        <v>42130300</v>
+        <v>48543600</v>
       </c>
       <c r="G46" s="3">
-        <v>48476300</v>
+        <v>42417100</v>
       </c>
       <c r="H46" s="3">
-        <v>46173500</v>
+        <v>48806300</v>
       </c>
       <c r="I46" s="3">
-        <v>44736700</v>
+        <v>46487900</v>
       </c>
       <c r="J46" s="3">
+        <v>45041200</v>
+      </c>
+      <c r="K46" s="3">
         <v>39936700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>41288800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>41053100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>41018200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>31679100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>32684300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>30587100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>30279000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>22804500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>21417800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>19956300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>19472800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>14524500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>15228200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>15330400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>18909200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>16212600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>17071400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>18350700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>19433200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>17126200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>15551100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>13557200</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>8655700</v>
+        <v>19127200</v>
       </c>
       <c r="E47" s="3">
-        <v>8926500</v>
+        <v>8714600</v>
       </c>
       <c r="F47" s="3">
-        <v>9333800</v>
+        <v>8987200</v>
       </c>
       <c r="G47" s="3">
-        <v>9562300</v>
+        <v>9397300</v>
       </c>
       <c r="H47" s="3">
-        <v>10212500</v>
+        <v>9627400</v>
       </c>
       <c r="I47" s="3">
-        <v>10136600</v>
+        <v>10282100</v>
       </c>
       <c r="J47" s="3">
+        <v>10205600</v>
+      </c>
+      <c r="K47" s="3">
         <v>9930000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>11340700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>12655200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>13323000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>13426300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>13584000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>11753100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>10996100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>9079600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>8775800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>8358600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>8423900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>8106100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>6863300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>7013800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>5555200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>4438500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>4241400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2881600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2652400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>3265500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>3299200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>3258900</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>13693800</v>
+        <v>14015700</v>
       </c>
       <c r="E48" s="3">
-        <v>12719200</v>
+        <v>13787000</v>
       </c>
       <c r="F48" s="3">
-        <v>12300700</v>
+        <v>12805800</v>
       </c>
       <c r="G48" s="3">
-        <v>12221200</v>
+        <v>12384500</v>
       </c>
       <c r="H48" s="3">
-        <v>11619400</v>
+        <v>12304400</v>
       </c>
       <c r="I48" s="3">
-        <v>10048100</v>
+        <v>11698500</v>
       </c>
       <c r="J48" s="3">
+        <v>10116500</v>
+      </c>
+      <c r="K48" s="3">
         <v>9642700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8094300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7452400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7186400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6362600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6401400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6278600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5475000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5079500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5405300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5221700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4807300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4842500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4013700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3446300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2997300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2456000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2340500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1904000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1599700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1382600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1311100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1280900</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>9562600</v>
+        <v>9241600</v>
       </c>
       <c r="E49" s="3">
-        <v>9571200</v>
+        <v>9627700</v>
       </c>
       <c r="F49" s="3">
-        <v>9093900</v>
+        <v>9636300</v>
       </c>
       <c r="G49" s="3">
-        <v>9128500</v>
+        <v>9155900</v>
       </c>
       <c r="H49" s="3">
-        <v>9123600</v>
+        <v>9190600</v>
       </c>
       <c r="I49" s="3">
-        <v>7449600</v>
+        <v>9185700</v>
       </c>
       <c r="J49" s="3">
+        <v>7500300</v>
+      </c>
+      <c r="K49" s="3">
         <v>7423000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4491400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4519900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4465800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4137700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3966100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4229400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3622600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3318700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3333000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3303300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3256200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3246200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3214100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3076700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2868200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2862900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3026700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3021300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2440200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2475700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2513800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2566700</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4480,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3959000</v>
+        <v>2261400</v>
       </c>
       <c r="E52" s="3">
-        <v>3957600</v>
+        <v>3986000</v>
       </c>
       <c r="F52" s="3">
-        <v>3228300</v>
+        <v>3984600</v>
       </c>
       <c r="G52" s="3">
-        <v>2803900</v>
+        <v>3250300</v>
       </c>
       <c r="H52" s="3">
-        <v>2896600</v>
+        <v>2822900</v>
       </c>
       <c r="I52" s="3">
-        <v>4085500</v>
+        <v>2916400</v>
       </c>
       <c r="J52" s="3">
+        <v>4113300</v>
+      </c>
+      <c r="K52" s="3">
         <v>3790000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3193600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2984600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2388700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2162100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2146600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2308600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1568800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1633700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1060400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1013300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1545900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2025800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1057800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1019700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1040600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>618800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>635500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>620000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>687900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>580500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1665500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>308700</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>85249600</v>
+        <v>87437700</v>
       </c>
       <c r="E54" s="3">
-        <v>83389800</v>
+        <v>85830000</v>
       </c>
       <c r="F54" s="3">
-        <v>76087100</v>
+        <v>83957500</v>
       </c>
       <c r="G54" s="3">
-        <v>82192100</v>
+        <v>76605000</v>
       </c>
       <c r="H54" s="3">
-        <v>80025800</v>
+        <v>82751700</v>
       </c>
       <c r="I54" s="3">
-        <v>76456400</v>
+        <v>80570600</v>
       </c>
       <c r="J54" s="3">
+        <v>76976900</v>
+      </c>
+      <c r="K54" s="3">
         <v>70722500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>68408700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>68665100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>68382000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>57767800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>58782500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>55156900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>51941500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>41916200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>39992300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>37853200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>37506100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>32745200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>30377000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>29887000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>31370400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>26588900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>27315600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>26777600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>26813400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>24830500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>23323100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>20972500</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,560 +4837,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>21225900</v>
+        <v>23325700</v>
       </c>
       <c r="E57" s="3">
-        <v>21014500</v>
+        <v>21370400</v>
       </c>
       <c r="F57" s="3">
-        <v>16803100</v>
+        <v>21157600</v>
       </c>
       <c r="G57" s="3">
-        <v>22244000</v>
+        <v>16917500</v>
       </c>
       <c r="H57" s="3">
-        <v>20833500</v>
+        <v>22395400</v>
       </c>
       <c r="I57" s="3">
-        <v>22126900</v>
+        <v>20975300</v>
       </c>
       <c r="J57" s="3">
+        <v>22277500</v>
+      </c>
+      <c r="K57" s="3">
         <v>17322400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>19427400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>18034400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>18431300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>13566400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>14950600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>15570300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>14940700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>12266000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>13973100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>13355500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>14326200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>10927000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>11647500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>10957000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>12582100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>8938300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>11032500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>10032000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>10014300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>6362200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>6695000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>6031800</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1897200</v>
+        <v>699800</v>
       </c>
       <c r="E58" s="3">
-        <v>2478700</v>
+        <v>1910100</v>
       </c>
       <c r="F58" s="3">
-        <v>1971800</v>
+        <v>2495500</v>
       </c>
       <c r="G58" s="3">
-        <v>1677100</v>
+        <v>1985200</v>
       </c>
       <c r="H58" s="3">
-        <v>2484900</v>
+        <v>1688500</v>
       </c>
       <c r="I58" s="3">
-        <v>1899200</v>
+        <v>2501800</v>
       </c>
       <c r="J58" s="3">
+        <v>1912100</v>
+      </c>
+      <c r="K58" s="3">
         <v>2368200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>601800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>999000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>80800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>598900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>453800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>934600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1815600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1357000</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
       <c r="T58" s="3">
         <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>21000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>285600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>660100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1340300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1701400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1939000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1912200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1825900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1807800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2944100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1615600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1993900</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>13114300</v>
+        <v>12905100</v>
       </c>
       <c r="E59" s="3">
-        <v>12365900</v>
+        <v>13203600</v>
       </c>
       <c r="F59" s="3">
-        <v>12180000</v>
+        <v>12450100</v>
       </c>
       <c r="G59" s="3">
-        <v>12885600</v>
+        <v>12263000</v>
       </c>
       <c r="H59" s="3">
-        <v>12075900</v>
+        <v>12973300</v>
       </c>
       <c r="I59" s="3">
-        <v>11251400</v>
+        <v>12158100</v>
       </c>
       <c r="J59" s="3">
+        <v>11328000</v>
+      </c>
+      <c r="K59" s="3">
         <v>10549700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10507800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9989200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9769000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8417900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8818700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8928800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8582000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>7926600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7586700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>7088800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>7054300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6348400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5245200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4735000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4852800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4456200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4604900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4511800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4433200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>6832000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>6921700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4873400</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>36237400</v>
+        <v>36930700</v>
       </c>
       <c r="E60" s="3">
-        <v>35859100</v>
+        <v>36484100</v>
       </c>
       <c r="F60" s="3">
-        <v>30954900</v>
+        <v>36103200</v>
       </c>
       <c r="G60" s="3">
-        <v>36806700</v>
+        <v>31165600</v>
       </c>
       <c r="H60" s="3">
-        <v>35394300</v>
+        <v>37057300</v>
       </c>
       <c r="I60" s="3">
-        <v>35277500</v>
+        <v>35635300</v>
       </c>
       <c r="J60" s="3">
+        <v>35517700</v>
+      </c>
+      <c r="K60" s="3">
         <v>30240300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>30537000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>29022600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>28281100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>22583300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>24223100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>25433700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>25338300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>21549600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>21559800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>20444300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>21401500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>17561000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>17552800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>17032300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>19136300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>15333500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>17549600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>16369700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>16255400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>16138300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>15232400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>12899100</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>4520900</v>
+        <v>5834100</v>
       </c>
       <c r="E61" s="3">
-        <v>4427400</v>
+        <v>4551700</v>
       </c>
       <c r="F61" s="3">
-        <v>4050700</v>
+        <v>4457500</v>
       </c>
       <c r="G61" s="3">
-        <v>4174600</v>
+        <v>4078300</v>
       </c>
       <c r="H61" s="3">
-        <v>3950900</v>
+        <v>4203000</v>
       </c>
       <c r="I61" s="3">
-        <v>3404900</v>
+        <v>3977800</v>
       </c>
       <c r="J61" s="3">
+        <v>3428100</v>
+      </c>
+      <c r="K61" s="3">
         <v>2155300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1293200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1775800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1782600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1757100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1744300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1943300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2002600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2702700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1547800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1568600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1512300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1480700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1434100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1384800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1408600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1036900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1621000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2315500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2602100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1957100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1330600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1488500</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3580400</v>
+        <v>3470200</v>
       </c>
       <c r="E62" s="3">
-        <v>3434300</v>
+        <v>3604800</v>
       </c>
       <c r="F62" s="3">
-        <v>3246800</v>
+        <v>3457700</v>
       </c>
       <c r="G62" s="3">
-        <v>3359900</v>
+        <v>3268900</v>
       </c>
       <c r="H62" s="3">
-        <v>3242100</v>
+        <v>3382800</v>
       </c>
       <c r="I62" s="3">
-        <v>2987800</v>
+        <v>3264200</v>
       </c>
       <c r="J62" s="3">
+        <v>3008100</v>
+      </c>
+      <c r="K62" s="3">
         <v>3001200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2576600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2450600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2498700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1952600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1965700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1980600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1611900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1376100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1390500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1409600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1145200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>914000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>232400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>255700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>295100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>326300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>370000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>400900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>438400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>471400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>765600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>430900</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>53478200</v>
+        <v>55204800</v>
       </c>
       <c r="E66" s="3">
-        <v>52765600</v>
+        <v>53842300</v>
       </c>
       <c r="F66" s="3">
-        <v>46882300</v>
+        <v>53124800</v>
       </c>
       <c r="G66" s="3">
-        <v>52730500</v>
+        <v>47201500</v>
       </c>
       <c r="H66" s="3">
-        <v>50730300</v>
+        <v>53089500</v>
       </c>
       <c r="I66" s="3">
-        <v>48658700</v>
+        <v>51075700</v>
       </c>
       <c r="J66" s="3">
+        <v>48990000</v>
+      </c>
+      <c r="K66" s="3">
         <v>42210400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>39625000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>38058200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>37251100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>31504700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>32676400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>32970600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>31849600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>28618600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>27388100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>26166900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>26836400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>22565900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>21696500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>20936000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>23011700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>18812300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>19592200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>19135000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>19340200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>19650900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>18394100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>15844000</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,8 +6200,11 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6044,11 +6217,11 @@
       <c r="F72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G72" s="3">
-        <v>4525800</v>
-      </c>
-      <c r="H72" s="3" t="s">
+      <c r="G72" s="3" t="s">
         <v>10</v>
+      </c>
+      <c r="H72" s="3">
+        <v>4556700</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>10</v>
@@ -6056,11 +6229,11 @@
       <c r="J72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L72" s="3">
         <v>4876200</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>10</v>
@@ -6068,23 +6241,23 @@
       <c r="N72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P72" s="3">
         <v>5422100</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R72" s="3">
+      <c r="R72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S72" s="3">
         <v>-1479900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1609600</v>
-      </c>
-      <c r="T72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>10</v>
@@ -6092,11 +6265,11 @@
       <c r="V72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W72" s="3">
+      <c r="W72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X72" s="3">
         <v>-3287700</v>
-      </c>
-      <c r="X72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Y72" s="3" t="s">
         <v>10</v>
@@ -6104,26 +6277,29 @@
       <c r="Z72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB72" s="3">
         <v>-3205500</v>
-      </c>
-      <c r="AB72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AC72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AD72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE72" s="3">
         <v>-3104800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-3159800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-2968300</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>31771400</v>
+        <v>32232900</v>
       </c>
       <c r="E76" s="3">
-        <v>30624200</v>
+        <v>31987700</v>
       </c>
       <c r="F76" s="3">
-        <v>29204700</v>
+        <v>30832700</v>
       </c>
       <c r="G76" s="3">
-        <v>29461600</v>
+        <v>29403600</v>
       </c>
       <c r="H76" s="3">
-        <v>29295500</v>
+        <v>29662100</v>
       </c>
       <c r="I76" s="3">
-        <v>27797700</v>
+        <v>29494900</v>
       </c>
       <c r="J76" s="3">
+        <v>27987000</v>
+      </c>
+      <c r="K76" s="3">
         <v>28512100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>28783800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>30606900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>31130900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>26263200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>26106000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>22186300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>20091900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13297600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12604200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11686300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>10669800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>10179200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>8680500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>8951000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>8358800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7776600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7723400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7642600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7473100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>5179500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4929000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5128500</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1095800</v>
+        <v>471100</v>
       </c>
       <c r="E81" s="3">
-        <v>908700</v>
+        <v>1103300</v>
       </c>
       <c r="F81" s="3">
-        <v>864500</v>
+        <v>914900</v>
       </c>
       <c r="G81" s="3">
-        <v>418700</v>
+        <v>870400</v>
       </c>
       <c r="H81" s="3">
-        <v>823400</v>
+        <v>421500</v>
       </c>
       <c r="I81" s="3">
-        <v>604200</v>
+        <v>829000</v>
       </c>
       <c r="J81" s="3">
+        <v>608400</v>
+      </c>
+      <c r="K81" s="3">
         <v>-413000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-711600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-398900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>114100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>503500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3386100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1114100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2423600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>169200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>559600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>94300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>94500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1118200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-697800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>420000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-317400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>218800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-134900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>150500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-73700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>34800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-250600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-134000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7002,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6897,8 +7095,11 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>2071800</v>
+        <v>2726600</v>
       </c>
       <c r="E89" s="3">
-        <v>6422200</v>
+        <v>2085900</v>
       </c>
       <c r="F89" s="3">
-        <v>-2983500</v>
+        <v>6466000</v>
       </c>
       <c r="G89" s="3">
-        <v>2552500</v>
+        <v>-3003800</v>
       </c>
       <c r="H89" s="3">
-        <v>1263600</v>
+        <v>2569900</v>
       </c>
       <c r="I89" s="3">
-        <v>4648700</v>
+        <v>1272200</v>
       </c>
       <c r="J89" s="3">
+        <v>4680400</v>
+      </c>
+      <c r="K89" s="3">
         <v>-481200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>891700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2053700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4149200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1045200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>725700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1806000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3922400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-243300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>194300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3085000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>507700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>875500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>309700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2355000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-541300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>200500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>52300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2767300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>650300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-433900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1047900</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7702,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7575,8 +7795,11 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>2066200</v>
+        <v>-8768300</v>
       </c>
       <c r="E94" s="3">
-        <v>-3883800</v>
+        <v>2080300</v>
       </c>
       <c r="F94" s="3">
-        <v>2304800</v>
+        <v>-3910200</v>
       </c>
       <c r="G94" s="3">
-        <v>-2472700</v>
+        <v>2320500</v>
       </c>
       <c r="H94" s="3">
-        <v>-1346800</v>
+        <v>-2489600</v>
       </c>
       <c r="I94" s="3">
-        <v>-4270300</v>
+        <v>-1356000</v>
       </c>
       <c r="J94" s="3">
+        <v>-4299300</v>
+      </c>
+      <c r="K94" s="3">
         <v>629900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2588300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4230000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2595800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1062300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1907800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1844800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3446700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1293100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>377600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-873100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3212700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-168500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-317800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-364300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2919400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-135000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>624600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-620100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-4568600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-980900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2206600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3057800</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8210,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8495,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-619400</v>
+        <v>-103600</v>
       </c>
       <c r="E100" s="3">
-        <v>-253000</v>
+        <v>-623600</v>
       </c>
       <c r="F100" s="3">
-        <v>173300</v>
+        <v>-254700</v>
       </c>
       <c r="G100" s="3">
-        <v>-584800</v>
+        <v>174500</v>
       </c>
       <c r="H100" s="3">
-        <v>556300</v>
+        <v>-588700</v>
       </c>
       <c r="I100" s="3">
-        <v>-1561500</v>
+        <v>560100</v>
       </c>
       <c r="J100" s="3">
+        <v>-1572200</v>
+      </c>
+      <c r="K100" s="3">
         <v>1752900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-472100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>864000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2505200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-82400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3259000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>606800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>4193100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2380000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>475500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>383300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-68600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-390500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-569400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-419200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>692900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1909300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-564100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-229500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>2462600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1161900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1772300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>415900</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-105400</v>
+        <v>-29600</v>
       </c>
       <c r="E101" s="3">
-        <v>252300</v>
+        <v>-106100</v>
       </c>
       <c r="F101" s="3">
-        <v>-100200</v>
+        <v>254000</v>
       </c>
       <c r="G101" s="3">
-        <v>-134800</v>
+        <v>-100900</v>
       </c>
       <c r="H101" s="3">
-        <v>248300</v>
+        <v>-135700</v>
       </c>
       <c r="I101" s="3">
-        <v>431800</v>
+        <v>250000</v>
       </c>
       <c r="J101" s="3">
+        <v>434700</v>
+      </c>
+      <c r="K101" s="3">
         <v>-63400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-197900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>44100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-138900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>82900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-413700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-392000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-8800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>96100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-60200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>123900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>63500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-64700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-19000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>150400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>171000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-65200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-31600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-44300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-13900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-5300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>42400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>3413200</v>
+        <v>-6174900</v>
       </c>
       <c r="E102" s="3">
-        <v>2537800</v>
+        <v>3436400</v>
       </c>
       <c r="F102" s="3">
-        <v>-605600</v>
+        <v>2555000</v>
       </c>
       <c r="G102" s="3">
-        <v>-639700</v>
+        <v>-609700</v>
       </c>
       <c r="H102" s="3">
-        <v>721300</v>
+        <v>-644100</v>
       </c>
       <c r="I102" s="3">
-        <v>-751300</v>
+        <v>726200</v>
       </c>
       <c r="J102" s="3">
+        <v>-756400</v>
+      </c>
+      <c r="K102" s="3">
         <v>1838300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2366600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1268100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3919700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2107000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1663300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>176100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>4659800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>939800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>793500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-171600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-132900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-115900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-30700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-323400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>299400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1167700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>605200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1085000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>515000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>825900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-736300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1679300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JD_QTR_FIN.xlsx
@@ -656,428 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>42550800</v>
+        <v>35928400</v>
       </c>
       <c r="E8" s="3">
-        <v>34435000</v>
+        <v>42287600</v>
       </c>
       <c r="F8" s="3">
-        <v>40028200</v>
+        <v>34222000</v>
       </c>
       <c r="G8" s="3">
-        <v>33775700</v>
+        <v>39780500</v>
       </c>
       <c r="H8" s="3">
-        <v>41072900</v>
+        <v>33566800</v>
       </c>
       <c r="I8" s="3">
-        <v>33856200</v>
+        <v>40818800</v>
       </c>
       <c r="J8" s="3">
+        <v>33646800</v>
+      </c>
+      <c r="K8" s="3">
         <v>37201800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>33091600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>38014500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>31089400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>36450800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>28282100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>31226500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>25672200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>29627300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>23065300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>26281900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>20763100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>22959900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>18498800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>19581700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>14663400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>17546300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>14366400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>16349600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>12428800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>13832100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>10939000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>11548800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>8751100</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>36503200</v>
+        <v>30433700</v>
       </c>
       <c r="E9" s="3">
-        <v>29047800</v>
+        <v>36277400</v>
       </c>
       <c r="F9" s="3">
-        <v>34268200</v>
+        <v>28868100</v>
       </c>
       <c r="G9" s="3">
-        <v>28768500</v>
+        <v>34056200</v>
       </c>
       <c r="H9" s="3">
-        <v>35298400</v>
+        <v>28590600</v>
       </c>
       <c r="I9" s="3">
-        <v>28824300</v>
+        <v>35080100</v>
       </c>
       <c r="J9" s="3">
+        <v>28646000</v>
+      </c>
+      <c r="K9" s="3">
         <v>32211800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>28473300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>32899800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>26669600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>31893800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>24228300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>26891500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>21723700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>25407600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>19510100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>22586700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>17665900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>19579600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>15720700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>16797400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>12408700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>15176900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>12334900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>14218500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>10502000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>11955000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>18670800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>19852900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>14923400</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>6047600</v>
+        <v>5494600</v>
       </c>
       <c r="E10" s="3">
-        <v>5387200</v>
+        <v>6010200</v>
       </c>
       <c r="F10" s="3">
-        <v>5760000</v>
+        <v>5353800</v>
       </c>
       <c r="G10" s="3">
-        <v>5007200</v>
+        <v>5724400</v>
       </c>
       <c r="H10" s="3">
-        <v>5774500</v>
+        <v>4976200</v>
       </c>
       <c r="I10" s="3">
-        <v>5032000</v>
+        <v>5738800</v>
       </c>
       <c r="J10" s="3">
+        <v>5000800</v>
+      </c>
+      <c r="K10" s="3">
         <v>4990000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4618200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5114600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4419800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4557000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4053800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4335000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3948500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4219700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3555200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3695200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3097200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3380300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2778100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2784300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2254700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2369400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2031400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2131100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1926800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1877100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>-7731900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>-8304100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>-6172300</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,103 +1124,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>594300</v>
+        <v>548200</v>
       </c>
       <c r="E12" s="3">
-        <v>518300</v>
+        <v>590600</v>
       </c>
       <c r="F12" s="3">
-        <v>554600</v>
+        <v>515100</v>
       </c>
       <c r="G12" s="3">
-        <v>569400</v>
+        <v>551100</v>
       </c>
       <c r="H12" s="3">
-        <v>594400</v>
+        <v>565900</v>
       </c>
       <c r="I12" s="3">
-        <v>560700</v>
+        <v>590800</v>
       </c>
       <c r="J12" s="3">
+        <v>557200</v>
+      </c>
+      <c r="K12" s="3">
         <v>551500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>600100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>562000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>565400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>526700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>627000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>623400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>601500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>527400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>616900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>549200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>548200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>565400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>564000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>505400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>478900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>395500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>342700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>302600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>257500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>226400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>184500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>168700</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>175700</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1301,198 +1318,207 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>597100</v>
+        <v>-3000</v>
       </c>
       <c r="E14" s="3">
+        <v>598500</v>
+      </c>
+      <c r="F14" s="3">
         <v>-700</v>
       </c>
-      <c r="F14" s="3">
-        <v>-144300</v>
-      </c>
       <c r="G14" s="3">
-        <v>-68500</v>
+        <v>-143400</v>
       </c>
       <c r="H14" s="3">
+        <v>-68100</v>
+      </c>
+      <c r="I14" s="3">
         <v>-11500</v>
       </c>
-      <c r="I14" s="3">
-        <v>-174600</v>
-      </c>
       <c r="J14" s="3">
+        <v>-173500</v>
+      </c>
+      <c r="K14" s="3">
         <v>-4300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>490000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-2500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-82300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-12500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-11500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-154400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-50700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-28800</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>-598200</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>10</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>3100</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>10</v>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="3" t="s">
+      <c r="AF14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>58700</v>
+        <v>58000</v>
       </c>
       <c r="E15" s="3">
-        <v>58500</v>
+        <v>58300</v>
       </c>
       <c r="F15" s="3">
-        <v>60900</v>
+        <v>58200</v>
       </c>
       <c r="G15" s="3">
-        <v>62000</v>
+        <v>60500</v>
       </c>
       <c r="H15" s="3">
-        <v>61000</v>
+        <v>61600</v>
       </c>
       <c r="I15" s="3">
-        <v>61600</v>
+        <v>60700</v>
       </c>
       <c r="J15" s="3">
+        <v>61200</v>
+      </c>
+      <c r="K15" s="3">
         <v>58100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>54100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>51900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>53400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>53300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>50600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>51900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>50300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>43800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>44500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>72600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>22500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>22600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>67800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>65800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>63900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>64600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>64000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>66700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>66300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>65700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>63900</v>
-      </c>
-      <c r="AF15" s="3">
-        <v>65100</v>
       </c>
       <c r="AG15" s="3">
         <v>65100</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>65100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>42259400</v>
+        <v>34861500</v>
       </c>
       <c r="E17" s="3">
-        <v>33141000</v>
+        <v>42003100</v>
       </c>
       <c r="F17" s="3">
-        <v>38874400</v>
+        <v>32936000</v>
       </c>
       <c r="G17" s="3">
-        <v>32879300</v>
+        <v>38634000</v>
       </c>
       <c r="H17" s="3">
-        <v>40411000</v>
+        <v>32675900</v>
       </c>
       <c r="I17" s="3">
-        <v>32639100</v>
+        <v>40161000</v>
       </c>
       <c r="J17" s="3">
+        <v>32437200</v>
+      </c>
+      <c r="K17" s="3">
         <v>36675000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>33249000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>38068500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>30723700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>36407600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>28051100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>31143700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>25026300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>28884000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>22699300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>26200400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>19997300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>22613600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>18311500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>19718100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>14754400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>17694700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>14365700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>16586500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>12354200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>13891900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>10842800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>11598000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>8785200</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>291400</v>
+        <v>1066900</v>
       </c>
       <c r="E18" s="3">
-        <v>1294000</v>
+        <v>284500</v>
       </c>
       <c r="F18" s="3">
-        <v>1153700</v>
+        <v>1286000</v>
       </c>
       <c r="G18" s="3">
-        <v>896400</v>
+        <v>1146600</v>
       </c>
       <c r="H18" s="3">
-        <v>661900</v>
+        <v>890900</v>
       </c>
       <c r="I18" s="3">
-        <v>1217100</v>
+        <v>657800</v>
       </c>
       <c r="J18" s="3">
+        <v>1209600</v>
+      </c>
+      <c r="K18" s="3">
         <v>526700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-157400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-54000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>365700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>43200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>231000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>82800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>645900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>743300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>366100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>81500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>765800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>346300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>187200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-136400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-91100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-148400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-236900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>74600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-59800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>96200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-49200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-34100</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,483 +1781,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>297100</v>
+        <v>268600</v>
       </c>
       <c r="E20" s="3">
-        <v>306400</v>
+        <v>300400</v>
       </c>
       <c r="F20" s="3">
-        <v>290400</v>
+        <v>304500</v>
       </c>
       <c r="G20" s="3">
-        <v>271100</v>
+        <v>288600</v>
       </c>
       <c r="H20" s="3">
-        <v>-34300</v>
+        <v>269400</v>
       </c>
       <c r="I20" s="3">
-        <v>-64800</v>
+        <v>-34100</v>
       </c>
       <c r="J20" s="3">
+        <v>-64400</v>
+      </c>
+      <c r="K20" s="3">
         <v>271200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-197500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-591600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-698300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>140600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>378600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3292200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>617500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1840500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-115100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>573300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-562800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-172200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>990200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-542100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>534700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-120500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>265800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>95700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>120500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>42100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-15000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-113100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-26100</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>556100</v>
+        <v>1641800</v>
       </c>
       <c r="E21" s="3">
-        <v>1606900</v>
+        <v>593900</v>
       </c>
       <c r="F21" s="3">
-        <v>1457200</v>
+        <v>1597000</v>
       </c>
       <c r="G21" s="3">
-        <v>1440000</v>
+        <v>1448200</v>
       </c>
       <c r="H21" s="3">
-        <v>643800</v>
+        <v>1431100</v>
       </c>
       <c r="I21" s="3">
-        <v>1173700</v>
+        <v>639800</v>
       </c>
       <c r="J21" s="3">
+        <v>1166500</v>
+      </c>
+      <c r="K21" s="3">
         <v>803700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-124000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-641300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-321900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>153900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>841900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3397100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1272200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2592000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>472700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>658500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>207000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>126300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1433100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-660600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>476100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-259600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>437800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-31900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>117300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-15000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>219700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-158100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-50000</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>128900</v>
+        <v>83000</v>
       </c>
       <c r="E22" s="3">
-        <v>98700</v>
+        <v>128100</v>
       </c>
       <c r="F22" s="3">
-        <v>90900</v>
+        <v>98100</v>
       </c>
       <c r="G22" s="3">
-        <v>82000</v>
+        <v>90400</v>
       </c>
       <c r="H22" s="3">
-        <v>97000</v>
+        <v>81500</v>
       </c>
       <c r="I22" s="3">
-        <v>80500</v>
+        <v>96400</v>
       </c>
       <c r="J22" s="3">
+        <v>80000</v>
+      </c>
+      <c r="K22" s="3">
         <v>67300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>47600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>61500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>39300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>33400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>35900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>41200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>43900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>47800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>32700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>33800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>25100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>23700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>28600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>21000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>33700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>34400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>32800</v>
       </c>
-      <c r="AB22" s="3" t="s">
+      <c r="AC22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>42000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>30900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>27600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>9200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>10400</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>459600</v>
+        <v>1252400</v>
       </c>
       <c r="E23" s="3">
-        <v>1501700</v>
+        <v>456800</v>
       </c>
       <c r="F23" s="3">
-        <v>1353200</v>
+        <v>1492400</v>
       </c>
       <c r="G23" s="3">
-        <v>1085500</v>
+        <v>1344800</v>
       </c>
       <c r="H23" s="3">
-        <v>530500</v>
+        <v>1078800</v>
       </c>
       <c r="I23" s="3">
-        <v>1071800</v>
+        <v>527200</v>
       </c>
       <c r="J23" s="3">
+        <v>1065200</v>
+      </c>
+      <c r="K23" s="3">
         <v>730700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-402500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-707200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-371900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>150400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>573800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3333800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1219500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2536000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>218300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>621000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>177900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>150400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1148800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-699500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>409900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-303300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>233600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-141200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>153100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-48600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>53600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-171500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-70600</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>193800</v>
+        <v>234900</v>
       </c>
       <c r="E24" s="3">
-        <v>358500</v>
+        <v>192600</v>
       </c>
       <c r="F24" s="3">
-        <v>390800</v>
+        <v>356300</v>
       </c>
       <c r="G24" s="3">
-        <v>223700</v>
+        <v>388400</v>
       </c>
       <c r="H24" s="3">
-        <v>82700</v>
+        <v>222300</v>
       </c>
       <c r="I24" s="3">
-        <v>243400</v>
+        <v>82200</v>
       </c>
       <c r="J24" s="3">
+        <v>241900</v>
+      </c>
+      <c r="K24" s="3">
         <v>170600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>83300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>25600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>92700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>81800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>66700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-46200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>101700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>117400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>51500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>73800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>93100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>67000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>42700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>8900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>7200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>23400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>21700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>7900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>13000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>14600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>265800</v>
+        <v>1017500</v>
       </c>
       <c r="E26" s="3">
-        <v>1143200</v>
+        <v>264200</v>
       </c>
       <c r="F26" s="3">
-        <v>962400</v>
+        <v>1136100</v>
       </c>
       <c r="G26" s="3">
-        <v>861800</v>
+        <v>956500</v>
       </c>
       <c r="H26" s="3">
-        <v>447800</v>
+        <v>856500</v>
       </c>
       <c r="I26" s="3">
-        <v>828400</v>
+        <v>445000</v>
       </c>
       <c r="J26" s="3">
+        <v>823300</v>
+      </c>
+      <c r="K26" s="3">
         <v>560100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-485800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-732800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-464600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>68600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>507000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3380000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1117800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2418600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>166800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>547200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>84800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>83400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1106100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-708400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>402600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-326700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>212000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-143100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>145200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-46200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>40500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-186100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-70900</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>471100</v>
+        <v>985100</v>
       </c>
       <c r="E27" s="3">
-        <v>1103300</v>
+        <v>468200</v>
       </c>
       <c r="F27" s="3">
-        <v>914900</v>
+        <v>1096400</v>
       </c>
       <c r="G27" s="3">
-        <v>870400</v>
+        <v>909200</v>
       </c>
       <c r="H27" s="3">
-        <v>421500</v>
+        <v>865000</v>
       </c>
       <c r="I27" s="3">
-        <v>829000</v>
+        <v>418900</v>
       </c>
       <c r="J27" s="3">
+        <v>823800</v>
+      </c>
+      <c r="K27" s="3">
         <v>608400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-413000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-711600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-398900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>114100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>503500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3386100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1114100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2423600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>169200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>559600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>94300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>94500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1118200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-697800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>420000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-317400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>218800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-134900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>150500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-42600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>43500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-183400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-68000</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2687,19 +2748,22 @@
         <v>0</v>
       </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-31100</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-8700</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-67100</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-66100</v>
       </c>
     </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,198 +2955,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-297100</v>
+        <v>-268600</v>
       </c>
       <c r="E32" s="3">
-        <v>-306400</v>
+        <v>-300400</v>
       </c>
       <c r="F32" s="3">
-        <v>-290400</v>
+        <v>-304500</v>
       </c>
       <c r="G32" s="3">
-        <v>-271100</v>
+        <v>-288600</v>
       </c>
       <c r="H32" s="3">
-        <v>34300</v>
+        <v>-269400</v>
       </c>
       <c r="I32" s="3">
-        <v>64800</v>
+        <v>34100</v>
       </c>
       <c r="J32" s="3">
+        <v>64400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-271200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>197500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>591600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>698300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-140600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-378600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3292200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-617500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1840500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>115100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-573300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>562800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>172200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-990200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>542100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-534700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>120500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-265800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-95700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-120500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-42100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>15000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>113100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>471100</v>
+        <v>985100</v>
       </c>
       <c r="E33" s="3">
-        <v>1103300</v>
+        <v>468200</v>
       </c>
       <c r="F33" s="3">
-        <v>914900</v>
+        <v>1096400</v>
       </c>
       <c r="G33" s="3">
-        <v>870400</v>
+        <v>909200</v>
       </c>
       <c r="H33" s="3">
-        <v>421500</v>
+        <v>865000</v>
       </c>
       <c r="I33" s="3">
-        <v>829000</v>
+        <v>418900</v>
       </c>
       <c r="J33" s="3">
+        <v>823800</v>
+      </c>
+      <c r="K33" s="3">
         <v>608400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-413000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-711600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-398900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>114100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>503500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3386100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1114100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2423600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>169200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>559600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>94300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>94500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1118200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-697800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>420000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-317400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>218800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-134900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>150500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-73700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>34800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-250600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-134000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>471100</v>
+        <v>985100</v>
       </c>
       <c r="E35" s="3">
-        <v>1103300</v>
+        <v>468200</v>
       </c>
       <c r="F35" s="3">
-        <v>914900</v>
+        <v>1096400</v>
       </c>
       <c r="G35" s="3">
-        <v>870400</v>
+        <v>909200</v>
       </c>
       <c r="H35" s="3">
-        <v>421500</v>
+        <v>865000</v>
       </c>
       <c r="I35" s="3">
-        <v>829000</v>
+        <v>418900</v>
       </c>
       <c r="J35" s="3">
+        <v>823800</v>
+      </c>
+      <c r="K35" s="3">
         <v>608400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-413000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-711600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-398900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>114100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>503500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3386100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1114100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2423600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>169200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>559600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>94300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>94500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1118200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-697800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>420000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-317400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>218800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-134900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>150500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-73700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>34800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-250600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-134000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,863 +3524,891 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>9994400</v>
+        <v>11277400</v>
       </c>
       <c r="E41" s="3">
-        <v>16122300</v>
+        <v>9932600</v>
       </c>
       <c r="F41" s="3">
-        <v>12653600</v>
+        <v>16022600</v>
       </c>
       <c r="G41" s="3">
-        <v>10339300</v>
+        <v>12575300</v>
       </c>
       <c r="H41" s="3">
-        <v>10963300</v>
+        <v>10275400</v>
       </c>
       <c r="I41" s="3">
-        <v>11588200</v>
+        <v>10895400</v>
       </c>
       <c r="J41" s="3">
+        <v>11516500</v>
+      </c>
+      <c r="K41" s="3">
         <v>10957700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11662700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9750300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>12508900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>13981000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9940000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>11983000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10773900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10546800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6867200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5692900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4946600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5007900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5202700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4975900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4758300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5055400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5051100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3812400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3207200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4134000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3435700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2263900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3611700</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>16439700</v>
+        <v>12485700</v>
       </c>
       <c r="E42" s="3">
-        <v>17569600</v>
+        <v>16338000</v>
       </c>
       <c r="F42" s="3">
-        <v>20032900</v>
+        <v>17460900</v>
       </c>
       <c r="G42" s="3">
-        <v>17021600</v>
+        <v>19909000</v>
       </c>
       <c r="H42" s="3">
-        <v>19615000</v>
+        <v>16916300</v>
       </c>
       <c r="I42" s="3">
-        <v>17857000</v>
+        <v>19493700</v>
       </c>
       <c r="J42" s="3">
+        <v>17746500</v>
+      </c>
+      <c r="K42" s="3">
         <v>16991400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>13268900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>15784600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>14548600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>10836500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>8835100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>8432300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>7132600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>7180900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>4632500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>3788300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>3767300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>3752600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>644900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>295600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>723900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1829700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1713700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1274500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>2383300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1890700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>3089800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>2623300</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1793200</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3116300</v>
+        <v>2829900</v>
       </c>
       <c r="E43" s="3">
-        <v>3522300</v>
+        <v>3097000</v>
       </c>
       <c r="F43" s="3">
-        <v>3389000</v>
+        <v>3500600</v>
       </c>
       <c r="G43" s="3">
-        <v>2909700</v>
+        <v>3368100</v>
       </c>
       <c r="H43" s="3">
-        <v>3714300</v>
+        <v>2891700</v>
       </c>
       <c r="I43" s="3">
-        <v>3367300</v>
+        <v>3691400</v>
       </c>
       <c r="J43" s="3">
+        <v>3346500</v>
+      </c>
+      <c r="K43" s="3">
         <v>2713700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2280400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2397400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2461700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3709000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2365400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2013200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2079900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1986200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1702600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1844100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2499900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2102900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1622800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2463500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2348300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3701700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2819300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4850500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5597400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>6769800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>5409200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>4288500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>4025000</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>9461400</v>
+        <v>9394100</v>
       </c>
       <c r="E44" s="3">
-        <v>8986000</v>
+        <v>9402900</v>
       </c>
       <c r="F44" s="3">
-        <v>8836400</v>
+        <v>8930400</v>
       </c>
       <c r="G44" s="3">
-        <v>8799800</v>
+        <v>8781700</v>
       </c>
       <c r="H44" s="3">
-        <v>10836500</v>
+        <v>8745400</v>
       </c>
       <c r="I44" s="3">
-        <v>9975700</v>
+        <v>10769400</v>
       </c>
       <c r="J44" s="3">
+        <v>9913900</v>
+      </c>
+      <c r="K44" s="3">
         <v>10569600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>9498500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>10416300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8535300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>9445600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8285800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>8203400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>8155700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>8027700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>7980200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>8920400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>7431900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>6954700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5841700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>6394500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5578100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>6227400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5188800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>6188800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5388800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4622900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3906300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4204300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3287100</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3780000</v>
+        <v>3260300</v>
       </c>
       <c r="E45" s="3">
-        <v>3514400</v>
+        <v>3756600</v>
       </c>
       <c r="F45" s="3">
-        <v>3631600</v>
+        <v>3492700</v>
       </c>
       <c r="G45" s="3">
-        <v>3346600</v>
+        <v>3609200</v>
       </c>
       <c r="H45" s="3">
-        <v>3677200</v>
+        <v>3325900</v>
       </c>
       <c r="I45" s="3">
-        <v>3699700</v>
+        <v>3654500</v>
       </c>
       <c r="J45" s="3">
+        <v>3676900</v>
+      </c>
+      <c r="K45" s="3">
         <v>3808900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3226200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2940200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2998600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3046100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2252800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2052400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2445100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2537400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1621900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1172100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1310600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1654700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1212300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1098700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1921800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2095000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1439700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>945200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1774000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2015800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1285200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3842100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>840300</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>42791700</v>
+        <v>39247400</v>
       </c>
       <c r="E46" s="3">
-        <v>49714700</v>
+        <v>42527000</v>
       </c>
       <c r="F46" s="3">
-        <v>48543600</v>
+        <v>49407100</v>
       </c>
       <c r="G46" s="3">
-        <v>42417100</v>
+        <v>48243300</v>
       </c>
       <c r="H46" s="3">
-        <v>48806300</v>
+        <v>42154700</v>
       </c>
       <c r="I46" s="3">
-        <v>46487900</v>
+        <v>48504400</v>
       </c>
       <c r="J46" s="3">
+        <v>46200300</v>
+      </c>
+      <c r="K46" s="3">
         <v>45041200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>39936700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>41288800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>41053100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>41018200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>31679100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>32684300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>30587100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>30279000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>22804500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>21417800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>19956300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>19472800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>14524500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>15228200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>15330400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>18909200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>16212600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>17071400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>18350700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>19433200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>17126200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>15551100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>13557200</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>19127200</v>
+        <v>18709800</v>
       </c>
       <c r="E47" s="3">
-        <v>8714600</v>
+        <v>19008900</v>
       </c>
       <c r="F47" s="3">
-        <v>8987200</v>
+        <v>8660700</v>
       </c>
       <c r="G47" s="3">
-        <v>9397300</v>
+        <v>8931600</v>
       </c>
       <c r="H47" s="3">
-        <v>9627400</v>
+        <v>9339200</v>
       </c>
       <c r="I47" s="3">
-        <v>10282100</v>
+        <v>9567900</v>
       </c>
       <c r="J47" s="3">
+        <v>10218500</v>
+      </c>
+      <c r="K47" s="3">
         <v>10205600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9930000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>11340700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>12655200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>13323000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>13426300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>13584000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>11753100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>10996100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>9079600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>8775800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>8358600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>8423900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>8106100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>6863300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>7013800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>5555200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>4438500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>4241400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2881600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2652400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>3265500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>3299200</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>3258900</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>14015700</v>
+        <v>14128100</v>
       </c>
       <c r="E48" s="3">
-        <v>13787000</v>
+        <v>13929000</v>
       </c>
       <c r="F48" s="3">
-        <v>12805800</v>
+        <v>13701700</v>
       </c>
       <c r="G48" s="3">
-        <v>12384500</v>
+        <v>12726600</v>
       </c>
       <c r="H48" s="3">
-        <v>12304400</v>
+        <v>12307800</v>
       </c>
       <c r="I48" s="3">
-        <v>11698500</v>
+        <v>12228300</v>
       </c>
       <c r="J48" s="3">
+        <v>11626200</v>
+      </c>
+      <c r="K48" s="3">
         <v>10116500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9642700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8094300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7452400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7186400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6362600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6401400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6278600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5475000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5079500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5405300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5221700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4807300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4842500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4013700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3446300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2997300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2456000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2340500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1904000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1599700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1382600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1311100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1280900</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>9241600</v>
+        <v>9015200</v>
       </c>
       <c r="E49" s="3">
-        <v>9627700</v>
+        <v>9184600</v>
       </c>
       <c r="F49" s="3">
-        <v>9636300</v>
+        <v>9568100</v>
       </c>
       <c r="G49" s="3">
-        <v>9155900</v>
+        <v>9576700</v>
       </c>
       <c r="H49" s="3">
-        <v>9190600</v>
+        <v>9099200</v>
       </c>
       <c r="I49" s="3">
-        <v>9185700</v>
+        <v>9133800</v>
       </c>
       <c r="J49" s="3">
+        <v>9128900</v>
+      </c>
+      <c r="K49" s="3">
         <v>7500300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7423000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4491400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4519900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4465800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4137700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3966100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4229400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3622600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3318700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3333000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3303300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3256200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3246200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3214100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3076700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2868200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2862900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3026700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3021300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2440200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2475700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2513800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2566700</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,103 +4600,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2261400</v>
+        <v>2047300</v>
       </c>
       <c r="E52" s="3">
-        <v>3986000</v>
+        <v>2247300</v>
       </c>
       <c r="F52" s="3">
-        <v>3984600</v>
+        <v>3961300</v>
       </c>
       <c r="G52" s="3">
-        <v>3250300</v>
+        <v>3959900</v>
       </c>
       <c r="H52" s="3">
-        <v>2822900</v>
+        <v>3230200</v>
       </c>
       <c r="I52" s="3">
-        <v>2916400</v>
+        <v>2805500</v>
       </c>
       <c r="J52" s="3">
+        <v>2898300</v>
+      </c>
+      <c r="K52" s="3">
         <v>4113300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3790000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3193600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2984600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2388700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2162100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2146600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2308600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1568800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1633700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1060400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1013300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1545900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2025800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1057800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1019700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1040600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>618800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>635500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>620000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>687900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>580500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1665500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>308700</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>87437700</v>
+        <v>83147700</v>
       </c>
       <c r="E54" s="3">
-        <v>85830000</v>
+        <v>86896800</v>
       </c>
       <c r="F54" s="3">
-        <v>83957500</v>
+        <v>85299000</v>
       </c>
       <c r="G54" s="3">
-        <v>76605000</v>
+        <v>83438100</v>
       </c>
       <c r="H54" s="3">
-        <v>82751700</v>
+        <v>76131100</v>
       </c>
       <c r="I54" s="3">
-        <v>80570600</v>
+        <v>82239700</v>
       </c>
       <c r="J54" s="3">
+        <v>80072100</v>
+      </c>
+      <c r="K54" s="3">
         <v>76976900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>70722500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>68408700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>68665100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>68382000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>57767800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>58782500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>55156900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>51941500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>41916200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>39992300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>37853200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>37506100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>32745200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>30377000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>29887000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>31370400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>26588900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>27315600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>26777600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>26813400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>24830500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>23323100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>20972500</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,578 +4968,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>23325700</v>
+        <v>20385100</v>
       </c>
       <c r="E57" s="3">
-        <v>21370400</v>
+        <v>23181500</v>
       </c>
       <c r="F57" s="3">
-        <v>21157600</v>
+        <v>21238200</v>
       </c>
       <c r="G57" s="3">
-        <v>16917500</v>
+        <v>21026700</v>
       </c>
       <c r="H57" s="3">
-        <v>22395400</v>
+        <v>16812800</v>
       </c>
       <c r="I57" s="3">
-        <v>20975300</v>
+        <v>22256900</v>
       </c>
       <c r="J57" s="3">
+        <v>20845600</v>
+      </c>
+      <c r="K57" s="3">
         <v>22277500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>17322400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>19427400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>18034400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>18431300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>13566400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>14950600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>15570300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>14940700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>12266000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>13973100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>13355500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>14326200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>10927000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>11647500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>10957000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>12582100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>8938300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>11032500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>10032000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>10014300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>6362200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>6695000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>6031800</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>699800</v>
+        <v>727700</v>
       </c>
       <c r="E58" s="3">
-        <v>1910100</v>
+        <v>695500</v>
       </c>
       <c r="F58" s="3">
-        <v>2495500</v>
+        <v>1898300</v>
       </c>
       <c r="G58" s="3">
-        <v>1985200</v>
+        <v>2480100</v>
       </c>
       <c r="H58" s="3">
-        <v>1688500</v>
+        <v>1972900</v>
       </c>
       <c r="I58" s="3">
-        <v>2501800</v>
+        <v>1678100</v>
       </c>
       <c r="J58" s="3">
+        <v>2486300</v>
+      </c>
+      <c r="K58" s="3">
         <v>1912100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2368200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>601800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>999000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>80800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>598900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>453800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>934600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1815600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1357000</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
       <c r="U58" s="3">
         <v>0</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>21000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>285600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>660100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1340300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1701400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1939000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1912200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1825900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1807800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2944100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1615600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1993900</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>12905100</v>
+        <v>12888300</v>
       </c>
       <c r="E59" s="3">
-        <v>13203600</v>
+        <v>12825300</v>
       </c>
       <c r="F59" s="3">
-        <v>12450100</v>
+        <v>13121900</v>
       </c>
       <c r="G59" s="3">
-        <v>12263000</v>
+        <v>12373100</v>
       </c>
       <c r="H59" s="3">
-        <v>12973300</v>
+        <v>12187100</v>
       </c>
       <c r="I59" s="3">
-        <v>12158100</v>
+        <v>12893100</v>
       </c>
       <c r="J59" s="3">
+        <v>12082900</v>
+      </c>
+      <c r="K59" s="3">
         <v>11328000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10549700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10507800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9989200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9769000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8417900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8818700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8928800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8582000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7926600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>7586700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>7088800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7054300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6348400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5245200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4735000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4852800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4456200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4604900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4511800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4433200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>6832000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>6921700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4873400</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>36930700</v>
+        <v>34001000</v>
       </c>
       <c r="E60" s="3">
-        <v>36484100</v>
+        <v>36702200</v>
       </c>
       <c r="F60" s="3">
-        <v>36103200</v>
+        <v>36258400</v>
       </c>
       <c r="G60" s="3">
-        <v>31165600</v>
+        <v>35879900</v>
       </c>
       <c r="H60" s="3">
-        <v>37057300</v>
+        <v>30972800</v>
       </c>
       <c r="I60" s="3">
-        <v>35635300</v>
+        <v>36828100</v>
       </c>
       <c r="J60" s="3">
+        <v>35414800</v>
+      </c>
+      <c r="K60" s="3">
         <v>35517700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>30240300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>30537000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>29022600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>28281100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>22583300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>24223100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>25433700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>25338300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>21549600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>21559800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>20444300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>21401500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>17561000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>17552800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>17032300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>19136300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>15333500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>17549600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>16369700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>16255400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>16138300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>15232400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>12899100</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>5834100</v>
+        <v>5884100</v>
       </c>
       <c r="E61" s="3">
-        <v>4551700</v>
+        <v>5798000</v>
       </c>
       <c r="F61" s="3">
-        <v>4457500</v>
+        <v>4523500</v>
       </c>
       <c r="G61" s="3">
-        <v>4078300</v>
+        <v>4430000</v>
       </c>
       <c r="H61" s="3">
-        <v>4203000</v>
+        <v>4053100</v>
       </c>
       <c r="I61" s="3">
-        <v>3977800</v>
+        <v>4177000</v>
       </c>
       <c r="J61" s="3">
+        <v>3953200</v>
+      </c>
+      <c r="K61" s="3">
         <v>3428100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2155300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1293200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1775800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1782600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1757100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1744300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1943300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2002600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2702700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1547800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1568600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1512300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1480700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1434100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1384800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1408600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1036900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1621000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2315500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2602100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1957100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1330600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1488500</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3470200</v>
+        <v>3477600</v>
       </c>
       <c r="E62" s="3">
-        <v>3604800</v>
+        <v>3448700</v>
       </c>
       <c r="F62" s="3">
-        <v>3457700</v>
+        <v>3582500</v>
       </c>
       <c r="G62" s="3">
-        <v>3268900</v>
+        <v>3436300</v>
       </c>
       <c r="H62" s="3">
-        <v>3382800</v>
+        <v>3248700</v>
       </c>
       <c r="I62" s="3">
-        <v>3264200</v>
+        <v>3361800</v>
       </c>
       <c r="J62" s="3">
+        <v>3244000</v>
+      </c>
+      <c r="K62" s="3">
         <v>3008100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3001200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2576600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2450600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2498700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1952600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1965700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1980600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1611900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1376100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1390500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1409600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1145200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>914000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>232400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>255700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>295100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>326300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>370000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>400900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>438400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>471400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>765600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>430900</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>55204800</v>
+        <v>52423700</v>
       </c>
       <c r="E66" s="3">
-        <v>53842300</v>
+        <v>54863300</v>
       </c>
       <c r="F66" s="3">
-        <v>53124800</v>
+        <v>53509200</v>
       </c>
       <c r="G66" s="3">
-        <v>47201500</v>
+        <v>52796200</v>
       </c>
       <c r="H66" s="3">
-        <v>53089500</v>
+        <v>46909500</v>
       </c>
       <c r="I66" s="3">
-        <v>51075700</v>
+        <v>52761100</v>
       </c>
       <c r="J66" s="3">
+        <v>50759700</v>
+      </c>
+      <c r="K66" s="3">
         <v>48990000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>42210400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>39625000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>38058200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>37251100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>31504700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>32676400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>32970600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>31849600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>28618600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>27388100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>26166900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>26836400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>22565900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>21696500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>20936000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>23011700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>18812300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>19592200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>19135000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>19340200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>19650900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>18394100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>15844000</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,16 +6374,19 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>10</v>
+      <c r="E72" s="3">
+        <v>6930100</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>10</v>
@@ -6220,11 +6394,11 @@
       <c r="G72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H72" s="3">
-        <v>4556700</v>
-      </c>
-      <c r="I72" s="3" t="s">
+      <c r="H72" s="3" t="s">
         <v>10</v>
+      </c>
+      <c r="I72" s="3">
+        <v>4528500</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>10</v>
@@ -6232,11 +6406,11 @@
       <c r="K72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M72" s="3">
         <v>4876200</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>10</v>
@@ -6244,23 +6418,23 @@
       <c r="O72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q72" s="3">
         <v>5422100</v>
-      </c>
-      <c r="Q72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="R72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T72" s="3">
         <v>-1479900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1609600</v>
-      </c>
-      <c r="U72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="V72" s="3" t="s">
         <v>10</v>
@@ -6268,11 +6442,11 @@
       <c r="W72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X72" s="3">
+      <c r="X72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y72" s="3">
         <v>-3287700</v>
-      </c>
-      <c r="Y72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Z72" s="3" t="s">
         <v>10</v>
@@ -6280,26 +6454,29 @@
       <c r="AA72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AB72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC72" s="3">
         <v>-3205500</v>
-      </c>
-      <c r="AC72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AD72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF72" s="3">
         <v>-3104800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-3159800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-2968300</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>32232900</v>
+        <v>30724000</v>
       </c>
       <c r="E76" s="3">
-        <v>31987700</v>
+        <v>32033500</v>
       </c>
       <c r="F76" s="3">
-        <v>30832700</v>
+        <v>31789800</v>
       </c>
       <c r="G76" s="3">
-        <v>29403600</v>
+        <v>30642000</v>
       </c>
       <c r="H76" s="3">
-        <v>29662100</v>
+        <v>29221700</v>
       </c>
       <c r="I76" s="3">
-        <v>29494900</v>
+        <v>29478600</v>
       </c>
       <c r="J76" s="3">
+        <v>29312400</v>
+      </c>
+      <c r="K76" s="3">
         <v>27987000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>28512100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>28783800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>30606900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>31130900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>26263200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>26106000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>22186300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>20091900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13297600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>12604200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>11686300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>10669800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>10179200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>8680500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>8951000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>8358800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7776600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7723400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7642600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7473100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5179500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4929000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5128500</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>471100</v>
+        <v>985100</v>
       </c>
       <c r="E81" s="3">
-        <v>1103300</v>
+        <v>468200</v>
       </c>
       <c r="F81" s="3">
-        <v>914900</v>
+        <v>1096400</v>
       </c>
       <c r="G81" s="3">
-        <v>870400</v>
+        <v>909200</v>
       </c>
       <c r="H81" s="3">
-        <v>421500</v>
+        <v>865000</v>
       </c>
       <c r="I81" s="3">
-        <v>829000</v>
+        <v>418900</v>
       </c>
       <c r="J81" s="3">
+        <v>823800</v>
+      </c>
+      <c r="K81" s="3">
         <v>608400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-413000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-711600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-398900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>114100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>503500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3386100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1114100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2423600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>169200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>559600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>94300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>94500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1118200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-697800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>420000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-317400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>218800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-134900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>150500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-73700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>34800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-250600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-134000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,8 +7201,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7098,8 +7297,11 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>2726600</v>
+        <v>-1563300</v>
       </c>
       <c r="E89" s="3">
-        <v>2085900</v>
+        <v>2709700</v>
       </c>
       <c r="F89" s="3">
-        <v>6466000</v>
+        <v>2073000</v>
       </c>
       <c r="G89" s="3">
-        <v>-3003800</v>
+        <v>6426000</v>
       </c>
       <c r="H89" s="3">
-        <v>2569900</v>
+        <v>-2985200</v>
       </c>
       <c r="I89" s="3">
-        <v>1272200</v>
+        <v>2554000</v>
       </c>
       <c r="J89" s="3">
+        <v>1264300</v>
+      </c>
+      <c r="K89" s="3">
         <v>4680400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-481200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>891700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2053700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4149200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1045200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>725700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1806000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3922400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-243300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>194300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3085000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>507700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>875500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>309700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2355000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-541300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>200500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>52300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2767300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>650300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-433900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1047900</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,8 +7923,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7798,8 +8019,11 @@
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-8768300</v>
+        <v>3925700</v>
       </c>
       <c r="E94" s="3">
-        <v>2080300</v>
+        <v>-8714000</v>
       </c>
       <c r="F94" s="3">
-        <v>-3910200</v>
+        <v>2067400</v>
       </c>
       <c r="G94" s="3">
-        <v>2320500</v>
+        <v>-3886000</v>
       </c>
       <c r="H94" s="3">
-        <v>-2489600</v>
+        <v>2306200</v>
       </c>
       <c r="I94" s="3">
-        <v>-1356000</v>
+        <v>-2474200</v>
       </c>
       <c r="J94" s="3">
+        <v>-1347600</v>
+      </c>
+      <c r="K94" s="3">
         <v>-4299300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>629900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2588300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4230000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2595800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1062300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1907800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1844800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3446700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1293100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>377600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-873100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3212700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-168500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-317800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-364300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2919400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-135000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>624600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-620100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-4568600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-980900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2206600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3057800</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8213,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,289 +8741,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-103600</v>
+        <v>-1028600</v>
       </c>
       <c r="E100" s="3">
-        <v>-623600</v>
+        <v>-102900</v>
       </c>
       <c r="F100" s="3">
-        <v>-254700</v>
+        <v>-619800</v>
       </c>
       <c r="G100" s="3">
-        <v>174500</v>
+        <v>-253100</v>
       </c>
       <c r="H100" s="3">
-        <v>-588700</v>
+        <v>173400</v>
       </c>
       <c r="I100" s="3">
-        <v>560100</v>
+        <v>-585100</v>
       </c>
       <c r="J100" s="3">
+        <v>556600</v>
+      </c>
+      <c r="K100" s="3">
         <v>-1572200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1752900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-472100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>864000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2505200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-82400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3259000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>606800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>4193100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2380000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>475500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>383300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-68600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-390500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-569400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-419200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>692900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1909300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-564100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-229500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>2462600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1161900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1772300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>415900</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-29600</v>
+        <v>-18000</v>
       </c>
       <c r="E101" s="3">
-        <v>-106100</v>
+        <v>-29400</v>
       </c>
       <c r="F101" s="3">
-        <v>254000</v>
+        <v>-105400</v>
       </c>
       <c r="G101" s="3">
-        <v>-100900</v>
+        <v>252400</v>
       </c>
       <c r="H101" s="3">
-        <v>-135700</v>
+        <v>-100300</v>
       </c>
       <c r="I101" s="3">
-        <v>250000</v>
+        <v>-134800</v>
       </c>
       <c r="J101" s="3">
+        <v>248400</v>
+      </c>
+      <c r="K101" s="3">
         <v>434700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-63400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-197900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>44100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-138900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>82900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-413700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-392000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-8800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>96100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-60200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>123900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>63500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-64700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>150400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>171000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-65200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-31600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-44300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-13900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-5300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>42400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-6174900</v>
+        <v>1315800</v>
       </c>
       <c r="E102" s="3">
-        <v>3436400</v>
+        <v>-6136700</v>
       </c>
       <c r="F102" s="3">
-        <v>2555000</v>
+        <v>3415200</v>
       </c>
       <c r="G102" s="3">
-        <v>-609700</v>
+        <v>2539200</v>
       </c>
       <c r="H102" s="3">
-        <v>-644100</v>
+        <v>-606000</v>
       </c>
       <c r="I102" s="3">
-        <v>726200</v>
+        <v>-640100</v>
       </c>
       <c r="J102" s="3">
+        <v>721700</v>
+      </c>
+      <c r="K102" s="3">
         <v>-756400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1838300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2366600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1268100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3919700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2107000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1663300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>176100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4659800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>939800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>793500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-171600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-132900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-115900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-30700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-323400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>299400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1167700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>605200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1085000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>515000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>825900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-736300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1679300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
   <si>
     <t>JD</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>35928400</v>
+        <v>41081100</v>
       </c>
       <c r="E8" s="3">
-        <v>42287600</v>
+        <v>36661700</v>
       </c>
       <c r="F8" s="3">
-        <v>34222000</v>
+        <v>43150700</v>
       </c>
       <c r="G8" s="3">
-        <v>39780500</v>
+        <v>34920500</v>
       </c>
       <c r="H8" s="3">
-        <v>33566800</v>
+        <v>40592500</v>
       </c>
       <c r="I8" s="3">
-        <v>40818800</v>
+        <v>34251900</v>
       </c>
       <c r="J8" s="3">
+        <v>41652000</v>
+      </c>
+      <c r="K8" s="3">
         <v>33646800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>37201800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>33091600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>38014500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>31089400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>36450800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>28282100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>31226500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>25672200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>29627300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>23065300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>26281900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>20763100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>22959900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>18498800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>19581700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>14663400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>17546300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>14366400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>16349600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>12428800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>13832100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>10939000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>11548800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>8751100</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>30433700</v>
+        <v>34604800</v>
       </c>
       <c r="E9" s="3">
-        <v>36277400</v>
+        <v>31054900</v>
       </c>
       <c r="F9" s="3">
-        <v>28868100</v>
+        <v>37017800</v>
       </c>
       <c r="G9" s="3">
-        <v>34056200</v>
+        <v>29457300</v>
       </c>
       <c r="H9" s="3">
-        <v>28590600</v>
+        <v>34751300</v>
       </c>
       <c r="I9" s="3">
-        <v>35080100</v>
+        <v>29174100</v>
       </c>
       <c r="J9" s="3">
+        <v>35796100</v>
+      </c>
+      <c r="K9" s="3">
         <v>28646000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>32211800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>28473300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>32899800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>26669600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>31893800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>24228300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>26891500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>21723700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>25407600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>19510100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>22586700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>17665900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>19579600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>15720700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>16797400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>12408700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>15176900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>12334900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>14218500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>10502000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>11955000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>18670800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>19852900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>14923400</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>5494600</v>
+        <v>6476300</v>
       </c>
       <c r="E10" s="3">
-        <v>6010200</v>
+        <v>5606800</v>
       </c>
       <c r="F10" s="3">
-        <v>5353800</v>
+        <v>6132900</v>
       </c>
       <c r="G10" s="3">
-        <v>5724400</v>
+        <v>5463100</v>
       </c>
       <c r="H10" s="3">
-        <v>4976200</v>
+        <v>5841200</v>
       </c>
       <c r="I10" s="3">
-        <v>5738800</v>
+        <v>5077800</v>
       </c>
       <c r="J10" s="3">
+        <v>5855900</v>
+      </c>
+      <c r="K10" s="3">
         <v>5000800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4990000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4618200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5114600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4419800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4557000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4053800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4335000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3948500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4219700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3555200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3695200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3097200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3380300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2778100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2784300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2254700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2369400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2031400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2131100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1926800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1877100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>-7731900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>-8304100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>-6172300</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,106 +1138,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>584900</v>
+      </c>
+      <c r="E12" s="3">
+        <v>559400</v>
+      </c>
+      <c r="F12" s="3">
+        <v>602700</v>
+      </c>
+      <c r="G12" s="3">
+        <v>525600</v>
+      </c>
+      <c r="H12" s="3">
+        <v>562400</v>
+      </c>
+      <c r="I12" s="3">
+        <v>577500</v>
+      </c>
+      <c r="J12" s="3">
+        <v>602800</v>
+      </c>
+      <c r="K12" s="3">
+        <v>557200</v>
+      </c>
+      <c r="L12" s="3">
+        <v>551500</v>
+      </c>
+      <c r="M12" s="3">
+        <v>600100</v>
+      </c>
+      <c r="N12" s="3">
+        <v>562000</v>
+      </c>
+      <c r="O12" s="3">
+        <v>565400</v>
+      </c>
+      <c r="P12" s="3">
+        <v>526700</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>627000</v>
+      </c>
+      <c r="R12" s="3">
+        <v>623400</v>
+      </c>
+      <c r="S12" s="3">
+        <v>601500</v>
+      </c>
+      <c r="T12" s="3">
+        <v>527400</v>
+      </c>
+      <c r="U12" s="3">
+        <v>616900</v>
+      </c>
+      <c r="V12" s="3">
+        <v>549200</v>
+      </c>
+      <c r="W12" s="3">
         <v>548200</v>
       </c>
-      <c r="E12" s="3">
-        <v>590600</v>
-      </c>
-      <c r="F12" s="3">
-        <v>515100</v>
-      </c>
-      <c r="G12" s="3">
-        <v>551100</v>
-      </c>
-      <c r="H12" s="3">
-        <v>565900</v>
-      </c>
-      <c r="I12" s="3">
-        <v>590800</v>
-      </c>
-      <c r="J12" s="3">
-        <v>557200</v>
-      </c>
-      <c r="K12" s="3">
-        <v>551500</v>
-      </c>
-      <c r="L12" s="3">
-        <v>600100</v>
-      </c>
-      <c r="M12" s="3">
-        <v>562000</v>
-      </c>
-      <c r="N12" s="3">
+      <c r="X12" s="3">
         <v>565400</v>
       </c>
-      <c r="O12" s="3">
-        <v>526700</v>
-      </c>
-      <c r="P12" s="3">
-        <v>627000</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>623400</v>
-      </c>
-      <c r="R12" s="3">
-        <v>601500</v>
-      </c>
-      <c r="S12" s="3">
-        <v>527400</v>
-      </c>
-      <c r="T12" s="3">
-        <v>616900</v>
-      </c>
-      <c r="U12" s="3">
-        <v>549200</v>
-      </c>
-      <c r="V12" s="3">
-        <v>548200</v>
-      </c>
-      <c r="W12" s="3">
-        <v>565400</v>
-      </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>564000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>505400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>478900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>395500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>342700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>302600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>257500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>226400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>184500</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>168700</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>175700</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1321,204 +1338,213 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-3000</v>
+        <v>-29300</v>
       </c>
       <c r="E14" s="3">
-        <v>598500</v>
+        <v>-3100</v>
       </c>
       <c r="F14" s="3">
+        <v>610700</v>
+      </c>
+      <c r="G14" s="3">
         <v>-700</v>
       </c>
-      <c r="G14" s="3">
-        <v>-143400</v>
-      </c>
       <c r="H14" s="3">
-        <v>-68100</v>
+        <v>-146300</v>
       </c>
       <c r="I14" s="3">
+        <v>-69500</v>
+      </c>
+      <c r="J14" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="K14" s="3">
+        <v>-173500</v>
+      </c>
+      <c r="L14" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="M14" s="3">
+        <v>490000</v>
+      </c>
+      <c r="N14" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="O14" s="3">
+        <v>-82300</v>
+      </c>
+      <c r="P14" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-11500</v>
       </c>
-      <c r="J14" s="3">
-        <v>-173500</v>
-      </c>
-      <c r="K14" s="3">
-        <v>-4300</v>
-      </c>
-      <c r="L14" s="3">
-        <v>490000</v>
-      </c>
-      <c r="M14" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="N14" s="3">
-        <v>-82300</v>
-      </c>
-      <c r="O14" s="3">
-        <v>-12500</v>
-      </c>
-      <c r="P14" s="3">
-        <v>-11500</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-154400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-50700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-28800</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>-598200</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>10</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>3100</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>10</v>
+      <c r="AE14" s="3">
+        <v>0</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="3" t="s">
+      <c r="AG14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>58000</v>
+        <v>60500</v>
       </c>
       <c r="E15" s="3">
-        <v>58300</v>
+        <v>59200</v>
       </c>
       <c r="F15" s="3">
-        <v>58200</v>
+        <v>59500</v>
       </c>
       <c r="G15" s="3">
-        <v>60500</v>
+        <v>59400</v>
       </c>
       <c r="H15" s="3">
-        <v>61600</v>
+        <v>61700</v>
       </c>
       <c r="I15" s="3">
-        <v>60700</v>
+        <v>62900</v>
       </c>
       <c r="J15" s="3">
+        <v>61900</v>
+      </c>
+      <c r="K15" s="3">
         <v>61200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>58100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>54100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>51900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>53400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>53300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>50600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>51900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>50300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>43800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>44500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>72600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>22500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>22600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>67800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>65800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>63900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>64600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>64000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>66700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>66300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>65700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>63900</v>
-      </c>
-      <c r="AG15" s="3">
-        <v>65100</v>
       </c>
       <c r="AH15" s="3">
         <v>65100</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>65100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>34861500</v>
+        <v>39571400</v>
       </c>
       <c r="E17" s="3">
-        <v>42003100</v>
+        <v>35573100</v>
       </c>
       <c r="F17" s="3">
-        <v>32936000</v>
+        <v>42860500</v>
       </c>
       <c r="G17" s="3">
-        <v>38634000</v>
+        <v>33608200</v>
       </c>
       <c r="H17" s="3">
-        <v>32675900</v>
+        <v>39422500</v>
       </c>
       <c r="I17" s="3">
-        <v>40161000</v>
+        <v>33342900</v>
       </c>
       <c r="J17" s="3">
+        <v>40980800</v>
+      </c>
+      <c r="K17" s="3">
         <v>32437200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>36675000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>33249000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>38068500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>30723700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>36407600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>28051100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>31143700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>25026300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>28884000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>22699300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>26200400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>19997300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>22613600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>18311500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>19718100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>14754400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>17694700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>14365700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>16586500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>12354200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>13891900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>10842800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>11598000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>8785200</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1066900</v>
+        <v>1509800</v>
       </c>
       <c r="E18" s="3">
-        <v>284500</v>
+        <v>1088600</v>
       </c>
       <c r="F18" s="3">
-        <v>1286000</v>
+        <v>290300</v>
       </c>
       <c r="G18" s="3">
-        <v>1146600</v>
+        <v>1312200</v>
       </c>
       <c r="H18" s="3">
-        <v>890900</v>
+        <v>1170000</v>
       </c>
       <c r="I18" s="3">
-        <v>657800</v>
+        <v>909000</v>
       </c>
       <c r="J18" s="3">
+        <v>671200</v>
+      </c>
+      <c r="K18" s="3">
         <v>1209600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>526700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-157400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-54000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>365700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>43200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>231000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>82800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>645900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>743300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>366100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>81500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>765800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>346300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>187200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-136400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-91100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-148400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-236900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>74600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-59800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>96200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-49200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-34100</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,498 +1815,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>268600</v>
+        <v>788800</v>
       </c>
       <c r="E20" s="3">
-        <v>300400</v>
+        <v>274100</v>
       </c>
       <c r="F20" s="3">
-        <v>304500</v>
+        <v>306500</v>
       </c>
       <c r="G20" s="3">
-        <v>288600</v>
+        <v>310700</v>
       </c>
       <c r="H20" s="3">
-        <v>269400</v>
+        <v>294500</v>
       </c>
       <c r="I20" s="3">
-        <v>-34100</v>
+        <v>274900</v>
       </c>
       <c r="J20" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="K20" s="3">
         <v>-64400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>271200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-197500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-591600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-698300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>140600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>378600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3292200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>617500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1840500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-115100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>573300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-562800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-172200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>990200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-542100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>534700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-120500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>265800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>95700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>120500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>42100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-15000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-113100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-26100</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1641800</v>
+        <v>2303200</v>
       </c>
       <c r="E21" s="3">
-        <v>593900</v>
+        <v>1675300</v>
       </c>
       <c r="F21" s="3">
-        <v>1597000</v>
+        <v>606100</v>
       </c>
       <c r="G21" s="3">
-        <v>1448200</v>
+        <v>1629600</v>
       </c>
       <c r="H21" s="3">
-        <v>1431100</v>
+        <v>1477800</v>
       </c>
       <c r="I21" s="3">
-        <v>639800</v>
+        <v>1460300</v>
       </c>
       <c r="J21" s="3">
+        <v>652900</v>
+      </c>
+      <c r="K21" s="3">
         <v>1166500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>803700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-124000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-641300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-321900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>153900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>841900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3397100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1272200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2592000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>472700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>658500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>207000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>126300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1433100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-660600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>476100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-259600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>437800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-31900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>117300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-15000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>219700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-158100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-50000</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>83000</v>
+        <v>97000</v>
       </c>
       <c r="E22" s="3">
-        <v>128100</v>
+        <v>84700</v>
       </c>
       <c r="F22" s="3">
-        <v>98100</v>
+        <v>130700</v>
       </c>
       <c r="G22" s="3">
-        <v>90400</v>
+        <v>100100</v>
       </c>
       <c r="H22" s="3">
-        <v>81500</v>
+        <v>92200</v>
       </c>
       <c r="I22" s="3">
-        <v>96400</v>
+        <v>83200</v>
       </c>
       <c r="J22" s="3">
+        <v>98400</v>
+      </c>
+      <c r="K22" s="3">
         <v>80000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>67300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>47600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>61500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>39300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>33400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>35900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>41200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>43900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>47800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>32700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>33800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>25100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>23700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>28600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>21000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>33700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>34400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>32800</v>
       </c>
-      <c r="AC22" s="3" t="s">
+      <c r="AD22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>42000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>30900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>27600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>9200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>10400</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1252400</v>
+        <v>2201500</v>
       </c>
       <c r="E23" s="3">
-        <v>456800</v>
+        <v>1278000</v>
       </c>
       <c r="F23" s="3">
-        <v>1492400</v>
+        <v>466100</v>
       </c>
       <c r="G23" s="3">
-        <v>1344800</v>
+        <v>1522900</v>
       </c>
       <c r="H23" s="3">
-        <v>1078800</v>
+        <v>1372300</v>
       </c>
       <c r="I23" s="3">
-        <v>527200</v>
+        <v>1100800</v>
       </c>
       <c r="J23" s="3">
+        <v>538000</v>
+      </c>
+      <c r="K23" s="3">
         <v>1065200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>730700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-402500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-707200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-371900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>150400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>573800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3333800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1219500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2536000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>218300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>621000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>177900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>150400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1148800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-699500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>409900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-303300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>233600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-141200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>153100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-48600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>53600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-171500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-70600</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>234900</v>
+        <v>285100</v>
       </c>
       <c r="E24" s="3">
-        <v>192600</v>
+        <v>239700</v>
       </c>
       <c r="F24" s="3">
-        <v>356300</v>
+        <v>196500</v>
       </c>
       <c r="G24" s="3">
-        <v>388400</v>
+        <v>363600</v>
       </c>
       <c r="H24" s="3">
-        <v>222300</v>
+        <v>396300</v>
       </c>
       <c r="I24" s="3">
-        <v>82200</v>
+        <v>226800</v>
       </c>
       <c r="J24" s="3">
+        <v>83900</v>
+      </c>
+      <c r="K24" s="3">
         <v>241900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>170600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>83300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>25600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>92700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>81800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>66700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-46200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>101700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>117400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>51500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>73800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>93100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>67000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>42700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>8900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>7200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>23400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>21700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>7900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>13000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>14600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1017500</v>
+        <v>1916500</v>
       </c>
       <c r="E26" s="3">
-        <v>264200</v>
+        <v>1038300</v>
       </c>
       <c r="F26" s="3">
-        <v>1136100</v>
+        <v>269600</v>
       </c>
       <c r="G26" s="3">
-        <v>956500</v>
+        <v>1159300</v>
       </c>
       <c r="H26" s="3">
-        <v>856500</v>
+        <v>976000</v>
       </c>
       <c r="I26" s="3">
-        <v>445000</v>
+        <v>873900</v>
       </c>
       <c r="J26" s="3">
+        <v>454100</v>
+      </c>
+      <c r="K26" s="3">
         <v>823300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>560100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-485800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-732800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-464600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>68600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>507000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3380000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1117800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2418600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>166800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>547200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>84800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>83400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1106100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-708400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>402600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-326700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>212000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-143100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>145200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-46200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>40500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-186100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-70900</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>985100</v>
+        <v>1782600</v>
       </c>
       <c r="E27" s="3">
-        <v>468200</v>
+        <v>1005200</v>
       </c>
       <c r="F27" s="3">
-        <v>1096400</v>
+        <v>477800</v>
       </c>
       <c r="G27" s="3">
-        <v>909200</v>
+        <v>1118800</v>
       </c>
       <c r="H27" s="3">
-        <v>865000</v>
+        <v>927800</v>
       </c>
       <c r="I27" s="3">
-        <v>418900</v>
+        <v>882700</v>
       </c>
       <c r="J27" s="3">
+        <v>427500</v>
+      </c>
+      <c r="K27" s="3">
         <v>823800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>608400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-413000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-711600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-398900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>114100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>503500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3386100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1114100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2423600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>169200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>559600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>94300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>94500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1118200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-697800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>420000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-317400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>218800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-134900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>150500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-42600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>43500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-183400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-68000</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2751,19 +2812,22 @@
         <v>0</v>
       </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-31100</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-8700</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-67100</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-66100</v>
       </c>
     </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-268600</v>
+        <v>-788800</v>
       </c>
       <c r="E32" s="3">
-        <v>-300400</v>
+        <v>-274100</v>
       </c>
       <c r="F32" s="3">
-        <v>-304500</v>
+        <v>-306500</v>
       </c>
       <c r="G32" s="3">
-        <v>-288600</v>
+        <v>-310700</v>
       </c>
       <c r="H32" s="3">
-        <v>-269400</v>
+        <v>-294500</v>
       </c>
       <c r="I32" s="3">
-        <v>34100</v>
+        <v>-274900</v>
       </c>
       <c r="J32" s="3">
+        <v>34800</v>
+      </c>
+      <c r="K32" s="3">
         <v>64400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-271200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>197500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>591600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>698300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-140600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-378600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3292200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-617500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1840500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>115100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-573300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>562800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>172200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-990200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>542100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-534700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>120500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-265800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-95700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-120500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-42100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>15000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>113100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>985100</v>
+        <v>1782600</v>
       </c>
       <c r="E33" s="3">
-        <v>468200</v>
+        <v>1005200</v>
       </c>
       <c r="F33" s="3">
-        <v>1096400</v>
+        <v>477800</v>
       </c>
       <c r="G33" s="3">
-        <v>909200</v>
+        <v>1118800</v>
       </c>
       <c r="H33" s="3">
-        <v>865000</v>
+        <v>927800</v>
       </c>
       <c r="I33" s="3">
-        <v>418900</v>
+        <v>882700</v>
       </c>
       <c r="J33" s="3">
+        <v>427500</v>
+      </c>
+      <c r="K33" s="3">
         <v>823800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>608400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-413000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-711600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-398900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>114100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>503500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3386100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1114100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2423600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>169200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>559600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>94300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>94500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1118200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-697800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>420000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-317400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>218800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-134900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>150500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-73700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>34800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-250600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-134000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>985100</v>
+        <v>1782600</v>
       </c>
       <c r="E35" s="3">
-        <v>468200</v>
+        <v>1005200</v>
       </c>
       <c r="F35" s="3">
-        <v>1096400</v>
+        <v>477800</v>
       </c>
       <c r="G35" s="3">
-        <v>909200</v>
+        <v>1118800</v>
       </c>
       <c r="H35" s="3">
-        <v>865000</v>
+        <v>927800</v>
       </c>
       <c r="I35" s="3">
-        <v>418900</v>
+        <v>882700</v>
       </c>
       <c r="J35" s="3">
+        <v>427500</v>
+      </c>
+      <c r="K35" s="3">
         <v>823800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>608400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-413000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-711600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-398900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>114100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>503500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3386100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1114100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2423600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>169200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>559600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>94300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>94500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1118200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-697800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>420000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-317400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>218800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-134900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>150500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-73700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>34800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-250600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-134000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,890 +3611,918 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>11277400</v>
+        <v>11912200</v>
       </c>
       <c r="E41" s="3">
-        <v>9932600</v>
+        <v>11507600</v>
       </c>
       <c r="F41" s="3">
-        <v>16022600</v>
+        <v>10135300</v>
       </c>
       <c r="G41" s="3">
-        <v>12575300</v>
+        <v>16349600</v>
       </c>
       <c r="H41" s="3">
-        <v>10275400</v>
+        <v>12832000</v>
       </c>
       <c r="I41" s="3">
-        <v>10895400</v>
+        <v>10485100</v>
       </c>
       <c r="J41" s="3">
+        <v>11117800</v>
+      </c>
+      <c r="K41" s="3">
         <v>11516500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>10957700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11662700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9750300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>12508900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>13981000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9940000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>11983000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10773900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10546800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6867200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5692900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4946600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5007900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5202700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4975900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4758300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5055400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5051100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3812400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3207200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4134000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3435700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2263900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3611700</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>12485700</v>
+        <v>16551900</v>
       </c>
       <c r="E42" s="3">
-        <v>16338000</v>
+        <v>12740500</v>
       </c>
       <c r="F42" s="3">
-        <v>17460900</v>
+        <v>16671400</v>
       </c>
       <c r="G42" s="3">
-        <v>19909000</v>
+        <v>17817300</v>
       </c>
       <c r="H42" s="3">
-        <v>16916300</v>
+        <v>20315400</v>
       </c>
       <c r="I42" s="3">
-        <v>19493700</v>
+        <v>17261600</v>
       </c>
       <c r="J42" s="3">
+        <v>19891600</v>
+      </c>
+      <c r="K42" s="3">
         <v>17746500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>16991400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>13268900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>15784600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>14548600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>10836500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>8835100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>8432300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>7132600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>7180900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>4632500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>3788300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>3767300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>3752600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>644900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>295600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>723900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1829700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1713700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1274500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>2383300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1890700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>3089800</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>2623300</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1793200</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2829900</v>
+        <v>3544000</v>
       </c>
       <c r="E43" s="3">
-        <v>3097000</v>
+        <v>2887700</v>
       </c>
       <c r="F43" s="3">
-        <v>3500600</v>
+        <v>3160200</v>
       </c>
       <c r="G43" s="3">
-        <v>3368100</v>
+        <v>3572000</v>
       </c>
       <c r="H43" s="3">
-        <v>2891700</v>
+        <v>3436800</v>
       </c>
       <c r="I43" s="3">
-        <v>3691400</v>
+        <v>2950700</v>
       </c>
       <c r="J43" s="3">
+        <v>3766700</v>
+      </c>
+      <c r="K43" s="3">
         <v>3346500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2713700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2280400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2397400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2461700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3709000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2365400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2013200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2079900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1986200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1702600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1844100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2499900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2102900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1622800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2463500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2348300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3701700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2819300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4850500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5597400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>6769800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5409200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>4288500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>4025000</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>9394100</v>
+        <v>9959400</v>
       </c>
       <c r="E44" s="3">
-        <v>9402900</v>
+        <v>9585800</v>
       </c>
       <c r="F44" s="3">
-        <v>8930400</v>
+        <v>9594800</v>
       </c>
       <c r="G44" s="3">
-        <v>8781700</v>
+        <v>9112700</v>
       </c>
       <c r="H44" s="3">
-        <v>8745400</v>
+        <v>8961000</v>
       </c>
       <c r="I44" s="3">
-        <v>10769400</v>
+        <v>8923900</v>
       </c>
       <c r="J44" s="3">
+        <v>10989300</v>
+      </c>
+      <c r="K44" s="3">
         <v>9913900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>10569600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>9498500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>10416300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8535300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>9445600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>8285800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>8203400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>8155700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>8027700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>7980200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>8920400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>7431900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>6954700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>5841700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>6394500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5578100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>6227400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5188800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>6188800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5388800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4622900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3906300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4204300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3287100</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3260300</v>
+        <v>3456400</v>
       </c>
       <c r="E45" s="3">
-        <v>3756600</v>
+        <v>3326800</v>
       </c>
       <c r="F45" s="3">
-        <v>3492700</v>
+        <v>3833200</v>
       </c>
       <c r="G45" s="3">
-        <v>3609200</v>
+        <v>3564000</v>
       </c>
       <c r="H45" s="3">
-        <v>3325900</v>
+        <v>3682800</v>
       </c>
       <c r="I45" s="3">
-        <v>3654500</v>
+        <v>3393800</v>
       </c>
       <c r="J45" s="3">
+        <v>3729100</v>
+      </c>
+      <c r="K45" s="3">
         <v>3676900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3808900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3226200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2940200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2998600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3046100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2252800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2052400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2445100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2537400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1621900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1172100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1310600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1654700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1212300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1098700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1921800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2095000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1439700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>945200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1774000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2015800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1285200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3842100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>840300</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>39247400</v>
+        <v>45423900</v>
       </c>
       <c r="E46" s="3">
-        <v>42527000</v>
+        <v>40048500</v>
       </c>
       <c r="F46" s="3">
-        <v>49407100</v>
+        <v>43395100</v>
       </c>
       <c r="G46" s="3">
-        <v>48243300</v>
+        <v>50415600</v>
       </c>
       <c r="H46" s="3">
-        <v>42154700</v>
+        <v>49228000</v>
       </c>
       <c r="I46" s="3">
-        <v>48504400</v>
+        <v>43015100</v>
       </c>
       <c r="J46" s="3">
+        <v>49494400</v>
+      </c>
+      <c r="K46" s="3">
         <v>46200300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>45041200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>39936700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>41288800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>41053100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>41018200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>31679100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>32684300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>30587100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>30279000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>22804500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>21417800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>19956300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>19472800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>14524500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>15228200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>15330400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>18909200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>16212600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>17071400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>18350700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>19433200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>17126200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>15551100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>13557200</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>18709800</v>
+        <v>20015100</v>
       </c>
       <c r="E47" s="3">
-        <v>19008900</v>
+        <v>19091700</v>
       </c>
       <c r="F47" s="3">
-        <v>8660700</v>
+        <v>19396900</v>
       </c>
       <c r="G47" s="3">
-        <v>8931600</v>
+        <v>8837500</v>
       </c>
       <c r="H47" s="3">
-        <v>9339200</v>
+        <v>9113900</v>
       </c>
       <c r="I47" s="3">
-        <v>9567900</v>
+        <v>9529800</v>
       </c>
       <c r="J47" s="3">
+        <v>9763100</v>
+      </c>
+      <c r="K47" s="3">
         <v>10218500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>10205600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>9930000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>11340700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>12655200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>13323000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>13426300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>13584000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>11753100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>10996100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>9079600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>8775800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>8358600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>8423900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>8106100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>6863300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>7013800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>5555200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>4438500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>4241400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2881600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2652400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>3265500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>3299200</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>3258900</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>14128100</v>
+        <v>15094200</v>
       </c>
       <c r="E48" s="3">
-        <v>13929000</v>
+        <v>14416500</v>
       </c>
       <c r="F48" s="3">
-        <v>13701700</v>
+        <v>14213300</v>
       </c>
       <c r="G48" s="3">
-        <v>12726600</v>
+        <v>13981400</v>
       </c>
       <c r="H48" s="3">
-        <v>12307800</v>
+        <v>12986400</v>
       </c>
       <c r="I48" s="3">
-        <v>12228300</v>
+        <v>12559100</v>
       </c>
       <c r="J48" s="3">
+        <v>12477900</v>
+      </c>
+      <c r="K48" s="3">
         <v>11626200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10116500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9642700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8094300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7452400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7186400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6362600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6401400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6278600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5475000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5079500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5405300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5221700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4807300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4842500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4013700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3446300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2997300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2456000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2340500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1904000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1599700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1382600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1311100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1280900</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>9015200</v>
+        <v>9424700</v>
       </c>
       <c r="E49" s="3">
-        <v>9184600</v>
+        <v>9199200</v>
       </c>
       <c r="F49" s="3">
-        <v>9568100</v>
+        <v>9372100</v>
       </c>
       <c r="G49" s="3">
-        <v>9576700</v>
+        <v>9763400</v>
       </c>
       <c r="H49" s="3">
-        <v>9099200</v>
+        <v>9772200</v>
       </c>
       <c r="I49" s="3">
-        <v>9133800</v>
+        <v>9284900</v>
       </c>
       <c r="J49" s="3">
+        <v>9320200</v>
+      </c>
+      <c r="K49" s="3">
         <v>9128900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7500300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7423000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4491400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4519900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4465800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4137700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3966100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4229400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3622600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3318700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3333000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3303300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3256200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3246200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3214100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3076700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2868200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2862900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3026700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3021300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2440200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2475700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2513800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2566700</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2047300</v>
+        <v>1909900</v>
       </c>
       <c r="E52" s="3">
-        <v>2247300</v>
+        <v>2089000</v>
       </c>
       <c r="F52" s="3">
-        <v>3961300</v>
+        <v>2293200</v>
       </c>
       <c r="G52" s="3">
-        <v>3959900</v>
+        <v>4042200</v>
       </c>
       <c r="H52" s="3">
-        <v>3230200</v>
+        <v>4040800</v>
       </c>
       <c r="I52" s="3">
-        <v>2805500</v>
+        <v>3296100</v>
       </c>
       <c r="J52" s="3">
+        <v>2862700</v>
+      </c>
+      <c r="K52" s="3">
         <v>2898300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4113300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3790000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3193600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2984600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2388700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2162100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2146600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2308600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1568800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1633700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1060400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1013300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1545900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2025800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1057800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1019700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1040600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>618800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>635500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>620000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>687900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>580500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1665500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>308700</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>83147700</v>
+        <v>91867600</v>
       </c>
       <c r="E54" s="3">
-        <v>86896800</v>
+        <v>84844900</v>
       </c>
       <c r="F54" s="3">
-        <v>85299000</v>
+        <v>88670500</v>
       </c>
       <c r="G54" s="3">
-        <v>83438100</v>
+        <v>87040100</v>
       </c>
       <c r="H54" s="3">
-        <v>76131100</v>
+        <v>85141200</v>
       </c>
       <c r="I54" s="3">
-        <v>82239700</v>
+        <v>77685100</v>
       </c>
       <c r="J54" s="3">
+        <v>83918300</v>
+      </c>
+      <c r="K54" s="3">
         <v>80072100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>76976900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>70722500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>68408700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>68665100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>68382000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>57767800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>58782500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>55156900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>51941500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>41916200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>39992300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>37853200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>37506100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>32745200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>30377000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>29887000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>31370400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>26588900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>27315600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>26777600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>26813400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>24830500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>23323100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>20972500</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,596 +5099,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>20385100</v>
+        <v>25762800</v>
       </c>
       <c r="E57" s="3">
-        <v>23181500</v>
+        <v>20801200</v>
       </c>
       <c r="F57" s="3">
-        <v>21238200</v>
+        <v>23654600</v>
       </c>
       <c r="G57" s="3">
-        <v>21026700</v>
+        <v>21671700</v>
       </c>
       <c r="H57" s="3">
-        <v>16812800</v>
+        <v>21455900</v>
       </c>
       <c r="I57" s="3">
-        <v>22256900</v>
+        <v>17156000</v>
       </c>
       <c r="J57" s="3">
+        <v>22711200</v>
+      </c>
+      <c r="K57" s="3">
         <v>20845600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>22277500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>17322400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>19427400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>18034400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>18431300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>13566400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>14950600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>15570300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>14940700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>12266000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>13973100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>13355500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>14326200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>10927000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>11647500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>10957000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>12582100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>8938300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>11032500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>10032000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>10014300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>6362200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>6695000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>6031800</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>727700</v>
+        <v>789600</v>
       </c>
       <c r="E58" s="3">
-        <v>695500</v>
+        <v>742500</v>
       </c>
       <c r="F58" s="3">
-        <v>1898300</v>
+        <v>709700</v>
       </c>
       <c r="G58" s="3">
-        <v>2480100</v>
+        <v>1937100</v>
       </c>
       <c r="H58" s="3">
-        <v>1972900</v>
+        <v>2530700</v>
       </c>
       <c r="I58" s="3">
-        <v>1678100</v>
+        <v>2013200</v>
       </c>
       <c r="J58" s="3">
+        <v>1712300</v>
+      </c>
+      <c r="K58" s="3">
         <v>2486300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1912100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2368200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>601800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>999000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>80800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>598900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>453800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>934600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1815600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1357000</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
       <c r="V58" s="3">
         <v>0</v>
       </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>21000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>285600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>660100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1340300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1701400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1939000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1912200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1825900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1807800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2944100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1615600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1993900</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>12888300</v>
+        <v>12953900</v>
       </c>
       <c r="E59" s="3">
-        <v>12825300</v>
+        <v>13151300</v>
       </c>
       <c r="F59" s="3">
-        <v>13121900</v>
+        <v>13087000</v>
       </c>
       <c r="G59" s="3">
-        <v>12373100</v>
+        <v>13389700</v>
       </c>
       <c r="H59" s="3">
-        <v>12187100</v>
+        <v>12625600</v>
       </c>
       <c r="I59" s="3">
-        <v>12893100</v>
+        <v>12435800</v>
       </c>
       <c r="J59" s="3">
+        <v>13156300</v>
+      </c>
+      <c r="K59" s="3">
         <v>12082900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11328000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10549700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10507800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9989200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9769000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8417900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8818700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8928800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>8582000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>7926600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>7586700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7088800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>7054300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>6348400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5245200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4735000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4852800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4456200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4604900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4511800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4433200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>6832000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>6921700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4873400</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>34001000</v>
+        <v>39506400</v>
       </c>
       <c r="E60" s="3">
-        <v>36702200</v>
+        <v>34695000</v>
       </c>
       <c r="F60" s="3">
-        <v>36258400</v>
+        <v>37451300</v>
       </c>
       <c r="G60" s="3">
-        <v>35879900</v>
+        <v>36998500</v>
       </c>
       <c r="H60" s="3">
-        <v>30972800</v>
+        <v>36612200</v>
       </c>
       <c r="I60" s="3">
-        <v>36828100</v>
+        <v>31605000</v>
       </c>
       <c r="J60" s="3">
+        <v>37579800</v>
+      </c>
+      <c r="K60" s="3">
         <v>35414800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>35517700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>30240300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>30537000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>29022600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>28281100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>22583300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>24223100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>25433700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>25338300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>21549600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>21559800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>20444300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>21401500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>17561000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>17552800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>17032300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>19136300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>15333500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>17549600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>16369700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>16255400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>16138300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>15232400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>12899100</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>5884100</v>
+        <v>8005000</v>
       </c>
       <c r="E61" s="3">
-        <v>5798000</v>
+        <v>6004200</v>
       </c>
       <c r="F61" s="3">
-        <v>4523500</v>
+        <v>5916400</v>
       </c>
       <c r="G61" s="3">
-        <v>4430000</v>
+        <v>4615800</v>
       </c>
       <c r="H61" s="3">
-        <v>4053100</v>
+        <v>4520400</v>
       </c>
       <c r="I61" s="3">
-        <v>4177000</v>
+        <v>4135800</v>
       </c>
       <c r="J61" s="3">
+        <v>4262200</v>
+      </c>
+      <c r="K61" s="3">
         <v>3953200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3428100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2155300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1293200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1775800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1782600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1757100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1744300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1943300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2002600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2702700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1547800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1568600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1512300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1480700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1434100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1384800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1408600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1036900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1621000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2315500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2602100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1957100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1330600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1488500</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3477600</v>
+        <v>3761100</v>
       </c>
       <c r="E62" s="3">
-        <v>3448700</v>
+        <v>3548600</v>
       </c>
       <c r="F62" s="3">
-        <v>3582500</v>
+        <v>3519100</v>
       </c>
       <c r="G62" s="3">
-        <v>3436300</v>
+        <v>3655600</v>
       </c>
       <c r="H62" s="3">
-        <v>3248700</v>
+        <v>3506500</v>
       </c>
       <c r="I62" s="3">
-        <v>3361800</v>
+        <v>3315000</v>
       </c>
       <c r="J62" s="3">
+        <v>3430500</v>
+      </c>
+      <c r="K62" s="3">
         <v>3244000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3008100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3001200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2576600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2450600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2498700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1952600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1965700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1980600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1611900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1376100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1390500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1409600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1145200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>914000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>232400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>255700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>295100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>326300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>370000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>400900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>438400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>471400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>765600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>430900</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>52423700</v>
+        <v>60744300</v>
       </c>
       <c r="E66" s="3">
-        <v>54863300</v>
+        <v>53493700</v>
       </c>
       <c r="F66" s="3">
-        <v>53509200</v>
+        <v>55983200</v>
       </c>
       <c r="G66" s="3">
-        <v>52796200</v>
+        <v>54601400</v>
       </c>
       <c r="H66" s="3">
-        <v>46909500</v>
+        <v>53873800</v>
       </c>
       <c r="I66" s="3">
-        <v>52761100</v>
+        <v>47866900</v>
       </c>
       <c r="J66" s="3">
+        <v>53838000</v>
+      </c>
+      <c r="K66" s="3">
         <v>50759700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>48990000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>42210400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>39625000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>38058200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>37251100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>31504700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>32676400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>32970600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>31849600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>28618600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>27388100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>26166900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>26836400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>22565900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>21696500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>20936000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>23011700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>18812300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>19592200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>19135000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>19340200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>19650900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>18394100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>15844000</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,19 +6548,22 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E72" s="3">
-        <v>6930100</v>
-      </c>
-      <c r="F72" s="3" t="s">
+      <c r="E72" s="3" t="s">
         <v>10</v>
+      </c>
+      <c r="F72" s="3">
+        <v>7071600</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>10</v>
@@ -6397,11 +6571,11 @@
       <c r="H72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I72" s="3">
-        <v>4528500</v>
-      </c>
-      <c r="J72" s="3" t="s">
+      <c r="I72" s="3" t="s">
         <v>10</v>
+      </c>
+      <c r="J72" s="3">
+        <v>4620900</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>10</v>
@@ -6409,11 +6583,11 @@
       <c r="L72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N72" s="3">
         <v>4876200</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>10</v>
@@ -6421,23 +6595,23 @@
       <c r="P72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R72" s="3">
         <v>5422100</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T72" s="3">
+      <c r="T72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="U72" s="3">
         <v>-1479900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1609600</v>
-      </c>
-      <c r="V72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="W72" s="3" t="s">
         <v>10</v>
@@ -6445,11 +6619,11 @@
       <c r="X72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z72" s="3">
         <v>-3287700</v>
-      </c>
-      <c r="Z72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AA72" s="3" t="s">
         <v>10</v>
@@ -6457,26 +6631,29 @@
       <c r="AB72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AC72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD72" s="3">
         <v>-3205500</v>
-      </c>
-      <c r="AD72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AE72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AF72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG72" s="3">
         <v>-3104800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-3159800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-2968300</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>30724000</v>
+        <v>31123300</v>
       </c>
       <c r="E76" s="3">
-        <v>32033500</v>
+        <v>31351100</v>
       </c>
       <c r="F76" s="3">
-        <v>31789800</v>
+        <v>32687300</v>
       </c>
       <c r="G76" s="3">
-        <v>30642000</v>
+        <v>32438700</v>
       </c>
       <c r="H76" s="3">
-        <v>29221700</v>
+        <v>31267400</v>
       </c>
       <c r="I76" s="3">
-        <v>29478600</v>
+        <v>29818100</v>
       </c>
       <c r="J76" s="3">
+        <v>30080300</v>
+      </c>
+      <c r="K76" s="3">
         <v>29312400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>27987000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>28512100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>28783800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>30606900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>31130900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>26263200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>26106000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>22186300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>20091900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13297600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>12604200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>11686300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>10669800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>10179200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>8680500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>8951000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>8358800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7776600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7723400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7642600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7473100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5179500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4929000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5128500</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>985100</v>
+        <v>1782600</v>
       </c>
       <c r="E81" s="3">
-        <v>468200</v>
+        <v>1005200</v>
       </c>
       <c r="F81" s="3">
-        <v>1096400</v>
+        <v>477800</v>
       </c>
       <c r="G81" s="3">
-        <v>909200</v>
+        <v>1118800</v>
       </c>
       <c r="H81" s="3">
-        <v>865000</v>
+        <v>927800</v>
       </c>
       <c r="I81" s="3">
-        <v>418900</v>
+        <v>882700</v>
       </c>
       <c r="J81" s="3">
+        <v>427500</v>
+      </c>
+      <c r="K81" s="3">
         <v>823800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>608400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-413000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-711600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-398900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>114100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>503500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3386100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1114100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2423600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>169200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>559600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>94300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>94500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1118200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-697800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>420000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-317400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>218800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-134900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>150500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-73700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>34800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-250600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-134000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-1563300</v>
+        <v>7153000</v>
       </c>
       <c r="E89" s="3">
-        <v>2709700</v>
+        <v>-1595200</v>
       </c>
       <c r="F89" s="3">
-        <v>2073000</v>
+        <v>2765000</v>
       </c>
       <c r="G89" s="3">
-        <v>6426000</v>
+        <v>2115300</v>
       </c>
       <c r="H89" s="3">
-        <v>-2985200</v>
+        <v>6557100</v>
       </c>
       <c r="I89" s="3">
-        <v>2554000</v>
+        <v>-3046200</v>
       </c>
       <c r="J89" s="3">
+        <v>2606200</v>
+      </c>
+      <c r="K89" s="3">
         <v>1264300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4680400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-481200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>891700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2053700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4149200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1045200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>725700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1806000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3922400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-243300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>194300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3085000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>507700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>875500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>309700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2355000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-541300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>200500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>52300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2767300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>650300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-433900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1047900</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8022,8 +8243,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>3925700</v>
+        <v>-5431500</v>
       </c>
       <c r="E94" s="3">
-        <v>-8714000</v>
+        <v>4005800</v>
       </c>
       <c r="F94" s="3">
-        <v>2067400</v>
+        <v>-8891900</v>
       </c>
       <c r="G94" s="3">
-        <v>-3886000</v>
+        <v>2109600</v>
       </c>
       <c r="H94" s="3">
-        <v>2306200</v>
+        <v>-3965300</v>
       </c>
       <c r="I94" s="3">
-        <v>-2474200</v>
+        <v>2353200</v>
       </c>
       <c r="J94" s="3">
+        <v>-2524700</v>
+      </c>
+      <c r="K94" s="3">
         <v>-1347600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4299300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>629900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2588300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4230000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2595800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1062300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1907800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1844800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3446700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1293100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>377600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-873100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3212700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-168500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-317800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-364300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2919400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-135000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>624600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-620100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-4568600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-980900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2206600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-3057800</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1028600</v>
+        <v>-1264400</v>
       </c>
       <c r="E100" s="3">
-        <v>-102900</v>
+        <v>-1049600</v>
       </c>
       <c r="F100" s="3">
-        <v>-619800</v>
+        <v>-105000</v>
       </c>
       <c r="G100" s="3">
-        <v>-253100</v>
+        <v>-632400</v>
       </c>
       <c r="H100" s="3">
-        <v>173400</v>
+        <v>-258300</v>
       </c>
       <c r="I100" s="3">
-        <v>-585100</v>
+        <v>176900</v>
       </c>
       <c r="J100" s="3">
+        <v>-597100</v>
+      </c>
+      <c r="K100" s="3">
         <v>556600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1572200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1752900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-472100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>864000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2505200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-82400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>3259000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>606800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>4193100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2380000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>475500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>383300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-68600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-390500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-569400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-419200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>692900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1909300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-564100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-229500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>2462600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1161900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1772300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>415900</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-18000</v>
+        <v>-16500</v>
       </c>
       <c r="E101" s="3">
-        <v>-29400</v>
+        <v>-18300</v>
       </c>
       <c r="F101" s="3">
-        <v>-105400</v>
+        <v>-30000</v>
       </c>
       <c r="G101" s="3">
-        <v>252400</v>
+        <v>-107600</v>
       </c>
       <c r="H101" s="3">
-        <v>-100300</v>
+        <v>257600</v>
       </c>
       <c r="I101" s="3">
-        <v>-134800</v>
+        <v>-102400</v>
       </c>
       <c r="J101" s="3">
+        <v>-137600</v>
+      </c>
+      <c r="K101" s="3">
         <v>248400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>434700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-63400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-197900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>44100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-138900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>82900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-413700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-392000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-8800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>96100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-60200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>123900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>63500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-64700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-19000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>150400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>171000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-65200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-31600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-44300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-13900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-5300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>42400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1315800</v>
+        <v>440600</v>
       </c>
       <c r="E102" s="3">
-        <v>-6136700</v>
+        <v>1342700</v>
       </c>
       <c r="F102" s="3">
-        <v>3415200</v>
+        <v>-6261900</v>
       </c>
       <c r="G102" s="3">
-        <v>2539200</v>
+        <v>3484900</v>
       </c>
       <c r="H102" s="3">
-        <v>-606000</v>
+        <v>2591100</v>
       </c>
       <c r="I102" s="3">
-        <v>-640100</v>
+        <v>-618300</v>
       </c>
       <c r="J102" s="3">
+        <v>-653200</v>
+      </c>
+      <c r="K102" s="3">
         <v>721700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-756400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1838300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2366600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1268100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3919700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2107000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1663300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>176100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>4659800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>939800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>793500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-171600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-132900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-115900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-30700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-323400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>299400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1167700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>605200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1085000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>515000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>825900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-736300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1679300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
   <si>
     <t>JD</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>41081100</v>
+        <v>37121200</v>
       </c>
       <c r="E8" s="3">
-        <v>36661700</v>
+        <v>40099200</v>
       </c>
       <c r="F8" s="3">
-        <v>43150700</v>
+        <v>36015400</v>
       </c>
       <c r="G8" s="3">
-        <v>34920500</v>
+        <v>43164800</v>
       </c>
       <c r="H8" s="3">
-        <v>40592500</v>
+        <v>33947000</v>
       </c>
       <c r="I8" s="3">
-        <v>34251900</v>
+        <v>39702000</v>
       </c>
       <c r="J8" s="3">
+        <v>35368900</v>
+      </c>
+      <c r="K8" s="3">
         <v>41652000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>33646800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>37201800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>33091600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>38014500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>31089400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>36450800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>28282100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>31226500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>25672200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>29627300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>23065300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>26281900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>20763100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>22959900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>18498800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>19581700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>14663400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>17546300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>14366400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>16349600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>12428800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>13832100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>10939000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>11548800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>8751100</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>34604800</v>
+        <v>33020500</v>
       </c>
       <c r="E9" s="3">
-        <v>31054900</v>
+        <v>36147500</v>
       </c>
       <c r="F9" s="3">
-        <v>37017800</v>
+        <v>32835000</v>
       </c>
       <c r="G9" s="3">
-        <v>29457300</v>
+        <v>39467200</v>
       </c>
       <c r="H9" s="3">
-        <v>34751300</v>
+        <v>30722800</v>
       </c>
       <c r="I9" s="3">
-        <v>29174100</v>
+        <v>36288800</v>
       </c>
       <c r="J9" s="3">
+        <v>32363200</v>
+      </c>
+      <c r="K9" s="3">
         <v>35796100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>28646000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>32211800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>28473300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>32899800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>26669600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>31893800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>24228300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>26891500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>21723700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>25407600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>19510100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>22586700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>17665900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>19579600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>15720700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>16797400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>12408700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>15176900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>12334900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>14218500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>10502000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>11955000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>18670800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>19852900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>14923400</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>6476300</v>
+        <v>4100800</v>
       </c>
       <c r="E10" s="3">
-        <v>5606800</v>
+        <v>3951800</v>
       </c>
       <c r="F10" s="3">
-        <v>6132900</v>
+        <v>3180400</v>
       </c>
       <c r="G10" s="3">
-        <v>5463100</v>
+        <v>3697600</v>
       </c>
       <c r="H10" s="3">
-        <v>5841200</v>
+        <v>3224200</v>
       </c>
       <c r="I10" s="3">
-        <v>5077800</v>
+        <v>3413300</v>
       </c>
       <c r="J10" s="3">
+        <v>3005700</v>
+      </c>
+      <c r="K10" s="3">
         <v>5855900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5000800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4990000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4618200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5114600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4419800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4557000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4053800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4335000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3948500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4219700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3555200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3695200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3097200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3380300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2778100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2784300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2254700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2369400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2031400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2131100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1926800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1877100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>-7731900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>-8304100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>-6172300</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,109 +1152,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>584900</v>
+        <v>626700</v>
       </c>
       <c r="E12" s="3">
-        <v>559400</v>
+        <v>580300</v>
       </c>
       <c r="F12" s="3">
-        <v>602700</v>
+        <v>558700</v>
       </c>
       <c r="G12" s="3">
-        <v>525600</v>
+        <v>612200</v>
       </c>
       <c r="H12" s="3">
-        <v>562400</v>
+        <v>520000</v>
       </c>
       <c r="I12" s="3">
-        <v>577500</v>
+        <v>561500</v>
       </c>
       <c r="J12" s="3">
+        <v>609400</v>
+      </c>
+      <c r="K12" s="3">
         <v>602800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>557200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>551500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>600100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>562000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>565400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>526700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>627000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>623400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>601500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>527400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>616900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>549200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>548200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>565400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>564000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>505400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>478900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>395500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>342700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>302600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>257500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>226400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>184500</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>168700</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>175700</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1341,210 +1358,219 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-29300</v>
+        <v>-58300</v>
       </c>
       <c r="E14" s="3">
-        <v>-3100</v>
+        <v>-42900</v>
       </c>
       <c r="F14" s="3">
-        <v>610700</v>
+        <v>10700</v>
       </c>
       <c r="G14" s="3">
-        <v>-700</v>
+        <v>1104900</v>
       </c>
       <c r="H14" s="3">
-        <v>-146300</v>
+        <v>106600</v>
       </c>
       <c r="I14" s="3">
-        <v>-69500</v>
+        <v>-75800</v>
       </c>
       <c r="J14" s="3">
+        <v>-198000</v>
+      </c>
+      <c r="K14" s="3">
         <v>-11700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-173500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-4300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>490000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-2500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-82300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-12500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-11500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-154400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-50700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-28800</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>-598200</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>10</v>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>3100</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>10</v>
+      <c r="AF14" s="3">
+        <v>0</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="3" t="s">
+      <c r="AH14" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>60500</v>
+        <v>284800</v>
       </c>
       <c r="E15" s="3">
-        <v>59200</v>
+        <v>266100</v>
       </c>
       <c r="F15" s="3">
-        <v>59500</v>
+        <v>307000</v>
       </c>
       <c r="G15" s="3">
-        <v>59400</v>
+        <v>444100</v>
       </c>
       <c r="H15" s="3">
-        <v>61700</v>
+        <v>245600</v>
       </c>
       <c r="I15" s="3">
-        <v>62900</v>
+        <v>238100</v>
       </c>
       <c r="J15" s="3">
+        <v>285300</v>
+      </c>
+      <c r="K15" s="3">
         <v>61900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>61200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>58100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>54100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>51900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>53400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>53300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>50600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>51900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>50300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>43800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>44500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>72600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>22500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>22600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>67800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>65800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>63900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>64600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>64000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>66700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>66300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>65700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>63900</v>
-      </c>
-      <c r="AH15" s="3">
-        <v>65100</v>
       </c>
       <c r="AI15" s="3">
         <v>65100</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>65100</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>39571400</v>
+        <v>35404200</v>
       </c>
       <c r="E17" s="3">
-        <v>35573100</v>
+        <v>38654200</v>
       </c>
       <c r="F17" s="3">
-        <v>42860500</v>
+        <v>34949000</v>
       </c>
       <c r="G17" s="3">
-        <v>33608200</v>
+        <v>42263500</v>
       </c>
       <c r="H17" s="3">
-        <v>39422500</v>
+        <v>32672100</v>
       </c>
       <c r="I17" s="3">
-        <v>33342900</v>
+        <v>38700800</v>
       </c>
       <c r="J17" s="3">
+        <v>34502000</v>
+      </c>
+      <c r="K17" s="3">
         <v>40980800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>32437200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>36675000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>33249000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>38068500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>30723700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>36407600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>28051100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>31143700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>25026300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>28884000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>22699300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>26200400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>19997300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>22613600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>18311500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>19718100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>14754400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>17694700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>14365700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>16586500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>12354200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>13891900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>10842800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>11598000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>8785200</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1509800</v>
+        <v>1717000</v>
       </c>
       <c r="E18" s="3">
-        <v>1088600</v>
+        <v>1445000</v>
       </c>
       <c r="F18" s="3">
-        <v>290300</v>
+        <v>1066400</v>
       </c>
       <c r="G18" s="3">
-        <v>1312200</v>
+        <v>901300</v>
       </c>
       <c r="H18" s="3">
-        <v>1170000</v>
+        <v>1275000</v>
       </c>
       <c r="I18" s="3">
-        <v>909000</v>
+        <v>1001200</v>
       </c>
       <c r="J18" s="3">
+        <v>866900</v>
+      </c>
+      <c r="K18" s="3">
         <v>671200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1209600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>526700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-157400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-54000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>365700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>43200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>231000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>82800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>645900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>743300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>366100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>81500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>765800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>346300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>187200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-136400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-91100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-148400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-236900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>74600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-59800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>96200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-49200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-34100</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,513 +1849,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>788800</v>
+        <v>-494800</v>
       </c>
       <c r="E20" s="3">
-        <v>274100</v>
+        <v>-755600</v>
       </c>
       <c r="F20" s="3">
-        <v>306500</v>
+        <v>75600</v>
       </c>
       <c r="G20" s="3">
-        <v>310700</v>
+        <v>549900</v>
       </c>
       <c r="H20" s="3">
-        <v>294500</v>
+        <v>-409400</v>
       </c>
       <c r="I20" s="3">
-        <v>274900</v>
+        <v>-355300</v>
       </c>
       <c r="J20" s="3">
+        <v>140900</v>
+      </c>
+      <c r="K20" s="3">
         <v>-34800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-64400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>271200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-197500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-591600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-698300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>140600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>378600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3292200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>617500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1840500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-115100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>573300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-562800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-172200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>990200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-542100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>534700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-120500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>265800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>95700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>120500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>42100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-15000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-113100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-26100</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2303200</v>
+        <v>2496700</v>
       </c>
       <c r="E21" s="3">
-        <v>1675300</v>
+        <v>2466800</v>
       </c>
       <c r="F21" s="3">
-        <v>606100</v>
+        <v>1297800</v>
       </c>
       <c r="G21" s="3">
-        <v>1629600</v>
+        <v>795500</v>
       </c>
       <c r="H21" s="3">
-        <v>1477800</v>
+        <v>1929900</v>
       </c>
       <c r="I21" s="3">
-        <v>1460300</v>
+        <v>1594700</v>
       </c>
       <c r="J21" s="3">
+        <v>1011300</v>
+      </c>
+      <c r="K21" s="3">
         <v>652900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1166500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>803700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-124000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-641300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-321900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>153900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>841900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3397100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1272200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2592000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>472700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>658500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>207000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>126300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1433100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-660600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>476100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-259600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>437800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-31900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>117300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-15000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>219700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-158100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-50000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>97000</v>
+        <v>97100</v>
       </c>
       <c r="E22" s="3">
-        <v>84700</v>
+        <v>94700</v>
       </c>
       <c r="F22" s="3">
+        <v>83200</v>
+      </c>
+      <c r="G22" s="3">
         <v>130700</v>
       </c>
-      <c r="G22" s="3">
-        <v>100100</v>
-      </c>
       <c r="H22" s="3">
-        <v>92200</v>
+        <v>97300</v>
       </c>
       <c r="I22" s="3">
-        <v>83200</v>
+        <v>90200</v>
       </c>
       <c r="J22" s="3">
+        <v>85900</v>
+      </c>
+      <c r="K22" s="3">
         <v>98400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>80000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>67300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>47600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>61500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>39300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>33400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>35900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>41200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>43900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>47800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>32700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>33800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>25100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>23700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>28600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>21000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>33700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>34400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>32800</v>
       </c>
-      <c r="AD22" s="3" t="s">
+      <c r="AE22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>42000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>30900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>27600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>9200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>10400</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2201500</v>
+        <v>2173100</v>
       </c>
       <c r="E23" s="3">
-        <v>1278000</v>
+        <v>2148900</v>
       </c>
       <c r="F23" s="3">
-        <v>466100</v>
+        <v>1255500</v>
       </c>
       <c r="G23" s="3">
-        <v>1522900</v>
+        <v>466200</v>
       </c>
       <c r="H23" s="3">
-        <v>1372300</v>
+        <v>1480400</v>
       </c>
       <c r="I23" s="3">
-        <v>1100800</v>
+        <v>1342200</v>
       </c>
       <c r="J23" s="3">
+        <v>1136700</v>
+      </c>
+      <c r="K23" s="3">
         <v>538000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1065200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>730700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-402500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-707200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-371900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>150400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>573800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3333800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1219500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2536000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>218300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>621000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>177900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>150400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1148800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-699500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>409900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-303300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>233600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-141200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>153100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-48600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>53600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-171500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-70600</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>285100</v>
+        <v>343000</v>
       </c>
       <c r="E24" s="3">
-        <v>239700</v>
+        <v>278200</v>
       </c>
       <c r="F24" s="3">
-        <v>196500</v>
+        <v>235400</v>
       </c>
       <c r="G24" s="3">
-        <v>363600</v>
+        <v>196600</v>
       </c>
       <c r="H24" s="3">
-        <v>396300</v>
+        <v>353500</v>
       </c>
       <c r="I24" s="3">
-        <v>226800</v>
+        <v>387600</v>
       </c>
       <c r="J24" s="3">
+        <v>234200</v>
+      </c>
+      <c r="K24" s="3">
         <v>83900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>241900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>170600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>83300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>25600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>92700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>81800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>66700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-46200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>101700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>117400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>51500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>73800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>93100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>67000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>42700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>8900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>7200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>23400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>21700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>7900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-2400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>13000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>14600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1916500</v>
+        <v>1830100</v>
       </c>
       <c r="E26" s="3">
-        <v>1038300</v>
+        <v>1870700</v>
       </c>
       <c r="F26" s="3">
+        <v>1020000</v>
+      </c>
+      <c r="G26" s="3">
         <v>269600</v>
       </c>
-      <c r="G26" s="3">
-        <v>1159300</v>
-      </c>
       <c r="H26" s="3">
-        <v>976000</v>
+        <v>1127000</v>
       </c>
       <c r="I26" s="3">
-        <v>873900</v>
+        <v>954600</v>
       </c>
       <c r="J26" s="3">
+        <v>902400</v>
+      </c>
+      <c r="K26" s="3">
         <v>454100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>823300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>560100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-485800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-732800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-464600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>68600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>507000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3380000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1117800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2418600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>166800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>547200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>84800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>83400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1106100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-708400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>402600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-326700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>212000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-143100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>145200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-46200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>40500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-186100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-70900</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1782600</v>
+        <v>1672400</v>
       </c>
       <c r="E27" s="3">
-        <v>1005200</v>
+        <v>1739900</v>
       </c>
       <c r="F27" s="3">
-        <v>477800</v>
+        <v>987500</v>
       </c>
       <c r="G27" s="3">
-        <v>1118800</v>
+        <v>477900</v>
       </c>
       <c r="H27" s="3">
-        <v>927800</v>
+        <v>1087600</v>
       </c>
       <c r="I27" s="3">
-        <v>882700</v>
+        <v>907400</v>
       </c>
       <c r="J27" s="3">
+        <v>911500</v>
+      </c>
+      <c r="K27" s="3">
         <v>427500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>823800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>608400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-413000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-711600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-398900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>114100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>503500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3386100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1114100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2423600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>169200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>559600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>94300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>94500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1118200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-697800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>420000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-317400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>218800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-134900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>150500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-42600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>43500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-183400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-68000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2815,19 +2876,22 @@
         <v>0</v>
       </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-31100</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-8700</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-67100</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-66100</v>
       </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-788800</v>
+        <v>494800</v>
       </c>
       <c r="E32" s="3">
-        <v>-274100</v>
+        <v>755600</v>
       </c>
       <c r="F32" s="3">
-        <v>-306500</v>
+        <v>-75600</v>
       </c>
       <c r="G32" s="3">
-        <v>-310700</v>
+        <v>-549900</v>
       </c>
       <c r="H32" s="3">
-        <v>-294500</v>
+        <v>409400</v>
       </c>
       <c r="I32" s="3">
-        <v>-274900</v>
+        <v>355300</v>
       </c>
       <c r="J32" s="3">
+        <v>-140900</v>
+      </c>
+      <c r="K32" s="3">
         <v>34800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>64400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-271200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>197500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>591600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>698300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-140600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-378600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3292200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-617500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1840500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>115100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-573300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>562800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>172200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-990200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>542100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-534700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>120500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-265800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-95700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-120500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-42100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>15000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>113100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1782600</v>
+        <v>1672400</v>
       </c>
       <c r="E33" s="3">
-        <v>1005200</v>
+        <v>1739900</v>
       </c>
       <c r="F33" s="3">
-        <v>477800</v>
+        <v>987500</v>
       </c>
       <c r="G33" s="3">
-        <v>1118800</v>
+        <v>477900</v>
       </c>
       <c r="H33" s="3">
-        <v>927800</v>
+        <v>1087600</v>
       </c>
       <c r="I33" s="3">
-        <v>882700</v>
+        <v>907400</v>
       </c>
       <c r="J33" s="3">
+        <v>911500</v>
+      </c>
+      <c r="K33" s="3">
         <v>427500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>823800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>608400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-413000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-711600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-398900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>114100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>503500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3386100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1114100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2423600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>169200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>559600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>94300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>94500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1118200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-697800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>420000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-317400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>218800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-134900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>150500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-73700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>34800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-250600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-134000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1782600</v>
+        <v>1672400</v>
       </c>
       <c r="E35" s="3">
-        <v>1005200</v>
+        <v>1739900</v>
       </c>
       <c r="F35" s="3">
-        <v>477800</v>
+        <v>987500</v>
       </c>
       <c r="G35" s="3">
-        <v>1118800</v>
+        <v>477900</v>
       </c>
       <c r="H35" s="3">
-        <v>927800</v>
+        <v>1087600</v>
       </c>
       <c r="I35" s="3">
-        <v>882700</v>
+        <v>907400</v>
       </c>
       <c r="J35" s="3">
+        <v>911500</v>
+      </c>
+      <c r="K35" s="3">
         <v>427500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>823800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>608400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-413000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-711600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-398900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>114100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>503500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3386100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1114100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2423600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>169200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>559600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>94300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>94500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1118200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-697800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>420000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-317400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>218800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-134900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>150500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-73700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>34800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-250600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-134000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,917 +3698,945 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>11912200</v>
+        <v>14126700</v>
       </c>
       <c r="E41" s="3">
-        <v>11507600</v>
+        <v>11627500</v>
       </c>
       <c r="F41" s="3">
-        <v>10135300</v>
+        <v>11304800</v>
       </c>
       <c r="G41" s="3">
-        <v>16349600</v>
+        <v>10138600</v>
       </c>
       <c r="H41" s="3">
-        <v>12832000</v>
+        <v>15893800</v>
       </c>
       <c r="I41" s="3">
-        <v>10485100</v>
+        <v>12550500</v>
       </c>
       <c r="J41" s="3">
+        <v>10827000</v>
+      </c>
+      <c r="K41" s="3">
         <v>11117800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11516500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>10957700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11662700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9750300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>12508900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>13981000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9940000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11983000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10773900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10546800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6867200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5692900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4946600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5007900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5202700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4975900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4758300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5055400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5051100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3812400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3207200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4134000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3435700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2263900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3611700</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>16551900</v>
+        <v>13087300</v>
       </c>
       <c r="E42" s="3">
-        <v>12740500</v>
+        <v>16156300</v>
       </c>
       <c r="F42" s="3">
-        <v>16671400</v>
+        <v>12515900</v>
       </c>
       <c r="G42" s="3">
-        <v>17817300</v>
+        <v>16676900</v>
       </c>
       <c r="H42" s="3">
-        <v>20315400</v>
+        <v>17320700</v>
       </c>
       <c r="I42" s="3">
-        <v>17261600</v>
+        <v>19869700</v>
       </c>
       <c r="J42" s="3">
+        <v>17824500</v>
+      </c>
+      <c r="K42" s="3">
         <v>19891600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>17746500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>16991400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>13268900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>15784600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>14548600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>10836500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>8835100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>8432300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>7132600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>7180900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>4632500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>3788300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>3767300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>3752600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>644900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>295600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>723900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1829700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1713700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1274500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>2383300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1890700</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>3089800</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>2623300</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1793200</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3544000</v>
+        <v>3262500</v>
       </c>
       <c r="E43" s="3">
-        <v>2887700</v>
+        <v>3459200</v>
       </c>
       <c r="F43" s="3">
-        <v>3160200</v>
+        <v>2984600</v>
       </c>
       <c r="G43" s="3">
-        <v>3572000</v>
+        <v>3402500</v>
       </c>
       <c r="H43" s="3">
-        <v>3436800</v>
+        <v>3472400</v>
       </c>
       <c r="I43" s="3">
-        <v>2950700</v>
+        <v>3361400</v>
       </c>
       <c r="J43" s="3">
+        <v>3046900</v>
+      </c>
+      <c r="K43" s="3">
         <v>3766700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3346500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2713700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2280400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2397400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2461700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3709000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2365400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2013200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2079900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1986200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1702600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1844100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2499900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2102900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1622800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2463500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2348300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3701700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2819300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4850500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>5597400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>6769800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>5409200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>4288500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>4025000</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>9959400</v>
+        <v>10390300</v>
       </c>
       <c r="E44" s="3">
-        <v>9585800</v>
+        <v>9721300</v>
       </c>
       <c r="F44" s="3">
-        <v>9594800</v>
+        <v>9416800</v>
       </c>
       <c r="G44" s="3">
-        <v>9112700</v>
+        <v>9597900</v>
       </c>
       <c r="H44" s="3">
-        <v>8961000</v>
+        <v>8858600</v>
       </c>
       <c r="I44" s="3">
-        <v>8923900</v>
+        <v>8764400</v>
       </c>
       <c r="J44" s="3">
+        <v>9214900</v>
+      </c>
+      <c r="K44" s="3">
         <v>10989300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>9913900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>10569600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>9498500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>10416300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8535300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>9445600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>8285800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>8203400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>8155700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>8027700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>7980200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>8920400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>7431900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>6954700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5841700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>6394500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5578100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>6227400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5188800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>6188800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5388800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4622900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3906300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4204300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>3287100</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3456400</v>
+        <v>2648700</v>
       </c>
       <c r="E45" s="3">
-        <v>3326800</v>
+        <v>2335000</v>
       </c>
       <c r="F45" s="3">
-        <v>3833200</v>
+        <v>2110400</v>
       </c>
       <c r="G45" s="3">
-        <v>3564000</v>
+        <v>2534700</v>
       </c>
       <c r="H45" s="3">
-        <v>3682800</v>
+        <v>2382300</v>
       </c>
       <c r="I45" s="3">
-        <v>3393800</v>
+        <v>2481100</v>
       </c>
       <c r="J45" s="3">
+        <v>2573200</v>
+      </c>
+      <c r="K45" s="3">
         <v>3729100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3676900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3808900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3226200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2940200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2998600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3046100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2252800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2052400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2445100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2537400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1621900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1172100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1310600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1654700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1212300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1098700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1921800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2095000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1439700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>945200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1774000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2015800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1285200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3842100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>840300</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>45423900</v>
+        <v>44351300</v>
       </c>
       <c r="E46" s="3">
-        <v>40048500</v>
+        <v>44338200</v>
       </c>
       <c r="F46" s="3">
-        <v>43395100</v>
+        <v>39342400</v>
       </c>
       <c r="G46" s="3">
-        <v>50415600</v>
+        <v>43409200</v>
       </c>
       <c r="H46" s="3">
-        <v>49228000</v>
+        <v>49010200</v>
       </c>
       <c r="I46" s="3">
-        <v>43015100</v>
+        <v>48148000</v>
       </c>
       <c r="J46" s="3">
+        <v>44417800</v>
+      </c>
+      <c r="K46" s="3">
         <v>49494400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>46200300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>45041200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>39936700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>41288800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>41053100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>41018200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>31679100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>32684300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>30587100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>30279000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>22804500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>21417800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>19956300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>19472800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>14524500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>15228200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>15330400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>18909200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>16212600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>17071400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>18350700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>19433200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>17126200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>15551100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>13557200</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>20015100</v>
+        <v>20297000</v>
       </c>
       <c r="E47" s="3">
-        <v>19091700</v>
+        <v>19536700</v>
       </c>
       <c r="F47" s="3">
-        <v>19396900</v>
+        <v>18755100</v>
       </c>
       <c r="G47" s="3">
-        <v>8837500</v>
+        <v>19403200</v>
       </c>
       <c r="H47" s="3">
-        <v>9113900</v>
+        <v>8591100</v>
       </c>
       <c r="I47" s="3">
-        <v>9529800</v>
+        <v>8914000</v>
       </c>
       <c r="J47" s="3">
+        <v>9840600</v>
+      </c>
+      <c r="K47" s="3">
         <v>9763100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>10218500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>10205600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>9930000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>11340700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>12655200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>13323000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>13426300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>13584000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>11753100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>10996100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>9079600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>8775800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>8358600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>8423900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>8106100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>6863300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>7013800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>5555200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>4438500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>4241400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2881600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2652400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>3265500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>3299200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>3258900</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>15094200</v>
+        <v>16188600</v>
       </c>
       <c r="E48" s="3">
-        <v>14416500</v>
+        <v>14733400</v>
       </c>
       <c r="F48" s="3">
-        <v>14213300</v>
+        <v>14162300</v>
       </c>
       <c r="G48" s="3">
-        <v>13981400</v>
+        <v>14217900</v>
       </c>
       <c r="H48" s="3">
-        <v>12986400</v>
+        <v>13591700</v>
       </c>
       <c r="I48" s="3">
-        <v>12559100</v>
+        <v>12701500</v>
       </c>
       <c r="J48" s="3">
+        <v>12968600</v>
+      </c>
+      <c r="K48" s="3">
         <v>12477900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>11626200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10116500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9642700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8094300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7452400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7186400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6362600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6401400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6278600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5475000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5079500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5405300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5221700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4807300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4842500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4013700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3446300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2997300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2456000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2340500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1904000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1599700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1382600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1311100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1280900</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>9424700</v>
+        <v>9469000</v>
       </c>
       <c r="E49" s="3">
-        <v>9199200</v>
+        <v>9199400</v>
       </c>
       <c r="F49" s="3">
-        <v>9372100</v>
+        <v>9037000</v>
       </c>
       <c r="G49" s="3">
-        <v>9763400</v>
+        <v>9375100</v>
       </c>
       <c r="H49" s="3">
-        <v>9772200</v>
+        <v>9491300</v>
       </c>
       <c r="I49" s="3">
-        <v>9284900</v>
+        <v>9557800</v>
       </c>
       <c r="J49" s="3">
+        <v>9587700</v>
+      </c>
+      <c r="K49" s="3">
         <v>9320200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9128900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7500300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7423000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4491400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4519900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4465800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4137700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3966100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4229400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3622600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3318700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3333000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3303300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3256200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3246200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3214100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3076700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2868200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2862900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3026700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3021300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2440200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2475700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2513800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2566700</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1909900</v>
+        <v>1205100</v>
       </c>
       <c r="E52" s="3">
-        <v>2089000</v>
+        <v>1645000</v>
       </c>
       <c r="F52" s="3">
-        <v>2293200</v>
+        <v>1797400</v>
       </c>
       <c r="G52" s="3">
-        <v>4042200</v>
+        <v>2012600</v>
       </c>
       <c r="H52" s="3">
-        <v>4040800</v>
+        <v>3719400</v>
       </c>
       <c r="I52" s="3">
-        <v>3296100</v>
+        <v>3744500</v>
       </c>
       <c r="J52" s="3">
+        <v>3191100</v>
+      </c>
+      <c r="K52" s="3">
         <v>2862700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2898300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4113300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3790000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3193600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2984600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2388700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2162100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2146600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2308600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1568800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1633700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1060400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1013300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1545900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2025800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1057800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1019700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1040600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>618800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>635500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>620000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>687900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>580500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1665500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>308700</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>91867600</v>
+        <v>91747000</v>
       </c>
       <c r="E54" s="3">
-        <v>84844900</v>
+        <v>89671800</v>
       </c>
       <c r="F54" s="3">
-        <v>88670500</v>
+        <v>83349100</v>
       </c>
       <c r="G54" s="3">
-        <v>87040100</v>
+        <v>88699300</v>
       </c>
       <c r="H54" s="3">
-        <v>85141200</v>
+        <v>84613800</v>
       </c>
       <c r="I54" s="3">
-        <v>77685100</v>
+        <v>83273400</v>
       </c>
       <c r="J54" s="3">
+        <v>80218400</v>
+      </c>
+      <c r="K54" s="3">
         <v>83918300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>80072100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>76976900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>70722500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>68408700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>68665100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>68382000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>57767800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>58782500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>55156900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>51941500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>41916200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>39992300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>37853200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>37506100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>32745200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>30377000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>29887000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>31370400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>26588900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>27315600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>26777600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>26813400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>24830500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>23323100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>20972500</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,614 +5230,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>25762800</v>
+        <v>23243400</v>
       </c>
       <c r="E57" s="3">
-        <v>20801200</v>
+        <v>25147000</v>
       </c>
       <c r="F57" s="3">
-        <v>23654600</v>
+        <v>16393700</v>
       </c>
       <c r="G57" s="3">
-        <v>21671700</v>
+        <v>18762200</v>
       </c>
       <c r="H57" s="3">
-        <v>21455900</v>
+        <v>21045800</v>
       </c>
       <c r="I57" s="3">
-        <v>17156000</v>
+        <v>20960400</v>
       </c>
       <c r="J57" s="3">
+        <v>17677700</v>
+      </c>
+      <c r="K57" s="3">
         <v>22711200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>20845600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>22277500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>17322400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>19427400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>18034400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>18431300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>13566400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>14950600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>15570300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>14940700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>12266000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>13973100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>13355500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>14326200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>10927000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>11647500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>10957000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>12582100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>8938300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>11032500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>10032000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>10014300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>6362200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>6695000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>6031800</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>789600</v>
+        <v>2474700</v>
       </c>
       <c r="E58" s="3">
-        <v>742500</v>
+        <v>1850000</v>
       </c>
       <c r="F58" s="3">
-        <v>709700</v>
+        <v>1817900</v>
       </c>
       <c r="G58" s="3">
-        <v>1937100</v>
+        <v>1803600</v>
       </c>
       <c r="H58" s="3">
-        <v>2530700</v>
+        <v>2992800</v>
       </c>
       <c r="I58" s="3">
-        <v>2013200</v>
+        <v>3570700</v>
       </c>
       <c r="J58" s="3">
+        <v>3238200</v>
+      </c>
+      <c r="K58" s="3">
         <v>1712300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2486300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1912100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2368200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>601800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>999000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>80800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>598900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>453800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>934600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1815600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1357000</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
       <c r="W58" s="3">
         <v>0</v>
       </c>
       <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
         <v>21000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>285600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>660100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1340300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1701400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1939000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1912200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1825900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1807800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2944100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1615600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1993900</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>12953900</v>
+        <v>6204000</v>
       </c>
       <c r="E59" s="3">
-        <v>13151300</v>
+        <v>5787600</v>
       </c>
       <c r="F59" s="3">
-        <v>13087000</v>
+        <v>5333000</v>
       </c>
       <c r="G59" s="3">
-        <v>13389700</v>
+        <v>9546600</v>
       </c>
       <c r="H59" s="3">
-        <v>12625600</v>
+        <v>6126800</v>
       </c>
       <c r="I59" s="3">
-        <v>12435800</v>
+        <v>5773100</v>
       </c>
       <c r="J59" s="3">
+        <v>5261700</v>
+      </c>
+      <c r="K59" s="3">
         <v>13156300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12082900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11328000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10549700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10507800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9989200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9769000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8417900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8818700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>8928800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>8582000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>7926600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7586700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>7088800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>7054300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>6348400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5245200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4735000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4852800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4456200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4604900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4511800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4433200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>6832000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>6921700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4873400</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>39506400</v>
+        <v>37857700</v>
       </c>
       <c r="E60" s="3">
-        <v>34695000</v>
+        <v>38562100</v>
       </c>
       <c r="F60" s="3">
-        <v>37451300</v>
+        <v>34083400</v>
       </c>
       <c r="G60" s="3">
-        <v>36998500</v>
+        <v>37463500</v>
       </c>
       <c r="H60" s="3">
-        <v>36612200</v>
+        <v>35967200</v>
       </c>
       <c r="I60" s="3">
-        <v>31605000</v>
+        <v>35809100</v>
       </c>
       <c r="J60" s="3">
+        <v>32635700</v>
+      </c>
+      <c r="K60" s="3">
         <v>37579800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>35414800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>35517700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>30240300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>30537000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>29022600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>28281100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>22583300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>24223100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>25433700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>25338300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>21549600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>21559800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>20444300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>21401500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>17561000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>17552800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>17032300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>19136300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>15333500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>17549600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>16369700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>16255400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>16138300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>15232400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>12899100</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8005000</v>
+        <v>10070400</v>
       </c>
       <c r="E61" s="3">
-        <v>6004200</v>
+        <v>10010600</v>
       </c>
       <c r="F61" s="3">
-        <v>5916400</v>
+        <v>7873800</v>
       </c>
       <c r="G61" s="3">
-        <v>4615800</v>
+        <v>7847000</v>
       </c>
       <c r="H61" s="3">
-        <v>4520400</v>
+        <v>6581300</v>
       </c>
       <c r="I61" s="3">
-        <v>4135800</v>
+        <v>6486900</v>
       </c>
       <c r="J61" s="3">
+        <v>6380500</v>
+      </c>
+      <c r="K61" s="3">
         <v>4262200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3953200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3428100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2155300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1293200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1775800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1782600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1757100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1744300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1943300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2002600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2702700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1547800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1568600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1512300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1480700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1434100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1384800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1408600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1036900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1621000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2315500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2602100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1957100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1330600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1488500</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3761100</v>
+        <v>129600</v>
       </c>
       <c r="E62" s="3">
-        <v>3548600</v>
+        <v>124400</v>
       </c>
       <c r="F62" s="3">
-        <v>3519100</v>
+        <v>135600</v>
       </c>
       <c r="G62" s="3">
-        <v>3655600</v>
+        <v>148800</v>
       </c>
       <c r="H62" s="3">
-        <v>3506500</v>
+        <v>204600</v>
       </c>
       <c r="I62" s="3">
-        <v>3315000</v>
+        <v>220200</v>
       </c>
       <c r="J62" s="3">
+        <v>244000</v>
+      </c>
+      <c r="K62" s="3">
         <v>3430500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3244000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3008100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3001200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2576600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2450600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2498700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1952600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1965700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1980600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1611900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1376100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1390500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1409600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1145200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>914000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>232400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>255700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>295100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>326300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>370000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>400900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>438400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>471400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>765600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>430900</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>60744300</v>
+        <v>49442400</v>
       </c>
       <c r="E66" s="3">
-        <v>53493700</v>
+        <v>50046900</v>
       </c>
       <c r="F66" s="3">
-        <v>55983200</v>
+        <v>43467800</v>
       </c>
       <c r="G66" s="3">
-        <v>54601400</v>
+        <v>46902100</v>
       </c>
       <c r="H66" s="3">
-        <v>53873800</v>
+        <v>44008000</v>
       </c>
       <c r="I66" s="3">
-        <v>47866900</v>
+        <v>43659800</v>
       </c>
       <c r="J66" s="3">
+        <v>40329400</v>
+      </c>
+      <c r="K66" s="3">
         <v>53838000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>50759700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>48990000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>42210400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>39625000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>38058200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>37251100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>31504700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>32676400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>32970600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>31849600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>28618600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>27388100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>26166900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>26836400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>22565900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>21696500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>20936000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>23011700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>18812300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>19592200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>19135000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>19340200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>19650900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>18394100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>15844000</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,8 +6722,11 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6563,10 +6737,10 @@
         <v>10</v>
       </c>
       <c r="F72" s="3">
-        <v>7071600</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>10</v>
+        <v>6789600</v>
+      </c>
+      <c r="G72" s="3">
+        <v>7073900</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>10</v>
@@ -6574,11 +6748,11 @@
       <c r="I72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K72" s="3">
         <v>4620900</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>10</v>
@@ -6586,11 +6760,11 @@
       <c r="M72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O72" s="3">
         <v>4876200</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="P72" s="3" t="s">
         <v>10</v>
@@ -6598,23 +6772,23 @@
       <c r="Q72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R72" s="3">
+      <c r="R72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S72" s="3">
         <v>5422100</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V72" s="3">
         <v>-1479900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-1609600</v>
-      </c>
-      <c r="W72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="X72" s="3" t="s">
         <v>10</v>
@@ -6622,11 +6796,11 @@
       <c r="Y72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="Z72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA72" s="3">
         <v>-3287700</v>
-      </c>
-      <c r="AA72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AB72" s="3" t="s">
         <v>10</v>
@@ -6634,26 +6808,29 @@
       <c r="AC72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AD72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE72" s="3">
         <v>-3205500</v>
-      </c>
-      <c r="AE72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AF72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH72" s="3">
         <v>-3104800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-3159800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-2968300</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>31123300</v>
+        <v>32591200</v>
       </c>
       <c r="E76" s="3">
-        <v>31351100</v>
+        <v>30379400</v>
       </c>
       <c r="F76" s="3">
-        <v>32687300</v>
+        <v>30798400</v>
       </c>
       <c r="G76" s="3">
-        <v>32438700</v>
+        <v>32698000</v>
       </c>
       <c r="H76" s="3">
-        <v>31267400</v>
+        <v>31534400</v>
       </c>
       <c r="I76" s="3">
-        <v>29818100</v>
+        <v>30581500</v>
       </c>
       <c r="J76" s="3">
+        <v>30790500</v>
+      </c>
+      <c r="K76" s="3">
         <v>30080300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>29312400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>27987000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>28512100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>28783800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>30606900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>31130900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>26263200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>26106000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>22186300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>20091900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13297600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>12604200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>11686300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>10669800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>10179200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>8680500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>8951000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8358800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7776600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7723400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7642600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>7473100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5179500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4929000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5128500</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1782600</v>
+        <v>1672400</v>
       </c>
       <c r="E81" s="3">
-        <v>1005200</v>
+        <v>1739900</v>
       </c>
       <c r="F81" s="3">
-        <v>477800</v>
+        <v>987500</v>
       </c>
       <c r="G81" s="3">
-        <v>1118800</v>
+        <v>477900</v>
       </c>
       <c r="H81" s="3">
-        <v>927800</v>
+        <v>1087600</v>
       </c>
       <c r="I81" s="3">
-        <v>882700</v>
+        <v>907400</v>
       </c>
       <c r="J81" s="3">
+        <v>911500</v>
+      </c>
+      <c r="K81" s="3">
         <v>427500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>823800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>608400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-413000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-711600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-398900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>114100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>503500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3386100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1114100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2423600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>169200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>559600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>94300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>94500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1118200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-697800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>420000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-317400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>218800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-134900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>150500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-73700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>34800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-250600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-134000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,31 +7599,32 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>187900</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>177700</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>236400</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>415100</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>153800</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>149900</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>201900</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -7502,8 +7701,11 @@
       <c r="AI83" s="3">
         <v>0</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>7153000</v>
+        <v>-886600</v>
       </c>
       <c r="E89" s="3">
-        <v>-1595200</v>
+        <v>6982100</v>
       </c>
       <c r="F89" s="3">
-        <v>2765000</v>
+        <v>-1567100</v>
       </c>
       <c r="G89" s="3">
-        <v>2115300</v>
+        <v>2765900</v>
       </c>
       <c r="H89" s="3">
-        <v>6557100</v>
+        <v>2056300</v>
       </c>
       <c r="I89" s="3">
-        <v>-3046200</v>
+        <v>6413300</v>
       </c>
       <c r="J89" s="3">
+        <v>-3145500</v>
+      </c>
+      <c r="K89" s="3">
         <v>2606200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1264300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4680400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-481200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>891700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2053700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4149200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1045200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>725700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1806000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3922400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-243300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>194300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>3085000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>507700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>875500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>309700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2355000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-541300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>200500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>52300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2767300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>650300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-433900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1047900</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,31 +8365,32 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-763800</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-457000</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-451900</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-1225000</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>-684300</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
+        <v>-497400</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-423200</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -8246,8 +8467,11 @@
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-5431500</v>
+        <v>3097200</v>
       </c>
       <c r="E94" s="3">
-        <v>4005800</v>
+        <v>-5301700</v>
       </c>
       <c r="F94" s="3">
-        <v>-8891900</v>
+        <v>3935200</v>
       </c>
       <c r="G94" s="3">
-        <v>2109600</v>
+        <v>-8894800</v>
       </c>
       <c r="H94" s="3">
-        <v>-3965300</v>
+        <v>2050800</v>
       </c>
       <c r="I94" s="3">
-        <v>2353200</v>
+        <v>-3878400</v>
       </c>
       <c r="J94" s="3">
+        <v>2430000</v>
+      </c>
+      <c r="K94" s="3">
         <v>-2524700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1347600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4299300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>629900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2588300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4230000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2595800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1062300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1907800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1844800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3446700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1293100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>377600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-873100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3212700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-168500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-317800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-364300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2919400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-135000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>624600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-620100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-4568600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-980900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2206600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-3057800</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,31 +8819,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+        <v>950700</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,307 +9233,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1264400</v>
+        <v>-257500</v>
       </c>
       <c r="E100" s="3">
-        <v>-1049600</v>
+        <v>-1234200</v>
       </c>
       <c r="F100" s="3">
-        <v>-105000</v>
+        <v>-1031100</v>
       </c>
       <c r="G100" s="3">
-        <v>-632400</v>
+        <v>-105100</v>
       </c>
       <c r="H100" s="3">
-        <v>-258300</v>
+        <v>-614800</v>
       </c>
       <c r="I100" s="3">
-        <v>176900</v>
+        <v>-252600</v>
       </c>
       <c r="J100" s="3">
+        <v>182700</v>
+      </c>
+      <c r="K100" s="3">
         <v>-597100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>556600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1572200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1752900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-472100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>864000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2505200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-82400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>3259000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>606800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>4193100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2380000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>475500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>383300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-68600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-390500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-569400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-419200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>692900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1909300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-564100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-229500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>2462600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1161900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>1772300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>415900</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-16500</v>
+        <v>-104600</v>
       </c>
       <c r="E101" s="3">
-        <v>-18300</v>
+        <v>251900</v>
       </c>
       <c r="F101" s="3">
-        <v>-30000</v>
+        <v>-105700</v>
       </c>
       <c r="G101" s="3">
-        <v>-107600</v>
+        <v>-141500</v>
       </c>
       <c r="H101" s="3">
-        <v>257600</v>
+        <v>252900</v>
       </c>
       <c r="I101" s="3">
-        <v>-102400</v>
+        <v>466600</v>
       </c>
       <c r="J101" s="3">
+        <v>-72400</v>
+      </c>
+      <c r="K101" s="3">
         <v>-137600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>248400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>434700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-63400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-197900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>44100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-138900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>82900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-413700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-392000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-8800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>96100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-60200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>123900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>63500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-64700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-19000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>150400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>171000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-65200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-31600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-44300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-13900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-5300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>42400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>440600</v>
+        <v>1840300</v>
       </c>
       <c r="E102" s="3">
-        <v>1342700</v>
+        <v>430400</v>
       </c>
       <c r="F102" s="3">
-        <v>-6261900</v>
+        <v>1319000</v>
       </c>
       <c r="G102" s="3">
-        <v>3484900</v>
+        <v>-6263900</v>
       </c>
       <c r="H102" s="3">
-        <v>2591100</v>
+        <v>3387700</v>
       </c>
       <c r="I102" s="3">
-        <v>-618300</v>
+        <v>2534200</v>
       </c>
       <c r="J102" s="3">
+        <v>-638500</v>
+      </c>
+      <c r="K102" s="3">
         <v>-653200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>721700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-756400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1838300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2366600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1268100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3919700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2107000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1663300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>176100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>4659800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>939800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>793500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-171600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-132900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-115900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-30700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-323400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>299400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1167700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>605200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1085000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>515000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>825900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-736300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1679300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
   <si>
     <t>JD</t>
   </si>
@@ -656,467 +656,479 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>47538200</v>
+      </c>
+      <c r="E8" s="3">
         <v>37121200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>40099200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>36015400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>43164800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>33947000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>39702000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>35368900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>41652000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>33646800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>37201800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>33091600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>38014500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>31089400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>36450800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>28282100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>31226500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>25672200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>29627300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>23065300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>26281900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>20763100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>22959900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>18498800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>19581700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>14663400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>17546300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>14366400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>16349600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>12428800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>13832100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>10939000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>11548800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>8751100</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>43017600</v>
+      </c>
+      <c r="E9" s="3">
         <v>33020500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>36147500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>32835000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>39467200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>30722800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>36288800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>32363200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>35796100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>28646000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>32211800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>28473300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>32899800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>26669600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>31893800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>24228300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>26891500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>21723700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>25407600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>19510100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>22586700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>17665900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>19579600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>15720700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>16797400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>12408700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>15176900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>12334900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>14218500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>10502000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>11955000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>18670800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>19852900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>14923400</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4520600</v>
+      </c>
+      <c r="E10" s="3">
         <v>4100800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3951800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3180400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3697600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3224200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3413300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3005700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5855900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5000800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4990000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4618200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5114600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4419800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4557000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4053800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4335000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3948500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>4219700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3555200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3695200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3097200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3380300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2778100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2784300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2254700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2369400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2031400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2131100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1926800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1877100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>-7731900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>-8304100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>-6172300</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,112 +1165,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>600600</v>
+      </c>
+      <c r="E12" s="3">
         <v>626700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>580300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>558700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>612200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>520000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>561500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>609400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>602800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>557200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>551500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>600100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>562000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>565400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>526700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>627000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>623400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>601500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>527400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>616900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>549200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>548200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>565400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>564000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>505400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>478900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>395500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>342700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>302600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>257500</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>226400</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>184500</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>168700</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>175700</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1361,216 +1377,225 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-48100</v>
+      </c>
+      <c r="E14" s="3">
         <v>-58300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-42900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>10700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1104900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>106600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-75800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-198000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-11700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-173500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-4300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>490000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-2500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-82300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-12500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-11500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-154400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-50700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-28800</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>-598200</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>10</v>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>3100</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>10</v>
+      <c r="AG14" s="3">
+        <v>0</v>
       </c>
       <c r="AH14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ14" s="3" t="s">
+      <c r="AI14" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>273700</v>
+      </c>
+      <c r="E15" s="3">
         <v>284800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>266100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>307000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>444100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>245600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>238100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>285300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>61900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>61200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>58100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>54100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>51900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>53400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>53300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>50600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>51900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>50300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>43800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>44500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>72600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>22500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>22600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>67800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>65800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>63900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>64600</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>64000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>66700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>66300</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>65700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>63900</v>
-      </c>
-      <c r="AI15" s="3">
-        <v>65100</v>
       </c>
       <c r="AJ15" s="3">
         <v>65100</v>
       </c>
+      <c r="AK15" s="3">
+        <v>65100</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1629,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>46260600</v>
+      </c>
+      <c r="E17" s="3">
         <v>35404200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>38654200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>34949000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>42263500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>32672100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>38700800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>34502000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>40980800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>32437200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>36675000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>33249000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>38068500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>30723700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>36407600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>28051100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>31143700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>25026300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>28884000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>22699300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>26200400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>19997300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>22613600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>18311500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>19718100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>14754400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>17694700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>14365700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>16586500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>12354200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>13891900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>10842800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>11598000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>8785200</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1277600</v>
+      </c>
+      <c r="E18" s="3">
         <v>1717000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1445000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1066400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>901300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1275000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1001200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>866900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>671200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1209600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>526700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-157400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-54000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>365700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>43200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>231000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>82800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>645900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>743300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>366100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>81500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>765800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>346300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>187200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-136400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-91100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-148400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-236900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>74600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-59800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>96200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-49200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-34100</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,528 +1882,544 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-392400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-494800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-755600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>75600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>549900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-409400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-355300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>140900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-34800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-64400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>271200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-197500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-591600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-698300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>140600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>378600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>3292200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>617500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1840500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-115100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>573300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-562800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-172200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>990200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-542100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>534700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-120500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>265800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>95700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>120500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>42100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-15000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-113100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-26100</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1943700</v>
+      </c>
+      <c r="E21" s="3">
         <v>2496700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2466800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1297800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>795500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1929900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1594700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1011300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>652900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1166500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>803700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-124000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-641300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-321900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>153900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>841900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3397100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1272200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2592000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>472700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>658500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>207000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>126300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1433100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-660600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>476100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-259600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>437800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-31900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>117300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-15000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>219700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-158100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-50000</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>126900</v>
+      </c>
+      <c r="E22" s="3">
         <v>97100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>94700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>83200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>130700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>97300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>90200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>85900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>98400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>80000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>67300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>47600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>61500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>39300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>33400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>35900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>41200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>43900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>47800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>32700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>33800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>25100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>23700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>28600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>21000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>33700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>34400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>32800</v>
       </c>
-      <c r="AE22" s="3" t="s">
+      <c r="AF22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>42000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>30900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>27600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>9200</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>10400</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1591200</v>
+      </c>
+      <c r="E23" s="3">
         <v>2173100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2148900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1255500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>466200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1480400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1342200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1136700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>538000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1065200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>730700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-402500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-707200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-371900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>150400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>573800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3333800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1219500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2536000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>218300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>621000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>177900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>150400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1148800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-699500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>409900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-303300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>233600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-141200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>153100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-48600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>53600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-171500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-70600</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>102800</v>
+      </c>
+      <c r="E24" s="3">
         <v>343000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>278200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>235400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>196600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>353500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>387600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>234200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>83900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>241900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>170600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>83300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>25600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>92700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>81800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>66700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-46200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>101700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>117400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>51500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>73800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>93100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>67000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>42700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>8900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>7200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>23400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>21700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>7900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-2400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>13000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>14600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2522,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1488400</v>
+      </c>
+      <c r="E26" s="3">
         <v>1830100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1870700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1020000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>269600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1127000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>954600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>902400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>454100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>823300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>560100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-485800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-732800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-464600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>68600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>507000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3380000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1117800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2418600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>166800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>547200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>84800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>83400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1106100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-708400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>402600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-326700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>212000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-143100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>145200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-46200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>40500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-186100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-70900</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1350000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1672400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1739900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>987500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>477900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1087600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>907400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>911500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>427500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>823800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>608400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-413000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-711600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-398900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>114100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>503500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3386100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1114100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2423600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>169200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>559600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>94300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>94500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1118200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-697800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>420000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-317400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>218800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-134900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>150500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-42600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>43500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-183400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-68000</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2879,19 +2939,22 @@
         <v>0</v>
       </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-31100</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-8700</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-67100</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-66100</v>
       </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,216 +3164,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>392400</v>
+      </c>
+      <c r="E32" s="3">
         <v>494800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>755600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-75600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-549900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>409400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>355300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-140900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>34800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>64400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-271200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>197500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>591600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>698300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-140600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-378600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-3292200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-617500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1840500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>115100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-573300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>562800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>172200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-990200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>542100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-534700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>120500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-265800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-95700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-120500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-42100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>15000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>113100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1350000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1672400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1739900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>987500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>477900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1087600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>907400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>911500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>427500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>823800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>608400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-413000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-711600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-398900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>114100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>503500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3386100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1114100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2423600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>169200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>559600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>94300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>94500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1118200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-697800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>420000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-317400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>218800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-134900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>150500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-73700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>34800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-250600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-134000</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3485,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1350000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1672400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1739900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>987500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>477900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1087600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>907400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>911500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>427500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>823800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>608400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-413000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-711600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-398900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>114100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>503500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3386100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1114100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2423600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>169200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>559600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>94300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>94500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1118200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-697800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>420000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-317400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>218800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-134900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>150500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-73700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>34800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-250600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-134000</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,944 +3784,972 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>14844300</v>
+      </c>
+      <c r="E41" s="3">
         <v>14126700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11627500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>11304800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10138600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>15893800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>12550500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10827000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11117800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11516500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>10957700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11662700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9750300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>12508900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>13981000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9940000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>11983000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10773900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10546800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6867200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5692900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4946600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5007900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5202700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4975900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4758300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5055400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5051100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3812400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3207200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4134000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3435700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2263900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3611700</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>17213800</v>
+      </c>
+      <c r="E42" s="3">
         <v>13087300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>16156300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>12515900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>16676900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>17320700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>19869700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>17824500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>19891600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>17746500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>16991400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>13268900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>15784600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>14548600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>10836500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>8835100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>8432300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>7132600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>7180900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>4632500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>3788300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>3767300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>3752600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>644900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>295600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>723900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1829700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1713700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1274500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>2383300</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1890700</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>3089800</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>2623300</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1793200</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4165000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3262500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3459200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2984600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3402500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3472400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3361400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3046900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3766700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3346500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2713700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2280400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2397400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2461700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3709000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2365400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2013200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2079900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1986200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1702600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1844100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2499900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2102900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1622800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2463500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2348300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3701700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2819300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4850500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5597400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>6769800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>5409200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>4288500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>4025000</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>12237900</v>
+      </c>
+      <c r="E44" s="3">
         <v>10390300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>9721300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>9416800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>9597900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>8858600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>8764400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>9214900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>10989300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>9913900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>10569600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>9498500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>10416300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>8535300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>9445600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>8285800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>8203400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>8155700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>8027700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>7980200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>8920400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>7431900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>6954700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5841700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>6394500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5578100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>6227400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5188800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>6188800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5388800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4622900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3906300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4204300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>3287100</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3508700</v>
+      </c>
+      <c r="E45" s="3">
         <v>2648700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2335000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2110400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2534700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2382300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2481100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2573200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3729100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3676900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3808900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3226200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2940200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2998600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3046100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2252800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2052400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2445100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2537400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1621900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1172100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1310600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1654700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1212300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1098700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1921800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2095000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1439700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>945200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1774000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2015800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1285200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>3842100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>840300</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>52978900</v>
+      </c>
+      <c r="E46" s="3">
         <v>44351300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>44338200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>39342400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>43409200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>49010200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>48148000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>44417800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>49494400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>46200300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>45041200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>39936700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>41288800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>41053100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>41018200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>31679100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>32684300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>30587100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>30279000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>22804500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>21417800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>19956300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>19472800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>14524500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>15228200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>15330400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>18909200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>16212600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>17071400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>18350700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>19433200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>17126200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>15551100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>13557200</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>15922500</v>
+      </c>
+      <c r="E47" s="3">
         <v>20297000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>19536700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>18755100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>19403200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>8591100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8914000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>9840600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9763100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>10218500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>10205600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>9930000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>11340700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>12655200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>13323000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>13426300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>13584000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>11753100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>10996100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>9079600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>8775800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>8358600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>8423900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>8106100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>6863300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>7013800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>5555200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>4438500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>4241400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2881600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2652400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>3265500</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>3299200</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>3258900</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15540700</v>
+      </c>
+      <c r="E48" s="3">
         <v>16188600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>14733400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>14162300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>14217900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>13591700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>12701500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>12968600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>12477900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>11626200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10116500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9642700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8094300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7452400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7186400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6362600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6401400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6278600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5475000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5079500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5405300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5221700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4807300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4842500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4013700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3446300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2997300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2456000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2340500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1904000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1599700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1382600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1311100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1280900</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9636100</v>
+      </c>
+      <c r="E49" s="3">
         <v>9469000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9199400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9037000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9375100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9491300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9557800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9587700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9320200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9128900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7500300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7423000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4491400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4519900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4465800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4137700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3966100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4229400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3622600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3318700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3333000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3303300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3256200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3246200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3214100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3076700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2868200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2862900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3026700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3021300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2440200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2475700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2513800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2566700</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +4959,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1245200</v>
+      </c>
+      <c r="E52" s="3">
         <v>1205100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1645000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1797400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2012600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3719400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3744500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3191100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2862700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2898300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4113300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3790000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3193600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2984600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2388700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2162100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2146600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2308600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1568800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1633700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1060400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1013300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1545900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2025800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1057800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1019700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1040600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>618800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>635500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>620000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>687900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>580500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1665500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>308700</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>95660300</v>
+      </c>
+      <c r="E54" s="3">
         <v>91747000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>89671800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>83349100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>88699300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>84613800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>83273400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>80218400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>83918300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>80072100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>76976900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>70722500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>68408700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>68665100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>68382000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>57767800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>58782500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>55156900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>51941500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>41916200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>39992300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>37853200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>37506100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>32745200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>30377000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>29887000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>31370400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>26588900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>27315600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>26777600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>26813400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>24830500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>23323100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>20972500</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,632 +5360,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>26609700</v>
+      </c>
+      <c r="E57" s="3">
         <v>23243400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>25147000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>16393700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>18762200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>21045800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>20960400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>17677700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>22711200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>20845600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>22277500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>17322400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>19427400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>18034400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>18431300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>13566400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>14950600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>15570300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>14940700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>12266000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>13973100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>13355500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>14326200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>10927000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>11647500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>10957000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>12582100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>8938300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>11032500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>10032000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>10014300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>6362200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>6695000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>6031800</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2080700</v>
+      </c>
+      <c r="E58" s="3">
         <v>2474700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1850000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1817900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1803600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2992800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3570700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3238200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1712300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2486300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1912100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2368200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>601800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>999000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>80800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>598900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>453800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>934600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1815600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1357000</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
       <c r="X58" s="3">
         <v>0</v>
       </c>
       <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
         <v>21000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>285600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>660100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1340300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1701400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1939000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1912200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1825900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1807800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2944100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1615600</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1993900</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6044900</v>
+      </c>
+      <c r="E59" s="3">
         <v>6204000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5787600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5333000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9546600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6126800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5773100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5261700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13156300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12082900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11328000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10549700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10507800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9989200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9769000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8417900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>8818700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>8928800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8582000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7926600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>7586700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>7088800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>7054300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>6348400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>5245200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4735000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4852800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4456200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4604900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4511800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4433200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>6832000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>6921700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>4873400</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>41035300</v>
+      </c>
+      <c r="E60" s="3">
         <v>37857700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>38562100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>34083400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>37463500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>35967200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>35809100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>32635700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>37579800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>35414800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>35517700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>30240300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>30537000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>29022600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>28281100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>22583300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>24223100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>25433700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>25338300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>21549600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>21559800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>20444300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>21401500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>17561000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>17552800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>17032300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>19136300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>15333500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>17549600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>16369700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>16255400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>16138300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>15232400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>12899100</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10217800</v>
+      </c>
+      <c r="E61" s="3">
         <v>10070400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10010600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7873800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7847000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6581300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6486900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6380500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4262200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3953200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3428100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2155300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1293200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1775800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1782600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1757100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1744300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1943300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2002600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2702700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1547800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1568600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1512300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1480700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1434100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1384800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1408600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1036900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1621000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2315500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2602100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1957100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1330600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1488500</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>114400</v>
+      </c>
+      <c r="E62" s="3">
         <v>129600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>124400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>135600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>148800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>204600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>220200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>244000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3430500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3244000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3008100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3001200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2576600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2450600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2498700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1952600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1965700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1980600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1611900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1376100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1390500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1409600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1145200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>914000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>232400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>255700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>295100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>326300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>370000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>400900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>438400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>471400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>765600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>430900</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>52737600</v>
+      </c>
+      <c r="E66" s="3">
         <v>49442400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>50046900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>43467800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>46902100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>44008000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>43659800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>40329400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>53838000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>50759700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>48990000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>42210400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>39625000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>38058200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>37251100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>31504700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>32676400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>32970600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>31849600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>28618600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>27388100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>26166900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>26836400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>22565900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>21696500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>20936000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>23011700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>18812300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>19592200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>19135000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>19340200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>19650900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>18394100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>15844000</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,8 +6895,11 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6736,14 +6909,14 @@
       <c r="E72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F72" s="3">
+      <c r="F72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G72" s="3">
         <v>6789600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7073900</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>10</v>
@@ -6751,11 +6924,11 @@
       <c r="J72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L72" s="3">
         <v>4620900</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>10</v>
@@ -6763,11 +6936,11 @@
       <c r="N72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P72" s="3">
         <v>4876200</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>10</v>
@@ -6775,23 +6948,23 @@
       <c r="R72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T72" s="3">
         <v>5422100</v>
-      </c>
-      <c r="T72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V72" s="3">
+      <c r="V72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="W72" s="3">
         <v>-1479900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-1609600</v>
-      </c>
-      <c r="X72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Y72" s="3" t="s">
         <v>10</v>
@@ -6799,11 +6972,11 @@
       <c r="Z72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB72" s="3">
         <v>-3287700</v>
-      </c>
-      <c r="AB72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AC72" s="3" t="s">
         <v>10</v>
@@ -6811,26 +6984,29 @@
       <c r="AD72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF72" s="3">
         <v>-3205500</v>
-      </c>
-      <c r="AF72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AG72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AH72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI72" s="3">
         <v>-3104800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-3159800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-2968300</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>32791300</v>
+      </c>
+      <c r="E76" s="3">
         <v>32591200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>30379400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>30798400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>32698000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>31534400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>30581500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>30790500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>30080300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>29312400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>27987000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>28512100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>28783800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>30606900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>31130900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>26263200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>26106000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>22186300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>20091900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13297600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>12604200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>11686300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>10669800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>10179200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>8680500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8951000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>8358800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7776600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7723400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>7642600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>7473100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5179500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>4929000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>5128500</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7537,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1350000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1672400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1739900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>987500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>477900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1087600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>907400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>911500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>427500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>823800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>608400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-413000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-711600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-398900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>114100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>503500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3386100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1114100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2423600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>169200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>559600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>94300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>94500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1118200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-697800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>420000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-317400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>218800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-134900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>150500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-73700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>34800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-250600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-134000</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,35 +7797,36 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>444100</v>
+      </c>
+      <c r="E83" s="3">
         <v>187900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>177700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>236400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>415100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>153800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>149900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>201900</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
@@ -7704,8 +7902,11 @@
       <c r="AJ83" s="3">
         <v>0</v>
       </c>
+      <c r="AK83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E89" s="3">
         <v>-886600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6982100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1567100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2765900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2056300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6413300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3145500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2606200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1264300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4680400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-481200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>891700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2053700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4149200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1045200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>725700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1806000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3922400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-243300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>194300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3085000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>507700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>875500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>309700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2355000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-541300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>200500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>52300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2767300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>650300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-433900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1047900</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,35 +8585,36 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E91" s="3">
         <v>-763800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-457000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-451900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1225000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-684300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-497400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-423200</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
@@ -8470,8 +8690,11 @@
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8904,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E94" s="3">
         <v>3097200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5301700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>3935200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-8894800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>2050800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3878400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>2430000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2524700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1347600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4299300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>629900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2588300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4230000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2595800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1062300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1907800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1844800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3446700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1293100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>377600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-873100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3212700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-168500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-317800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-364300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2919400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-135000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>624600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-620100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-4568600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-980900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-2206600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-3057800</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9052,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8834,11 +9067,11 @@
       <c r="F96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G96" s="3">
+      <c r="G96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H96" s="3">
         <v>950700</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>10</v>
@@ -8846,8 +9079,8 @@
       <c r="J96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8924,8 +9157,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,316 +9478,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E100" s="3">
         <v>-257500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1234200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1031100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-105100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-614800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-252600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>182700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-597100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>556600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1572200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1752900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-472100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>864000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2505200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-82400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>3259000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>606800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>4193100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2380000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>475500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>383300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-68600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-390500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-569400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-419200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>692900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1909300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-564100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-229500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>2462600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>1161900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>1772300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>415900</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-104600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>251900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-105700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-141500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>252900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>466600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-72400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-137600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>248400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>434700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-63400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-197900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>44100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-138900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>82900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-413700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-392000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-8800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>96100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-60200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>123900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>63500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-64700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-19000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>150400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>171000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-65200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-31600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-44300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-13900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-5300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>42400</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>1840300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>430400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1319000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-6263900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3387700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2534200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-638500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-653200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>721700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-756400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1838300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2366600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1268100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3919700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2107000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1663300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>176100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>4659800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>939800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>793500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-171600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-132900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-115900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-30700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-323400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>299400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1167700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>605200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1085000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>515000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>825900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-736300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1679300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
   <si>
     <t>JD</t>
   </si>
@@ -656,479 +656,492 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>41491400</v>
+      </c>
+      <c r="E8" s="3">
         <v>47538200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>37121200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>40099200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>36015400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>43164800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>33947000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>39702000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>35368900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>41652000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>33646800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>37201800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>33091600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>38014500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>31089400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>36450800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>28282100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>31226500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>25672200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>29627300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>23065300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>26281900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>20763100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>22959900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>18498800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>19581700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>14663400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>17546300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>14366400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>16349600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>12428800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>13832100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>10939000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>11548800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>8751100</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>37617400</v>
+      </c>
+      <c r="E9" s="3">
         <v>43017600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>33020500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>36147500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>32835000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>39467200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>30722800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>36288800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>32363200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>35796100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>28646000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>32211800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>28473300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>32899800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>26669600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>31893800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>24228300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>26891500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>21723700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>25407600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>19510100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>22586700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>17665900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>19579600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>15720700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>16797400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>12408700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>15176900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>12334900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>14218500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>10502000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>11955000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>18670800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>19852900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>14923400</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3873900</v>
+      </c>
+      <c r="E10" s="3">
         <v>4520600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4100800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3951800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3180400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3697600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3224200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3413300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3005700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5855900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5000800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4990000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4618200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5114600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4419800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4557000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4053800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4335000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3948500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>4219700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3555200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3695200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3097200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3380300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2778100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2784300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2254700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2369400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2031400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2131100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1926800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1877100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>-7731900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>-8304100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>-6172300</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,115 +1179,119 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>636800</v>
+      </c>
+      <c r="E12" s="3">
         <v>600600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>626700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>580300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>558700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>612200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>520000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>561500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>609400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>602800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>557200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>551500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>600100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>562000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>565400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>526700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>627000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>623400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>601500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>527400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>616900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>549200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>548200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>565400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>564000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>505400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>478900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>395500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>342700</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>302600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>257500</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>226400</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>184500</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>168700</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>175700</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1380,222 +1397,231 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-48100</v>
+        <v>117400</v>
       </c>
       <c r="E14" s="3">
+        <v>394200</v>
+      </c>
+      <c r="F14" s="3">
         <v>-58300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-42900</v>
       </c>
-      <c r="G14" s="3">
-        <v>10700</v>
-      </c>
       <c r="H14" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="I14" s="3">
         <v>1104900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>106600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-75800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-198000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-11700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-173500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-4300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>490000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-82300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-12500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-11500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-154400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-50700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-28800</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>-598200</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>10</v>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>3100</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
+      <c r="AF14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>10</v>
+      <c r="AH14" s="3">
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="3" t="s">
+      <c r="AJ14" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>273700</v>
+        <v>50200</v>
       </c>
       <c r="E15" s="3">
+        <v>419800</v>
+      </c>
+      <c r="F15" s="3">
         <v>284800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>266100</v>
       </c>
-      <c r="G15" s="3">
-        <v>307000</v>
-      </c>
       <c r="H15" s="3">
+        <v>58200</v>
+      </c>
+      <c r="I15" s="3">
         <v>444100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>245600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>238100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>285300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>61900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>61200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>58100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>54100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>51900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>53400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>53300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>50600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>51900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>50300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>43800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>44500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>72600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>22500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>22600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>67800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>65800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>63900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>64600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>64000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>66700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>66300</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>65700</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>63900</v>
-      </c>
-      <c r="AJ15" s="3">
-        <v>65100</v>
       </c>
       <c r="AK15" s="3">
         <v>65100</v>
       </c>
+      <c r="AL15" s="3">
+        <v>65100</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,222 +1656,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>40039800</v>
+      </c>
+      <c r="E17" s="3">
         <v>46260600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>35404200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>38654200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>34949000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>42263500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>32672100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>38700800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>34502000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>40980800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>32437200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>36675000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>33249000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>38068500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>30723700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>36407600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>28051100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>31143700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>25026300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>28884000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>22699300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>26200400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>19997300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>22613600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>18311500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>19718100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>14754400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>17694700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>14365700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>16586500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>12354200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>13891900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>10842800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>11598000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>8785200</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1451500</v>
+      </c>
+      <c r="E18" s="3">
         <v>1277600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1717000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1445000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1066400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>901300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1275000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1001200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>866900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>671200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1209600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>526700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-157400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-54000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>365700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>43200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>231000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>82800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>645900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>743300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>366100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>81500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>765800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>346300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>187200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-136400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-91100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-148400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-236900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>74600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-59800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>96200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-49200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-34100</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,543 +1916,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-392400</v>
+        <v>-587200</v>
       </c>
       <c r="E20" s="3">
+        <v>446800</v>
+      </c>
+      <c r="F20" s="3">
         <v>-494800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-755600</v>
       </c>
-      <c r="G20" s="3">
-        <v>75600</v>
-      </c>
       <c r="H20" s="3">
+        <v>-268100</v>
+      </c>
+      <c r="I20" s="3">
         <v>549900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-409400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-355300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>140900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-34800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-64400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>271200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-197500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-591600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-698300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>140600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>378600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>3292200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>617500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1840500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-115100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>573300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-562800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-172200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>990200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-542100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>534700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-120500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>265800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>95700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>120500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>42100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-15000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-113100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-26100</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1943700</v>
+        <v>2088900</v>
       </c>
       <c r="E21" s="3">
+        <v>1250600</v>
+      </c>
+      <c r="F21" s="3">
         <v>2496700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2466800</v>
       </c>
-      <c r="G21" s="3">
-        <v>1297800</v>
-      </c>
       <c r="H21" s="3">
+        <v>1392700</v>
+      </c>
+      <c r="I21" s="3">
         <v>795500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1929900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1594700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1011300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>652900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1166500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>803700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-124000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-641300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-321900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>153900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>841900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3397100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1272200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2592000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>472700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>658500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>207000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>126300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1433100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-660600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>476100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-259600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>437800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-31900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>117300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-15000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>219700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-158100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-50000</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>82700</v>
+      </c>
+      <c r="E22" s="3">
         <v>126900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>97100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>94700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>83200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>130700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>97300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>90200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>85900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>98400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>80000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>67300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>47600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>61500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>39300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>33400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>35900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>41200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>43900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>47800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>32700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>33800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>25100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>23700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>28600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>21000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>33700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>34400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>32800</v>
       </c>
-      <c r="AF22" s="3" t="s">
+      <c r="AG22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>42000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>30900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>27600</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>9200</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>10400</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1838600</v>
+      </c>
+      <c r="E23" s="3">
         <v>1591200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2173100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2148900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1255500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>466200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1480400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1342200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1136700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>538000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1065200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>730700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-402500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-707200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-371900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>150400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>573800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3333800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1219500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2536000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>218300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>621000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>177900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>150400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1148800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-699500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>409900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-303300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>233600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-141200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>153100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-48600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>53600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-171500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-70600</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>284300</v>
+      </c>
+      <c r="E24" s="3">
         <v>102800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>343000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>278200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>235400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>196600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>353500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>387600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>234200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>83900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>241900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>170600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>83300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>25600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>92700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>81800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>66700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-46200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>101700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>117400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>51500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>73800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>93100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>67000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>42700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>8900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>7200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>23400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>21700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>7900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-2400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>13000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>14600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1554300</v>
+      </c>
+      <c r="E26" s="3">
         <v>1488400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1830100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1870700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1020000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>269600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1127000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>954600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>902400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>454100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>823300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>560100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-485800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-732800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-464600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>68600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>507000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3380000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1117800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2418600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>166800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>547200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>84800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>83400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1106100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-708400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>402600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-326700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>212000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-143100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>145200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-46200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>40500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-186100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-70900</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1500700</v>
+      </c>
+      <c r="E27" s="3">
         <v>1350000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1672400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1739900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>987500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>477900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1087600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>907400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>911500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>427500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>823800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>608400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-413000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-711600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-398900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>114100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>503500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3386100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1114100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2423600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>169200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>559600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>94300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>94500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1118200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-697800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>420000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-317400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>218800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-134900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>150500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-42600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>43500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-183400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-68000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2942,19 +3003,22 @@
         <v>0</v>
       </c>
       <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
         <v>-31100</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-8700</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-67100</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-66100</v>
       </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,222 +3234,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>392400</v>
+        <v>587200</v>
       </c>
       <c r="E32" s="3">
+        <v>-446800</v>
+      </c>
+      <c r="F32" s="3">
         <v>494800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>755600</v>
       </c>
-      <c r="G32" s="3">
-        <v>-75600</v>
-      </c>
       <c r="H32" s="3">
+        <v>268100</v>
+      </c>
+      <c r="I32" s="3">
         <v>-549900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>409400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>355300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-140900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>34800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>64400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-271200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>197500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>591600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>698300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-140600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-378600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-3292200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-617500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1840500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>115100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-573300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>562800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>172200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-990200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>542100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-534700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>120500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-265800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-95700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-120500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-42100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>15000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>113100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1500700</v>
+      </c>
+      <c r="E33" s="3">
         <v>1350000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1672400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1739900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>987500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>477900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1087600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>907400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>911500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>427500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>823800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>608400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-413000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-711600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-398900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>114100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>503500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3386100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1114100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2423600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>169200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>559600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>94300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>94500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1118200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-697800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>420000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-317400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>218800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-134900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>150500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-73700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>34800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-250600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-134000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1500700</v>
+      </c>
+      <c r="E35" s="3">
         <v>1350000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1672400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1739900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>987500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>477900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1087600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>907400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>911500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>427500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>823800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>608400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-413000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-711600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-398900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>114100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>503500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3386100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1114100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2423600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>169200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>559600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>94300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>94500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1118200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-697800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>420000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-317400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>218800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-134900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>150500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-73700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>34800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-250600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-134000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,971 +3871,999 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>13336700</v>
+      </c>
+      <c r="E41" s="3">
         <v>14844300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>14126700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>11627500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11304800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>10138600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>15893800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>12550500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>10827000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11117800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11516500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10957700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11662700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9750300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>12508900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>13981000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9940000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>11983000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10773900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10546800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6867200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5692900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4946600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5007900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5202700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4975900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4758300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5055400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5051100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3812400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3207200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4134000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3435700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2263900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>3611700</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>13420400</v>
+      </c>
+      <c r="E42" s="3">
         <v>17213800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>13087300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>16156300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>12515900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>16676900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>17320700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>19869700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>17824500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>19891600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>17746500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>16991400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>13268900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>15784600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>14548600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>10836500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>8835100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>8432300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>7132600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>7180900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>4632500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>3788300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>3767300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>3752600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>644900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>295600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>723900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1829700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1713700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1274500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>2383300</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1890700</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>3089800</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>2623300</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1793200</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4165000</v>
+        <v>4785200</v>
       </c>
       <c r="E43" s="3">
+        <v>4340300</v>
+      </c>
+      <c r="F43" s="3">
         <v>3262500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3459200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2984600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3402500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3472400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3361400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3046900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3766700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3346500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2713700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2280400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2397400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2461700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3709000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2365400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2013200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2079900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1986200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1702600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1844100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2499900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2102900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1622800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2463500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2348300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3701700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2819300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>4850500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>5597400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>6769800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>5409200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>4288500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>4025000</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>13151500</v>
+      </c>
+      <c r="E44" s="3">
         <v>12237900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>10390300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>9721300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>9416800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>9597900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>8858600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>8764400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>9214900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>10989300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>9913900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>10569600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>9498500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>10416300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>8535300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>9445600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>8285800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>8203400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>8155700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>8027700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>7980200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>8920400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>7431900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>6954700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5841700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>6394500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5578100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>6227400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5188800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>6188800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>5388800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4622900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>3906300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>4204300</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>3287100</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3508700</v>
+        <v>3256400</v>
       </c>
       <c r="E45" s="3">
+        <v>3333400</v>
+      </c>
+      <c r="F45" s="3">
         <v>2648700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2335000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2110400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2534700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2382300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2481100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2573200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3729100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3676900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3808900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3226200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2940200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2998600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3046100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2252800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2052400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2445100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2537400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1621900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1172100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1310600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1654700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1212300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1098700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1921800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2095000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1439700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>945200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1774000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2015800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1285200</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>3842100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>840300</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>49229000</v>
+      </c>
+      <c r="E46" s="3">
         <v>52978900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>44351300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>44338200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>39342400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>43409200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>49010200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>48148000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>44417800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>49494400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>46200300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>45041200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>39936700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>41288800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>41053100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>41018200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>31679100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>32684300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>30587100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>30279000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>22804500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>21417800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>19956300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>19472800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>14524500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>15228200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>15330400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>18909200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>16212600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>17071400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>18350700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>19433200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>17126200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>15551100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>13557200</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>17073400</v>
+      </c>
+      <c r="E47" s="3">
         <v>15922500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>20297000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>19536700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>18755100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>19403200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8591100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>8914000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9840600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>9763100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>10218500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>10205600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>9930000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>11340700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>12655200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>13323000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>13426300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>13584000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>11753100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>10996100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>9079600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>8775800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>8358600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>8423900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>8106100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>6863300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>7013800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>5555200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>4438500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>4241400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2881600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2652400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>3265500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>3299200</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>3258900</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15946300</v>
+      </c>
+      <c r="E48" s="3">
         <v>15540700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>16188600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>14733400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>14162300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>14217900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13591700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>12701500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>12968600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>12477900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>11626200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10116500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9642700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8094300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7452400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7186400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6362600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6401400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6278600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5475000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5079500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5405300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5221700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4807300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4842500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4013700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3446300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2997300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2456000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2340500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1904000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1599700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1382600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1311100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1280900</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9651900</v>
+      </c>
+      <c r="E49" s="3">
         <v>9636100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9469000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9199400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9037000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9375100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9491300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9557800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9587700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9320200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9128900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7500300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7423000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4491400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4519900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4465800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4137700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3966100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4229400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3622600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3318700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3333000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3303300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3256200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3246200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3214100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3076700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2868200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2862900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3026700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3021300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2440200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2475700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2513800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2566700</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,115 +5079,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1245200</v>
+        <v>1179100</v>
       </c>
       <c r="E52" s="3">
+        <v>1194100</v>
+      </c>
+      <c r="F52" s="3">
         <v>1205100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1645000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1797400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2012600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3719400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3744500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3191100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2862700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2898300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4113300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3790000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3193600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2984600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2388700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2162100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2146600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2308600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1568800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1633700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1060400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1013300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1545900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2025800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1057800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1019700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1040600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>618800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>635500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>620000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>687900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>580500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1665500</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>308700</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>93414500</v>
+      </c>
+      <c r="E54" s="3">
         <v>95660300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>91747000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>89671800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>83349100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>88699300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>84613800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>83273400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>80218400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>83918300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>80072100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>76976900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>70722500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>68408700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>68665100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>68382000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>57767800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>58782500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>55156900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>51941500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>41916200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>39992300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>37853200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>37506100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>32745200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>30377000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>29887000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>31370400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>26588900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>27315600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>26777600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>26813400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>24830500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>23323100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>20972500</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,650 +5491,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>26609700</v>
+        <v>24762600</v>
       </c>
       <c r="E57" s="3">
+        <v>21716900</v>
+      </c>
+      <c r="F57" s="3">
         <v>23243400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>25147000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>16393700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>18762200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>21045800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>20960400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>17677700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>22711200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>20845600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>22277500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>17322400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>19427400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>18034400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>18431300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>13566400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>14950600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>15570300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>14940700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>12266000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>13973100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>13355500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>14326200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>10927000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>11647500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>10957000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>12582100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>8938300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>11032500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>10032000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>10014300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>6362200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>6695000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>6031800</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1658000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2080700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2474700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1850000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1817900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1803600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2992800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3570700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3238200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1712300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2486300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1912100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2368200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>601800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>999000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>80800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>598900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>453800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>934600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1815600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1357000</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
       <c r="Y58" s="3">
         <v>0</v>
       </c>
       <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
         <v>21000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>285600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>660100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1340300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1701400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1939000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1912200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1825900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1807800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>2944100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1615600</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1993900</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>6044900</v>
+        <v>5757900</v>
       </c>
       <c r="E59" s="3">
+        <v>9523900</v>
+      </c>
+      <c r="F59" s="3">
         <v>6204000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5787600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5333000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9546600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6126800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5773100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5261700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13156300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12082900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11328000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10549700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10507800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9989200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9769000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>8417900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>8818700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8928800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>8582000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>7926600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>7586700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>7088800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>7054300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>6348400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>5245200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4735000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4852800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4456200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4604900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4511800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4433200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>6832000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>6921700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>4873400</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>39155100</v>
+      </c>
+      <c r="E60" s="3">
         <v>41035300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>37857700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>38562100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>34083400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>37463500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>35967200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>35809100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>32635700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>37579800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>35414800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>35517700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>30240300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>30537000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>29022600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>28281100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>22583300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>24223100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>25433700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>25338300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>21549600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>21559800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>20444300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>21401500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>17561000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>17552800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>17032300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>19136300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>15333500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>17549600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>16369700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>16255400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>16138300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>15232400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>12899100</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10390800</v>
+      </c>
+      <c r="E61" s="3">
         <v>10217800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10070400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10010600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7873800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7847000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6581300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6486900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6380500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4262200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3953200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3428100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2155300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1293200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1775800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1782600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1757100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1744300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1943300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2002600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2702700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1547800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1568600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1512300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1480700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1434100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1384800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1408600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1036900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1621000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2315500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2602100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1957100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1330600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1488500</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>109800</v>
+      </c>
+      <c r="E62" s="3">
         <v>114400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>129600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>124400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>135600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>148800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>204600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>220200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>244000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3430500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3244000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3008100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3001200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2576600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2450600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2498700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1952600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1965700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1980600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1611900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1376100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1390500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1409600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1145200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>914000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>232400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>255700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>295100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>326300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>370000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>400900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>438400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>471400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>765600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>430900</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>50877300</v>
+      </c>
+      <c r="E66" s="3">
         <v>52737600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>49442400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>50046900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>43467800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>46902100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>44008000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>43659800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>40329400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>53838000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>50759700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>48990000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>42210400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>39625000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>38058200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>37251100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>31504700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>32676400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>32970600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>31849600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>28618600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>27388100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>26166900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>26836400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>22565900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>21696500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>20936000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>23011700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>18812300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>19592200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>19135000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>19340200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>19650900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>18394100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>15844000</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,28 +7069,31 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>10</v>
+      <c r="E72" s="3">
+        <v>11407000</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H72" s="3">
         <v>6789600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7073900</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>10</v>
@@ -6927,11 +7101,11 @@
       <c r="K72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M72" s="3">
         <v>4620900</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>10</v>
@@ -6939,11 +7113,11 @@
       <c r="O72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q72" s="3">
         <v>4876200</v>
-      </c>
-      <c r="Q72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="R72" s="3" t="s">
         <v>10</v>
@@ -6951,23 +7125,23 @@
       <c r="S72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T72" s="3">
+      <c r="T72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="U72" s="3">
         <v>5422100</v>
-      </c>
-      <c r="U72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="V72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W72" s="3">
+      <c r="W72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X72" s="3">
         <v>-1479900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-1609600</v>
-      </c>
-      <c r="Y72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Z72" s="3" t="s">
         <v>10</v>
@@ -6975,11 +7149,11 @@
       <c r="AA72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AB72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC72" s="3">
         <v>-3287700</v>
-      </c>
-      <c r="AC72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AD72" s="3" t="s">
         <v>10</v>
@@ -6987,26 +7161,29 @@
       <c r="AE72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AF72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG72" s="3">
         <v>-3205500</v>
-      </c>
-      <c r="AG72" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AH72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AI72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ72" s="3">
         <v>-3104800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-3159800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-2968300</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>32291300</v>
+      </c>
+      <c r="E76" s="3">
         <v>32791300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>32591200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>30379400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>30798400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>32698000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>31534400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>30581500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>30790500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>30080300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>29312400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>27987000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>28512100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>28783800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>30606900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>31130900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>26263200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>26106000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>22186300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>20091900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13297600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>12604200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>11686300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>10669800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>10179200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8680500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>8951000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>8358800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7776600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>7723400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>7642600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>7473100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5179500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>4929000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>5128500</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1500700</v>
+      </c>
+      <c r="E81" s="3">
         <v>1350000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1672400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1739900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>987500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>477900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1087600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>907400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>911500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>427500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>823800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>608400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-413000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-711600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-398900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>114100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>503500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3386100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1114100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2423600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>169200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>559600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>94300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>94500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1118200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-697800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>420000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-317400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>218800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-134900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>150500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-73700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>34800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-250600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-134000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,38 +7996,39 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>444100</v>
+      <c r="D83" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E83" s="3">
+        <v>317300</v>
+      </c>
+      <c r="F83" s="3">
         <v>187900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>177700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>236400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>415100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>153800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>149900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>201900</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
@@ -7905,8 +8104,11 @@
       <c r="AK83" s="3">
         <v>0</v>
       </c>
+      <c r="AL83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>10</v>
+      <c r="D89" s="3">
+        <v>-2516600</v>
       </c>
       <c r="E89" s="3">
+        <v>3410100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-886600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6982100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1567100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2765900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2056300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6413300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3145500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2606200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1264300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4680400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-481200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>891700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2053700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4149200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1045200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>725700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1806000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3922400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-243300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>194300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3085000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>507700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>875500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>309700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2355000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-541300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>200500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>52300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2767300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>650300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-433900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1047900</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,38 +8806,39 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>10</v>
+      <c r="D91" s="3">
+        <v>-320100</v>
       </c>
       <c r="E91" s="3">
+        <v>-815200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-763800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-457000</v>
       </c>
-      <c r="G91" s="3">
-        <v>-451900</v>
-      </c>
       <c r="H91" s="3">
-        <v>-1225000</v>
+        <v>-398900</v>
       </c>
       <c r="I91" s="3">
+        <v>-1225400</v>
+      </c>
+      <c r="J91" s="3">
         <v>-684300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-497400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-423200</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
@@ -8693,8 +8914,11 @@
       <c r="AK91" s="3">
         <v>0</v>
       </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,115 +9134,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>10</v>
+      <c r="D94" s="3">
+        <v>2237400</v>
       </c>
       <c r="E94" s="3">
+        <v>-1710200</v>
+      </c>
+      <c r="F94" s="3">
         <v>3097200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5301700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>3935200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8894800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>2050800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3878400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>2430000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2524700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1347600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4299300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>629900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2588300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4230000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2595800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1062300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1907800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1844800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3446700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1293100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>377600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-873100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3212700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-168500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-317800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-364300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2919400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-135000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>624600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-620100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-4568600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-980900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-2206600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-3057800</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,16 +9286,17 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>10</v>
+      <c r="E96" s="3">
+        <v>1132100</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>10</v>
@@ -9070,11 +9304,11 @@
       <c r="G96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I96" s="3">
         <v>950700</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="J96" s="3" t="s">
         <v>10</v>
@@ -9082,8 +9316,8 @@
       <c r="K96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9160,8 +9394,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,325 +9724,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>10</v>
+      <c r="D100" s="3">
+        <v>-1004300</v>
       </c>
       <c r="E100" s="3">
+        <v>-381400</v>
+      </c>
+      <c r="F100" s="3">
         <v>-257500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1234200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1031100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-105100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-614800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-252600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>182700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-597100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>556600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1572200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1752900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-472100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>864000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2505200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-82400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>3259000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>606800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>4193100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2380000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>475500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>383300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-68600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-390500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-569400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-419200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>692900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1909300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-564100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-229500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>2462600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>1161900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>1772300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>415900</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-30000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-104600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>251900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-105700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-141500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>252900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>466600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-72400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-137600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>248400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>434700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-63400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-197900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>44100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-138900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>82900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-413700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-392000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-8800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>96100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-60200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>123900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>63500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-64700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-19000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>150400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>171000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-65200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-31600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-44300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-13900</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-5300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>42400</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-1331100</v>
       </c>
       <c r="E102" s="3">
+        <v>1474200</v>
+      </c>
+      <c r="F102" s="3">
         <v>1840300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>430400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1319000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-6263900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3387700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2534200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-638500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-653200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>721700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-756400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1838300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2366600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1268100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>3919700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2107000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1663300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>176100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>4659800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>939800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>793500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-171600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-132900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-115900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-30700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-323400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>299400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1167700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>605200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1085000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>515000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>825900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-736300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1679300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
   <si>
     <t>JD</t>
   </si>
@@ -656,492 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="3">
         <v>41491400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>47538200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>37121200</v>
       </c>
-      <c r="G8" s="3">
-        <v>40099200</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" s="3">
         <v>36015400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>43164800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>33947000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>39702000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>35368900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>41652000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>33646800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>37201800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>33091600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>38014500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>31089400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>36450800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>28282100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>31226500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>25672200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>29627300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>23065300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>26281900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>20763100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>22959900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>18498800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>19581700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>14663400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>17546300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>14366400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>16349600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>12428800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>13832100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>10939000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>11548800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>8751100</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="3">
         <v>37617400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>43017600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>33020500</v>
       </c>
-      <c r="G9" s="3">
-        <v>36147500</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="H9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" s="3">
         <v>32835000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>39467200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>30722800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>36288800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>32363200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>35796100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>28646000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>32211800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>28473300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>32899800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>26669600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>31893800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>24228300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>26891500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>21723700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>25407600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>19510100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>22586700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>17665900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>19579600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>15720700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>16797400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>12408700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>15176900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>12334900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>14218500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>10502000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>11955000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>18670800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>19852900</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>14923400</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="3">
         <v>3873900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4520600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4100800</v>
       </c>
-      <c r="G10" s="3">
-        <v>3951800</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" s="3">
         <v>3180400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3697600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3224200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3413300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3005700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5855900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5000800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4990000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4618200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5114600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4419800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4557000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4053800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>4335000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3948500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>4219700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3555200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3695200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3097200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3380300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2778100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2784300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2254700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2369400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2031400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2131100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1926800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1877100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>-7731900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>-8304100</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>-6172300</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1180,118 +1193,122 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="3">
         <v>636800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>600600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>626700</v>
       </c>
-      <c r="G12" s="3">
-        <v>580300</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12" s="3">
         <v>558700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>612200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>520000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>561500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>609400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>602800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>557200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>551500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>600100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>562000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>565400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>526700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>627000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>623400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>601500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>527400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>616900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>549200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>548200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>565400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>564000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>505400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>478900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>395500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>342700</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>302600</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>257500</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>226400</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>184500</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>168700</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>175700</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1400,228 +1417,237 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="3">
         <v>117400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>394200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-58300</v>
       </c>
-      <c r="G14" s="3">
-        <v>-42900</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="3">
         <v>-4200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1104900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>106600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-75800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-198000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-11700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-173500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-4300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>490000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-2500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-82300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-12500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-11500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-154400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-50700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-28800</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>-598200</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>10</v>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>3100</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AG14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-      <c r="AI14" s="3" t="s">
-        <v>10</v>
+      <c r="AI14" s="3">
+        <v>0</v>
       </c>
       <c r="AJ14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL14" s="3" t="s">
+      <c r="AK14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>50200</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
+        <v>315600</v>
+      </c>
+      <c r="F15" s="3">
         <v>419800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>284800</v>
       </c>
-      <c r="G15" s="3">
-        <v>266100</v>
-      </c>
       <c r="H15" s="3">
-        <v>58200</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
+        <v>307000</v>
+      </c>
+      <c r="J15" s="3">
         <v>444100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>245600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>238100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>285300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>61900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>61200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>58100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>54100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>51900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>53400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>53300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>50600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>51900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>50300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>43800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>44500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>72600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>22500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>22600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>67800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>65800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>63900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>64600</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>64000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>66700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>66300</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>65700</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>63900</v>
-      </c>
-      <c r="AK15" s="3">
-        <v>65100</v>
       </c>
       <c r="AL15" s="3">
         <v>65100</v>
       </c>
+      <c r="AM15" s="3">
+        <v>65100</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="3">
         <v>40039800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>46260600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>35404200</v>
       </c>
-      <c r="G17" s="3">
-        <v>38654200</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="H17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I17" s="3">
         <v>34949000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>42263500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>32672100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>38700800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>34502000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>40980800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>32437200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>36675000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>33249000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>38068500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>30723700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>36407600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>28051100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>31143700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>25026300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>28884000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>22699300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>26200400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>19997300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>22613600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>18311500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>19718100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>14754400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>17694700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>14365700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>16586500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>12354200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>13891900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>10842800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>11598000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>8785200</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="3">
         <v>1451500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1277600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1717000</v>
       </c>
-      <c r="G18" s="3">
-        <v>1445000</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="H18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I18" s="3">
         <v>1066400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>901300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1275000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1001200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>866900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>671200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1209600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>526700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-157400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-54000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>365700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>43200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>231000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>82800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>645900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>743300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>366100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>81500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>765800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>346300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>187200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-136400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-91100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-148400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-236900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>74600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-59800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>96200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-49200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-34100</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,558 +1950,574 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="3">
         <v>-587200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>446800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-494800</v>
       </c>
-      <c r="G20" s="3">
-        <v>-755600</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I20" s="3">
         <v>-268100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>549900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-409400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-355300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>140900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-34800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-64400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>271200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-197500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-591600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-698300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>140600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>378600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3292200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>617500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1840500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-115100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>573300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-562800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-172200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>990200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-542100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>534700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-120500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>265800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>95700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>120500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>42100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-15000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-113100</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-26100</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2088900</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3">
+        <v>2354300</v>
+      </c>
+      <c r="F21" s="3">
         <v>1250600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2496700</v>
       </c>
-      <c r="G21" s="3">
-        <v>2466800</v>
-      </c>
       <c r="H21" s="3">
-        <v>1392700</v>
+        <v>0</v>
       </c>
       <c r="I21" s="3">
+        <v>1641600</v>
+      </c>
+      <c r="J21" s="3">
         <v>795500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1929900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1594700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1011300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>652900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1166500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>803700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-124000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-641300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-321900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>153900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>841900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3397100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1272200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2592000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>472700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>658500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>207000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>126300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1433100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-660600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>476100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-259600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>437800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-31900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>117300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-15000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>219700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-158100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-50000</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="3">
         <v>82700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>126900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>97100</v>
       </c>
-      <c r="G22" s="3">
-        <v>94700</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I22" s="3">
         <v>83200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>130700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>97300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>90200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>85900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>98400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>80000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>67300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>47600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>61500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>39300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>33400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>35900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>41200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>43900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>47800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>32700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>33800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>25100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>23700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>28600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>21000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>33700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>34400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>32800</v>
       </c>
-      <c r="AG22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH22" s="3">
+      <c r="AH22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI22" s="3">
         <v>42000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>30900</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>27600</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>9200</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>10400</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="3">
         <v>1838600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1591200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2173100</v>
       </c>
-      <c r="G23" s="3">
-        <v>2148900</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="H23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I23" s="3">
         <v>1255500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>466200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1480400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1342200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1136700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>538000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1065200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>730700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-402500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-707200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-371900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>150400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>573800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3333800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1219500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2536000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>218300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>621000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>177900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>150400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1148800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-699500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>409900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-303300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>233600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-141200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>153100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-48600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>53600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-171500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-70600</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="3">
         <v>284300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>102800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>343000</v>
       </c>
-      <c r="G24" s="3">
-        <v>278200</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I24" s="3">
         <v>235400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>196600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>353500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>387600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>234200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>83900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>241900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>170600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>83300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>25600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>92700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>81800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>66700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-46200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>101700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>117400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>51500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>73800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>93100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>67000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>42700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>8900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>7200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>23400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>21700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>7900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-2400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>13000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>14600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="3">
         <v>1554300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1488400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1830100</v>
       </c>
-      <c r="G26" s="3">
-        <v>1870700</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="H26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I26" s="3">
         <v>1020000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>269600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1127000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>954600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>902400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>454100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>823300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>560100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-485800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-732800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-464600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>68600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>507000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3380000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1117800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2418600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>166800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>547200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>84800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>83400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1106100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-708400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>402600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-326700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>212000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-143100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>145200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-46200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>40500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-186100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-70900</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="3">
         <v>1500700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1350000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1672400</v>
       </c>
-      <c r="G27" s="3">
-        <v>1739900</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="H27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I27" s="3">
         <v>987500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>477900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1087600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>907400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>911500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>427500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>823800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>608400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-413000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-711600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-398900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>114100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>503500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3386100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1114100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2423600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>169200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>559600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>94300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>94500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1118200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-697800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>420000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-317400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>218800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-134900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>150500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-42600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>43500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-183400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-68000</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3006,19 +3067,22 @@
         <v>0</v>
       </c>
       <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-31100</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-8700</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-67100</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>-66100</v>
       </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,228 +3304,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="3">
         <v>587200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-446800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>494800</v>
       </c>
-      <c r="G32" s="3">
-        <v>755600</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I32" s="3">
         <v>268100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-549900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>409400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>355300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-140900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>34800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>64400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-271200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>197500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>591600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>698300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-140600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-378600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3292200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-617500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1840500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>115100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-573300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>562800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>172200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-990200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>542100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-534700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>120500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-265800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-95700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-120500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-42100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>15000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>113100</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="3">
         <v>1500700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1350000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1672400</v>
       </c>
-      <c r="G33" s="3">
-        <v>1739900</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="H33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I33" s="3">
         <v>987500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>477900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1087600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>907400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>911500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>427500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>823800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>608400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-413000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-711600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-398900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>114100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>503500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3386100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1114100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2423600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>169200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>559600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>94300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>94500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1118200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-697800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>420000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-317400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>218800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-134900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>150500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-73700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>34800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-250600</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-134000</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="3">
         <v>1500700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1350000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1672400</v>
       </c>
-      <c r="G35" s="3">
-        <v>1739900</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="H35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I35" s="3">
         <v>987500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>477900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1087600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>907400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>911500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>427500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>823800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>608400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-413000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-711600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-398900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>114100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>503500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3386100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1114100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2423600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>169200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>559600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>94300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>94500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1118200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-697800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>420000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-317400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>218800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-134900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>150500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-73700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>34800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-250600</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-134000</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,998 +3958,1026 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="3">
         <v>13336700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>14844300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>14126700</v>
       </c>
-      <c r="G41" s="3">
-        <v>11627500</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I41" s="3">
         <v>11304800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>10138600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>15893800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>12550500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>10827000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11117800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11516500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10957700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>11662700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9750300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>12508900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>13981000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9940000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>11983000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10773900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10546800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6867200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5692900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4946600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5007900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5202700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4975900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4758300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5055400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5051100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3812400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3207200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4134000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3435700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2263900</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>3611700</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>13420400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>17213800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>13087300</v>
       </c>
-      <c r="G42" s="3">
-        <v>16156300</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>12515900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>16676900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>17320700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>19869700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>17824500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>19891600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>17746500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>16991400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>13268900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>15784600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>14548600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>10836500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>8835100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>8432300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>7132600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>7180900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>4632500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>3788300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>3767300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>3752600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>644900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>295600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>723900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1829700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1713700</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1274500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>2383300</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1890700</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>3089800</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>2623300</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>1793200</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" s="3">
         <v>4785200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4340300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3262500</v>
       </c>
-      <c r="G43" s="3">
-        <v>3459200</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I43" s="3">
         <v>2984600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3402500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3472400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3361400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3046900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3766700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3346500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2713700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2280400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2397400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2461700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3709000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2365400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2013200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2079900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1986200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1702600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1844100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2499900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2102900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1622800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2463500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2348300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3701700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2819300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>4850500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>5597400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>6769800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>5409200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>4288500</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>4025000</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="3">
         <v>13151500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>12237900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>10390300</v>
       </c>
-      <c r="G44" s="3">
-        <v>9721300</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I44" s="3">
         <v>9416800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>9597900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>8858600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>8764400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>9214900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>10989300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>9913900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>10569600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>9498500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>10416300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>8535300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>9445600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>8285800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>8203400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>8155700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>8027700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>7980200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>8920400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>7431900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>6954700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5841700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>6394500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5578100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>6227400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5188800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>6188800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>5388800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4622900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>3906300</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>4204300</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>3287100</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="3">
         <v>3256400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3333400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2648700</v>
       </c>
-      <c r="G45" s="3">
-        <v>2335000</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I45" s="3">
         <v>2110400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2534700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2382300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2481100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2573200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3729100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3676900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3808900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3226200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2940200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2998600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3046100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2252800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2052400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2445100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2537400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1621900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1172100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1310600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1654700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1212300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1098700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1921800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2095000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1439700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>945200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1774000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2015800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1285200</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>3842100</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>840300</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" s="3">
         <v>49229000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>52978900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>44351300</v>
       </c>
-      <c r="G46" s="3">
-        <v>44338200</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="H46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I46" s="3">
         <v>39342400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>43409200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>49010200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>48148000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>44417800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>49494400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>46200300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>45041200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>39936700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>41288800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>41053100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>41018200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>31679100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>32684300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>30587100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>30279000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>22804500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>21417800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>19956300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>19472800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>14524500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>15228200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>15330400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>18909200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>16212600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>17071400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>18350700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>19433200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>17126200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>15551100</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>13557200</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="3">
         <v>17073400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>15922500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>20297000</v>
       </c>
-      <c r="G47" s="3">
-        <v>19536700</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I47" s="3">
         <v>18755100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>19403200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>8591100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>8914000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>9840600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>9763100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>10218500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>10205600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>9930000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>11340700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>12655200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>13323000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>13426300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>13584000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>11753100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>10996100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>9079600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>8775800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>8358600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>8423900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>8106100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>6863300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>7013800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>5555200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>4438500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>4241400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2881600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2652400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>3265500</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>3299200</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>3258900</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" s="3">
         <v>15946300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>15540700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>16188600</v>
       </c>
-      <c r="G48" s="3">
-        <v>14733400</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I48" s="3">
         <v>14162300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>14217900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13591700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>12701500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>12968600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12477900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>11626200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10116500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9642700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8094300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7452400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7186400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6362600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6401400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6278600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5475000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5079500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5405300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5221700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4807300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4842500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>4013700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3446300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2997300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2456000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2340500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1904000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1599700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1382600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1311100</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1280900</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="3">
         <v>9651900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9636100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9469000</v>
       </c>
-      <c r="G49" s="3">
-        <v>9199400</v>
-      </c>
-      <c r="H49" s="3">
+      <c r="H49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I49" s="3">
         <v>9037000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9375100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9491300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9557800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9587700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9320200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9128900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7500300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7423000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4491400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4519900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4465800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4137700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3966100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4229400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3622600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3318700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3333000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3303300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3256200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3246200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3214100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3076700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2868200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2862900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3026700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3021300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2440200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2475700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2513800</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>2566700</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,118 +5199,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" s="3">
         <v>1179100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1194100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1205100</v>
       </c>
-      <c r="G52" s="3">
-        <v>1645000</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I52" s="3">
         <v>1797400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2012600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3719400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3744500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3191100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2862700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2898300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4113300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3790000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3193600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2984600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2388700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2162100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2146600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2308600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1568800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1633700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1060400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1013300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1545900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2025800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1057800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1019700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1040600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>618800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>635500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>620000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>687900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>580500</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1665500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>308700</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E54" s="3">
         <v>93414500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>95660300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>91747000</v>
       </c>
-      <c r="G54" s="3">
-        <v>89671800</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I54" s="3">
         <v>83349100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>88699300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>84613800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>83273400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>80218400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>83918300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>80072100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>76976900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>70722500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>68408700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>68665100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>68382000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>57767800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>58782500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>55156900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>51941500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>41916200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>39992300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>37853200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>37506100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>32745200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>30377000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>29887000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>31370400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>26588900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>27315600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>26777600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>26813400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>24830500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>23323100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>20972500</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,668 +5622,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E57" s="3">
         <v>24762600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>21716900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>23243400</v>
       </c>
-      <c r="G57" s="3">
-        <v>25147000</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I57" s="3">
         <v>16393700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>18762200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>21045800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>20960400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>17677700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>22711200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>20845600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>22277500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>17322400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>19427400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>18034400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>18431300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>13566400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>14950600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>15570300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>14940700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>12266000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>13973100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>13355500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>14326200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>10927000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>11647500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>10957000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>12582100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>8938300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>11032500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>10032000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>10014300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>6362200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>6695000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>6031800</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E58" s="3">
         <v>1658000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2080700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2474700</v>
       </c>
-      <c r="G58" s="3">
-        <v>1850000</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="H58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I58" s="3">
         <v>1817900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1803600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2992800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3570700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3238200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1712300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2486300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1912100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2368200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>601800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>999000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>80800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>598900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>453800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>934600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1815600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1357000</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
       <c r="Z58" s="3">
         <v>0</v>
       </c>
       <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="3">
         <v>21000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>285600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>660100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1340300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1701400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1939000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1912200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1825900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1807800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2944100</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1615600</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1993900</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" s="3">
         <v>5757900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9523900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6204000</v>
       </c>
-      <c r="G59" s="3">
-        <v>5787600</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I59" s="3">
         <v>5333000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9546600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6126800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5773100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5261700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13156300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12082900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11328000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10549700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10507800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9989200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9769000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>8417900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8818700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>8928800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>8582000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>7926600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>7586700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>7088800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>7054300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>6348400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>5245200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4735000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4852800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4456200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4604900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4511800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4433200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>6832000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>6921700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>4873400</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E60" s="3">
         <v>39155100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>41035300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>37857700</v>
       </c>
-      <c r="G60" s="3">
-        <v>38562100</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I60" s="3">
         <v>34083400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>37463500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>35967200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>35809100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>32635700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>37579800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>35414800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>35517700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>30240300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>30537000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>29022600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>28281100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>22583300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>24223100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>25433700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>25338300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>21549600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>21559800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>20444300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>21401500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>17561000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>17552800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>17032300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>19136300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>15333500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>17549600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>16369700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>16255400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>16138300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>15232400</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>12899100</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>10390800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10217800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10070400</v>
       </c>
-      <c r="G61" s="3">
-        <v>10010600</v>
-      </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>7873800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7847000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6581300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6486900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6380500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4262200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3953200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3428100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2155300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1293200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1775800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1782600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1757100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1744300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1943300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2002600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2702700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1547800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1568600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1512300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1480700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1434100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1384800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1408600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1036900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1621000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2315500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2602100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1957100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1330600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1488500</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62" s="3">
         <v>109800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>114400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>129600</v>
       </c>
-      <c r="G62" s="3">
-        <v>124400</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I62" s="3">
         <v>135600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>148800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>204600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>220200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>244000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3430500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3244000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3008100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3001200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2576600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2450600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2498700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1952600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1965700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1980600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1611900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1376100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1390500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1409600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1145200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>914000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>232400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>255700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>295100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>326300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>370000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>400900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>438400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>471400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>765600</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>430900</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E66" s="3">
         <v>50877300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>52737600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>49442400</v>
       </c>
-      <c r="G66" s="3">
-        <v>50046900</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="H66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I66" s="3">
         <v>43467800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>46902100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>44008000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>43659800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>40329400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>53838000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>50759700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>48990000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>42210400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>39625000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>38058200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>37251100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>31504700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>32676400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>32970600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>31849600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>28618600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>27388100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>26166900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>26836400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>22565900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>21696500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>20936000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>23011700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>18812300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>19592200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>19135000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>19340200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>19650900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>18394100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>15844000</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E72" s="3">
+      <c r="E72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F72" s="3">
         <v>11407000</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="G72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I72" s="3">
         <v>6789600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7073900</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>10</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N72" s="3">
         <v>4620900</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>10</v>
       </c>
       <c r="P72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R72" s="3">
         <v>4876200</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>10</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V72" s="3">
         <v>5422100</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X72" s="3">
+      <c r="X72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y72" s="3">
         <v>-1479900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-1609600</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AB72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AC72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD72" s="3">
         <v>-3287700</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AF72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH72" s="3">
         <v>-3205500</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AI72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AJ72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK72" s="3">
         <v>-3104800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-3159800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-2968300</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E76" s="3">
         <v>32291300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>32791300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>32591200</v>
       </c>
-      <c r="G76" s="3">
-        <v>30379400</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="H76" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I76" s="3">
         <v>30798400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>32698000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>31534400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>30581500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>30790500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>30080300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>29312400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>27987000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>28512100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>28783800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>30606900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>31130900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>26263200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>26106000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>22186300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>20091900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13297600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12604200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>11686300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>10669800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>10179200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>8680500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>8951000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>8358800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>7776600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>7723400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>7642600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>7473100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>5179500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>4929000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>5128500</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E81" s="3">
         <v>1500700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1350000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1672400</v>
       </c>
-      <c r="G81" s="3">
-        <v>1739900</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="H81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I81" s="3">
         <v>987500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>477900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1087600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>907400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>911500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>427500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>823800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>608400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-413000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-711600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-398900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>114100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>503500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3386100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1114100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2423600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>169200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>559600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>94300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>94500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1118200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-697800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>420000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-317400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>218800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-134900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>150500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-73700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>34800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-250600</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-134000</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,8 +8195,9 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8006,32 +8205,32 @@
         <v>10</v>
       </c>
       <c r="E83" s="3">
+        <v>264200</v>
+      </c>
+      <c r="F83" s="3">
         <v>317300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>187900</v>
       </c>
-      <c r="G83" s="3">
-        <v>177700</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I83" s="3">
         <v>236400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>415100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>153800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>149900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>201900</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
@@ -8107,8 +8306,11 @@
       <c r="AL83" s="3">
         <v>0</v>
       </c>
+      <c r="AM83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2516600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3410100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-886600</v>
       </c>
-      <c r="G89" s="3">
-        <v>6982100</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I89" s="3">
         <v>-1567100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2765900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2056300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6413300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3145500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2606200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1264300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4680400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-481200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>891700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2053700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4149200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1045200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>725700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1806000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3922400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-243300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>194300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3085000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>507700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>875500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>309700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2355000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-541300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>200500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>52300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2767300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>650300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-433900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1047900</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,41 +9027,42 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E91" s="3">
         <v>-320100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-815200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-763800</v>
       </c>
-      <c r="G91" s="3">
-        <v>-457000</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I91" s="3">
         <v>-398900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1225400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-684300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-497400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-423200</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
@@ -8917,8 +9138,11 @@
       <c r="AL91" s="3">
         <v>0</v>
       </c>
+      <c r="AM91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,118 +9364,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E94" s="3">
         <v>2237400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1710200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>3097200</v>
       </c>
-      <c r="G94" s="3">
-        <v>-5301700</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I94" s="3">
         <v>3935200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8894800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>2050800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3878400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>2430000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2524700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1347600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4299300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>629900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2588300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4230000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2595800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1062300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1907800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1844800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3446700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1293100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>377600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-873100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3212700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-168500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-317800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-364300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2919400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-135000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>624600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-620100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-4568600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-980900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-2206600</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-3057800</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,40 +9520,41 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E96" s="3">
+      <c r="E96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" s="3">
         <v>1132100</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J96" s="3">
         <v>950700</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="K96" s="3" t="s">
         <v>10</v>
       </c>
       <c r="L96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9397,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,334 +9970,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1004300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-381400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-257500</v>
       </c>
-      <c r="G100" s="3">
-        <v>-1234200</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I100" s="3">
         <v>-1031100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-105100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-614800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-252600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>182700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-597100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>556600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1572200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1752900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-472100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>864000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2505200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-82400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>3259000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>606800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>4193100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2380000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>475500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>383300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-68600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-390500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-569400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-419200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>692900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1909300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-564100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-229500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>2462600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>1161900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>1772300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>415900</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E101" s="3">
         <v>-18000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-30000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-104600</v>
       </c>
-      <c r="G101" s="3">
-        <v>251900</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I101" s="3">
         <v>-105700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-141500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>252900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>466600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-72400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-137600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>248400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>434700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-63400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-197900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>44100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-138900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>82900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-413700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-392000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-8800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>96100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-60200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>123900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>63500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-64700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-19000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>150400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>171000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-65200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-31600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-44300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-13900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-5300</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>42400</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1331100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1474200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1840300</v>
       </c>
-      <c r="G102" s="3">
-        <v>430400</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>1319000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6263900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3387700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2534200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-638500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-653200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>721700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-756400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1838300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2366600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1268100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3919700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2107000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1663300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>176100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>4659800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>939800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>793500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-171600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-132900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-115900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-30700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-323400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>299400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1167700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>605200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1085000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>515000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>825900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-736300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-1679300</v>
       </c>
     </row>
